--- a/castellan_btm_model/Castellan_BESS_Model.xlsx
+++ b/castellan_btm_model/Castellan_BESS_Model.xlsx
@@ -11,12 +11,14 @@
     <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Sizing Comparison" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="CF_Calc" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Load Profile" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Bill Impact" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Dispatch" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Cash Flow" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Backup Resilience" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Sensitivity" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Solar + Storage" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Value Stacking" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Load Profile" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Bill Impact" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Dispatch" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Cash Flow" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Global Adjustment" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Sensitivity" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +27,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="$0.0000"/>
     <numFmt numFmtId="165" formatCode="$0.00"/>
     <numFmt numFmtId="166" formatCode="$#,##0"/>
@@ -35,7 +37,6 @@
     <numFmt numFmtId="170" formatCode="0.0 &quot;yrs&quot;"/>
     <numFmt numFmtId="171" formatCode="#,##0 &quot;kWh&quot;"/>
     <numFmt numFmtId="172" formatCode="#,##0.0 &quot;kW&quot;"/>
-    <numFmt numFmtId="173" formatCode="0.0 &quot;h&quot;"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -65,15 +66,15 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="13"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00C00000"/>
     </font>
   </fonts>
   <fills count="7">
@@ -82,6 +83,11 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -101,11 +107,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -135,46 +136,53 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -264,7 +272,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Simple Payback by Size (yrs)</a:t>
+              <a:t>Annual value streams ($/yr)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -272,14 +280,14 @@
     </title>
     <plotArea>
       <barChart>
-        <barDir val="col"/>
+        <barDir val="bar"/>
         <grouping val="clustered"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Sizing Comparison'!L4</f>
+              <f>'Value Stacking'!B4</f>
             </strRef>
           </tx>
           <spPr>
@@ -289,12 +297,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Sizing Comparison'!$B$5:$B$13</f>
+              <f>'Value Stacking'!$A$5:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Sizing Comparison'!$L$5:$L$13</f>
+              <f>'Value Stacking'!$B$5:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -308,21 +316,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Energy (kWh)</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -361,7 +354,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Monthly Energy (kWh)</a:t>
+              <a:t>Monthly Energy</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -443,7 +436,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Monthly Peak (kW)</a:t>
+              <a:t>Monthly Peak kW</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -637,7 +630,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Load vs Net Grid Draw</a:t>
+              <a:t>Load vs Net Grid</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -757,7 +750,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Battery SOC (kWh)</a:t>
+              <a:t>Battery SOC</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -845,7 +838,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Cumulative Cash Flow — Value pick: 50/150</a:t>
+              <a:t>Cumulative — Value pick: 50/150</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -859,7 +852,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Cash Flow'!C5</f>
+              <f>'Cash Flow'!C4</f>
             </strRef>
           </tx>
           <spPr>
@@ -877,12 +870,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cash Flow'!$A$6:$A$21</f>
+              <f>'Cash Flow'!$A$5:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Cash Flow'!$C$6:$C$21</f>
+              <f>'Cash Flow'!$C$5:$C$20</f>
             </numRef>
           </val>
         </ser>
@@ -933,7 +926,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Cumulative Cash Flow — Deep shave: 100/300</a:t>
+              <a:t>Cumulative — Deep shave: 100/300</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -947,7 +940,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Cash Flow'!G5</f>
+              <f>'Cash Flow'!G4</f>
             </strRef>
           </tx>
           <spPr>
@@ -965,12 +958,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cash Flow'!$E$6:$E$21</f>
+              <f>'Cash Flow'!$E$5:$E$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Cash Flow'!$G$6:$G$21</f>
+              <f>'Cash Flow'!$G$5:$G$20</f>
             </numRef>
           </val>
         </ser>
@@ -1013,12 +1006,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6480000" cy="2880000"/>
+    <ext cx="5040000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1167,7 +1160,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4680000" cy="2520000"/>
@@ -1189,7 +1182,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4680000" cy="2520000"/>
@@ -1499,7 +1492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G27"/>
+  <dimension ref="B2:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1521,12 +1514,12 @@
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Account 200027805928 · Ontario GS &gt;50 kW · built from interval data + 22 months of bills</t>
+          <t>Account 200027805928 · Ontario GS &gt;50 kW · interval data + 22 months of bills</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>THE SITUATION</t>
         </is>
@@ -1535,188 +1528,199 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>• Winter-heating load: peaks ~115–120 kW in winter, &lt;25 kW summer (load factor 22%).</t>
+          <t>• Winter-heating load: peaks ~115–120 kW winter, &lt;25 kW summer (load factor 22%).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>• Bill dominated by a demand charge ~$25.8/kW-month — each kW of peak ≈ $310/yr.</t>
+          <t>• Bill dominated by demand charge ~$25.8/kW-month — each kW of peak ≈ $310/yr.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>• A battery saves almost entirely by shaving the winter peak (flat energy rate → little arbitrage).</t>
+          <t>• Battery value is mostly winter peak-shaving. Solar is anti-correlated with this load (see Solar tab).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>• Peaks are long plateaus (6–72 h) so the battery is energy-limited: duration matters, not power.</t>
+          <t>• At ~120 kW the site is below the Class A / GA 5CP threshold (see Global Adjustment tab).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>HEADLINE — value pick 50 kW / 150 kWh (live)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Yr-1 total benefit</t>
         </is>
       </c>
-      <c r="E12" s="24">
-        <f>'Sizing Comparison'!H7</f>
+      <c r="E12" s="37">
+        <f>'Sizing Comparison'!J7</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>Net capex (after ITC)</t>
-        </is>
-      </c>
-      <c r="E13" s="24">
-        <f>'Sizing Comparison'!K7</f>
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>Net capex (after ITC+grant)</t>
+        </is>
+      </c>
+      <c r="E13" s="37">
+        <f>'Sizing Comparison'!M7</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>Simple payback</t>
-        </is>
-      </c>
-      <c r="E14" s="25">
-        <f>'Sizing Comparison'!L7</f>
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>Simple payback (battery only)</t>
+        </is>
+      </c>
+      <c r="E14" s="38">
+        <f>'Sizing Comparison'!N7</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>15-yr NPV @ discount</t>
         </is>
       </c>
-      <c r="E15" s="24">
-        <f>'Sizing Comparison'!M7</f>
+      <c r="E15" s="37">
+        <f>'Sizing Comparison'!O7</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>IRR</t>
         </is>
       </c>
-      <c r="E16" s="26">
-        <f>'Sizing Comparison'!N7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>HOW TO USE</t>
-        </is>
+      <c r="E16" s="39">
+        <f>'Sizing Comparison'!P7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>Combined payback w/ solar</t>
+        </is>
+      </c>
+      <c r="E17" s="38">
+        <f>'Value Stacking'!B17</f>
+        <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="27" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>TABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="40" t="inlineStr">
         <is>
           <t>Assumptions</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Edit yellow cells — tariff, battery, capex, ITC, value streams. All else recalcs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="27" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Edit yellow cells. Tariff, battery, capex, GA, grid programs, solar, finance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>Sizing Comparison</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>9 sizes: benefit, capex, payback, NPV, IRR. Green = recommended.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="27" t="inlineStr">
-        <is>
-          <t>Bill Impact</t>
-        </is>
-      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Month-by-month bill before vs after.</t>
+          <t>9 sizes with the full value stack, payback, NPV, IRR.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="27" t="inlineStr">
-        <is>
-          <t>Dispatch</t>
+      <c r="B22" s="40" t="inlineStr">
+        <is>
+          <t>Value Stacking</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hour-by-hour of what the battery does on a cold week + state of charge.</t>
+          <t>All value streams for the recommended battery + solar, combined payback.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="27" t="inlineStr">
-        <is>
-          <t>Cash Flow</t>
+      <c r="B23" s="40" t="inlineStr">
+        <is>
+          <t>Solar + Storage</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15-yr cash flow for two sizes with payback / NPV / IRR.</t>
+          <t>PV generation vs load and its (limited) value for this heating load.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="27" t="inlineStr">
-        <is>
-          <t>Backup Resilience</t>
+      <c r="B24" s="40" t="inlineStr">
+        <is>
+          <t>Global Adjustment</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Outage runtime by season.</t>
+          <t>Ontario Class A / 5CP — why this site is currently below the threshold.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="27" t="inlineStr">
-        <is>
-          <t>Sensitivity</t>
+      <c r="B25" s="40" t="inlineStr">
+        <is>
+          <t>Bill Impact / Dispatch</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Payback heat-map vs demand charge and battery cost.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="28" t="inlineStr">
-        <is>
-          <t>⚠ Confirm the $25.84/kW demand charge (kW vs 15-min kVA) against the real tariff — it drives the whole result.</t>
+          <t>Monthly bill before vs after; hourly battery behaviour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="40" t="inlineStr">
+        <is>
+          <t>Cash Flow / Sensitivity</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>15-yr cash flows; payback heat-map vs demand charge &amp; cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>⚠ Confirm the $25.84/kW demand charge (kW vs 15-min kVA) against the real tariff.</t>
         </is>
       </c>
     </row>
@@ -1724,15 +1728,15 @@
   <mergeCells count="12">
     <mergeCell ref="C21:G21"/>
     <mergeCell ref="C20:G20"/>
+    <mergeCell ref="B28:G28"/>
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="B9:G9"/>
     <mergeCell ref="C25:G25"/>
     <mergeCell ref="B8:G8"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="C19:G19"/>
     <mergeCell ref="C23:G23"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="B7:G7"/>
+    <mergeCell ref="C26:G26"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1740,6 +1744,659 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>15-Year Cash Flow (live from CF_Calc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>Value pick: 50/150</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>Deep shave: 100/300</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Net CF $</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Cumulative $</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Net CF $</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Cumulative $</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" s="31">
+        <f>'CF_Calc'!E7</f>
+        <v/>
+      </c>
+      <c r="C5" s="31">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="31">
+        <f>'CF_Calc'!E10</f>
+        <v/>
+      </c>
+      <c r="G5" s="31">
+        <f>F5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="31">
+        <f>'CF_Calc'!F7</f>
+        <v/>
+      </c>
+      <c r="C6" s="31">
+        <f>C5+B6</f>
+        <v/>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="31">
+        <f>'CF_Calc'!F10</f>
+        <v/>
+      </c>
+      <c r="G6" s="31">
+        <f>G5+F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="31">
+        <f>'CF_Calc'!G7</f>
+        <v/>
+      </c>
+      <c r="C7" s="31">
+        <f>C6+B7</f>
+        <v/>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="31">
+        <f>'CF_Calc'!G10</f>
+        <v/>
+      </c>
+      <c r="G7" s="31">
+        <f>G6+F7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="31">
+        <f>'CF_Calc'!H7</f>
+        <v/>
+      </c>
+      <c r="C8" s="31">
+        <f>C7+B8</f>
+        <v/>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="31">
+        <f>'CF_Calc'!H10</f>
+        <v/>
+      </c>
+      <c r="G8" s="31">
+        <f>G7+F8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="31">
+        <f>'CF_Calc'!I7</f>
+        <v/>
+      </c>
+      <c r="C9" s="31">
+        <f>C8+B9</f>
+        <v/>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="31">
+        <f>'CF_Calc'!I10</f>
+        <v/>
+      </c>
+      <c r="G9" s="31">
+        <f>G8+F9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="31">
+        <f>'CF_Calc'!J7</f>
+        <v/>
+      </c>
+      <c r="C10" s="31">
+        <f>C9+B10</f>
+        <v/>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="31">
+        <f>'CF_Calc'!J10</f>
+        <v/>
+      </c>
+      <c r="G10" s="31">
+        <f>G9+F10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="31">
+        <f>'CF_Calc'!K7</f>
+        <v/>
+      </c>
+      <c r="C11" s="31">
+        <f>C10+B11</f>
+        <v/>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="31">
+        <f>'CF_Calc'!K10</f>
+        <v/>
+      </c>
+      <c r="G11" s="31">
+        <f>G10+F11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="31">
+        <f>'CF_Calc'!L7</f>
+        <v/>
+      </c>
+      <c r="C12" s="31">
+        <f>C11+B12</f>
+        <v/>
+      </c>
+      <c r="E12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" s="31">
+        <f>'CF_Calc'!L10</f>
+        <v/>
+      </c>
+      <c r="G12" s="31">
+        <f>G11+F12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="31">
+        <f>'CF_Calc'!M7</f>
+        <v/>
+      </c>
+      <c r="C13" s="31">
+        <f>C12+B13</f>
+        <v/>
+      </c>
+      <c r="E13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="31">
+        <f>'CF_Calc'!M10</f>
+        <v/>
+      </c>
+      <c r="G13" s="31">
+        <f>G12+F13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="31">
+        <f>'CF_Calc'!N7</f>
+        <v/>
+      </c>
+      <c r="C14" s="31">
+        <f>C13+B14</f>
+        <v/>
+      </c>
+      <c r="E14" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" s="31">
+        <f>'CF_Calc'!N10</f>
+        <v/>
+      </c>
+      <c r="G14" s="31">
+        <f>G13+F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="31">
+        <f>'CF_Calc'!O7</f>
+        <v/>
+      </c>
+      <c r="C15" s="31">
+        <f>C14+B15</f>
+        <v/>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="31">
+        <f>'CF_Calc'!O10</f>
+        <v/>
+      </c>
+      <c r="G15" s="31">
+        <f>G14+F15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="31">
+        <f>'CF_Calc'!P7</f>
+        <v/>
+      </c>
+      <c r="C16" s="31">
+        <f>C15+B16</f>
+        <v/>
+      </c>
+      <c r="E16" t="n">
+        <v>11</v>
+      </c>
+      <c r="F16" s="31">
+        <f>'CF_Calc'!P10</f>
+        <v/>
+      </c>
+      <c r="G16" s="31">
+        <f>G15+F16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="31">
+        <f>'CF_Calc'!Q7</f>
+        <v/>
+      </c>
+      <c r="C17" s="31">
+        <f>C16+B17</f>
+        <v/>
+      </c>
+      <c r="E17" t="n">
+        <v>12</v>
+      </c>
+      <c r="F17" s="31">
+        <f>'CF_Calc'!Q10</f>
+        <v/>
+      </c>
+      <c r="G17" s="31">
+        <f>G16+F17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="31">
+        <f>'CF_Calc'!R7</f>
+        <v/>
+      </c>
+      <c r="C18" s="31">
+        <f>C17+B18</f>
+        <v/>
+      </c>
+      <c r="E18" t="n">
+        <v>13</v>
+      </c>
+      <c r="F18" s="31">
+        <f>'CF_Calc'!R10</f>
+        <v/>
+      </c>
+      <c r="G18" s="31">
+        <f>G17+F18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="31">
+        <f>'CF_Calc'!S7</f>
+        <v/>
+      </c>
+      <c r="C19" s="31">
+        <f>C18+B19</f>
+        <v/>
+      </c>
+      <c r="E19" t="n">
+        <v>14</v>
+      </c>
+      <c r="F19" s="31">
+        <f>'CF_Calc'!S10</f>
+        <v/>
+      </c>
+      <c r="G19" s="31">
+        <f>G18+F19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="31">
+        <f>'CF_Calc'!T7</f>
+        <v/>
+      </c>
+      <c r="C20" s="31">
+        <f>C19+B20</f>
+        <v/>
+      </c>
+      <c r="E20" t="n">
+        <v>15</v>
+      </c>
+      <c r="F20" s="31">
+        <f>'CF_Calc'!T10</f>
+        <v/>
+      </c>
+      <c r="G20" s="31">
+        <f>G19+F20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>Payback yr</t>
+        </is>
+      </c>
+      <c r="B22" s="32">
+        <f>'Sizing Comparison'!N7</f>
+        <v/>
+      </c>
+      <c r="E22" s="30" t="inlineStr">
+        <is>
+          <t>Payback yr</t>
+        </is>
+      </c>
+      <c r="F22" s="32">
+        <f>'Sizing Comparison'!N10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>NPV</t>
+        </is>
+      </c>
+      <c r="B23" s="31">
+        <f>'CF_Calc'!U7</f>
+        <v/>
+      </c>
+      <c r="E23" s="30" t="inlineStr">
+        <is>
+          <t>NPV</t>
+        </is>
+      </c>
+      <c r="F23" s="31">
+        <f>'CF_Calc'!U10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>IRR</t>
+        </is>
+      </c>
+      <c r="B24" s="33">
+        <f>'CF_Calc'!V7</f>
+        <v/>
+      </c>
+      <c r="E24" s="30" t="inlineStr">
+        <is>
+          <t>IRR</t>
+        </is>
+      </c>
+      <c r="F24" s="33">
+        <f>'CF_Calc'!V10</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ontario Global Adjustment / Class A (5CP) — eligibility &amp; potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Global Adjustment (GA) is the largest line item on most Ontario C&amp;I bills. How you pay it depends on class:</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Class B (this site today): GA is volumetric (¢/kWh) — already inside the $0.111/kWh energy rate. A battery only helps by reducing kWh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Class A: GA is billed on your share of the province’s top-5 coincident peak hours (5CP). Shaving load in those 5 hours cuts GA enormously — this is THE battery use-case in Ontario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Eligibility: Class A requires peak demand ≥ 1 MW automatically, or 500 kW–1 MW via the Industrial Conservation Initiative (ICI) opt-in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>This site peaks at ~115 kW — about 4.4× below even the 500 kW ICI floor. So 5CP/GA peak-shaving is NOT available today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>The scenario below shows what it WOULD be worth if the site grew into Class A (or aggregated with others). Toggle Assumptions!B24 = 1 to include it in the model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr"/>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Class A eligible? (Assumptions B24)</t>
+        </is>
+      </c>
+      <c r="B13" s="12">
+        <f>Assumptions!B24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Battery power (value pick), kW</t>
+        </is>
+      </c>
+      <c r="B14" s="12">
+        <f>'Sizing Comparison'!A7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>GA value per kW-yr (Assumptions B25)</t>
+        </is>
+      </c>
+      <c r="B15" s="14">
+        <f>Assumptions!B25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>Potential GA 5CP value ($/yr)</t>
+        </is>
+      </c>
+      <c r="B16" s="43">
+        <f>'Sizing Comparison'!G7</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A6:H6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1771,183 +2428,183 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Demand $/kW  ↓ / Battery $/kWh →</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Demand $/kW ↓ / $/kWh →</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="n">
+      <c r="A5" s="44" t="n">
         <v>10</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="13">
         <f>(150*400*(1-Assumptions!$B$20))/(238.7*10)</f>
         <v/>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="13">
         <f>(150*500*(1-Assumptions!$B$20))/(238.7*10)</f>
         <v/>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="13">
         <f>(150*600*(1-Assumptions!$B$20))/(238.7*10)</f>
         <v/>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="13">
         <f>(150*700*(1-Assumptions!$B$20))/(238.7*10)</f>
         <v/>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="13">
         <f>(150*800*(1-Assumptions!$B$20))/(238.7*10)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="n">
+      <c r="A6" s="44" t="n">
         <v>15</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="13">
         <f>(150*400*(1-Assumptions!$B$20))/(238.7*15)</f>
         <v/>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="13">
         <f>(150*500*(1-Assumptions!$B$20))/(238.7*15)</f>
         <v/>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="13">
         <f>(150*600*(1-Assumptions!$B$20))/(238.7*15)</f>
         <v/>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="13">
         <f>(150*700*(1-Assumptions!$B$20))/(238.7*15)</f>
         <v/>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="13">
         <f>(150*800*(1-Assumptions!$B$20))/(238.7*15)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="n">
+      <c r="A7" s="44" t="n">
         <v>20</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="13">
         <f>(150*400*(1-Assumptions!$B$20))/(238.7*20)</f>
         <v/>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="13">
         <f>(150*500*(1-Assumptions!$B$20))/(238.7*20)</f>
         <v/>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="13">
         <f>(150*600*(1-Assumptions!$B$20))/(238.7*20)</f>
         <v/>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="13">
         <f>(150*700*(1-Assumptions!$B$20))/(238.7*20)</f>
         <v/>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="13">
         <f>(150*800*(1-Assumptions!$B$20))/(238.7*20)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="n">
+      <c r="A8" s="44" t="n">
         <v>25.84</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="13">
         <f>(150*400*(1-Assumptions!$B$20))/(238.7*25.84)</f>
         <v/>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <f>(150*500*(1-Assumptions!$B$20))/(238.7*25.84)</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>(150*600*(1-Assumptions!$B$20))/(238.7*25.84)</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>(150*700*(1-Assumptions!$B$20))/(238.7*25.84)</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>(150*800*(1-Assumptions!$B$20))/(238.7*25.84)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="n">
+      <c r="A9" s="44" t="n">
         <v>30</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="13">
         <f>(150*400*(1-Assumptions!$B$20))/(238.7*30)</f>
         <v/>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="13">
         <f>(150*500*(1-Assumptions!$B$20))/(238.7*30)</f>
         <v/>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="13">
         <f>(150*600*(1-Assumptions!$B$20))/(238.7*30)</f>
         <v/>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="13">
         <f>(150*700*(1-Assumptions!$B$20))/(238.7*30)</f>
         <v/>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="13">
         <f>(150*800*(1-Assumptions!$B$20))/(238.7*30)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="n">
+      <c r="A10" s="44" t="n">
         <v>40</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="13">
         <f>(150*400*(1-Assumptions!$B$20))/(238.7*40)</f>
         <v/>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="13">
         <f>(150*500*(1-Assumptions!$B$20))/(238.7*40)</f>
         <v/>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="13">
         <f>(150*600*(1-Assumptions!$B$20))/(238.7*40)</f>
         <v/>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="13">
         <f>(150*700*(1-Assumptions!$B$20))/(238.7*40)</f>
         <v/>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <f>(150*800*(1-Assumptions!$B$20))/(238.7*40)</f>
         <v/>
       </c>
@@ -1955,7 +2612,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Cells = simple payback in years. Lower is better.</t>
+          <t>Cells = simple payback (yrs). Lower is better.</t>
         </is>
       </c>
     </row>
@@ -1970,25 +2627,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Castellan BESS — Assumptions  (edit the YELLOW cells; everything recalculates)</t>
+          <t>Castellan BESS — Assumptions  (edit YELLOW; everything recalculates live)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TARIFF  (derived from 22 bills, R²=0.9994)</t>
+          <t>TARIFF (derived from 22 bills, R²=0.9994)</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2660,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Blended commodity + delivery</t>
+          <t>Blended commodity+delivery</t>
         </is>
       </c>
     </row>
@@ -2046,11 +2703,6 @@
       <c r="B7" s="7" t="n">
         <v>0.025</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Utility inflation</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2063,7 +2715,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Set &gt;0 if on TOU/ULO to value arbitrage</t>
+          <t>Set &gt;0 only if on a TOU commodity</t>
         </is>
       </c>
     </row>
@@ -2076,11 +2728,6 @@
       <c r="B9" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Full charge/discharge cycles for arbitrage</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2123,16 +2770,11 @@
       <c r="B14" s="7" t="n">
         <v>0.025</v>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Lowers savings over time</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>CAPEX (installed, CAD)</t>
+          <t>BATTERY CAPEX (installed, CAD)</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2789,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Inverter / PCS</t>
+          <t>Inverter/PCS</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2804,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Battery modules — set 0 to test</t>
+          <t>Modules — set 0 to test</t>
         </is>
       </c>
     </row>
@@ -2175,11 +2817,6 @@
       <c r="B19" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>EPC, interconnect, controls</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2196,60 +2833,211 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>OPERATING / FINANCE  (model horizon = 15 yrs)</t>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Upfront incentive / grant ($)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>e.g. Save-on-Energy capital rebate</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>O&amp;M (% of capex / yr)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n">
-        <v>0.015</v>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>GLOBAL ADJUSTMENT / CLASS A (Ontario)</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>O&amp;M inflation (%/yr)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n">
-        <v>0.02</v>
+          <t>Class A eligible?  (1=yes, 0=no)</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Site peaks ~120 kW → NOT eligible (need ≥1 MW, or 500kW–1MW via ICI)</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>GA 5CP value ($/kW-yr of peak cut)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Typical Class A value if eligible</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>GRID PROGRAMS (IESO capacity / DR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Capacity/DR payment ($/kW-yr)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Via aggregator; typical $30–60 if enrolled</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Program availability factor</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Fraction of power bid into program</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>SOLAR PV (optional add-on)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PV size (kW-DC)</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Set &gt;0 to add solar</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PV specific yield (kWh/kW-yr)</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Southern Ontario ~1,150–1,250</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PV capex ($/kW)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Installed C&amp;I</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PV export credit ($/kWh)</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Net-metering credit for exports</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>FINANCE (horizon = 15 yrs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>O&amp;M (% of capex / yr)</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>O&amp;M inflation (%/yr)</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Discount rate (%)</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n">
+      <c r="B40" s="7" t="n">
         <v>0.08</v>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>For NPV</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Resilience / backup value ($/yr)</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Optional $ you assign to outage protection</t>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Optional $ for outage protection</t>
         </is>
       </c>
     </row>
@@ -2264,612 +3052,696 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="9.5" customWidth="1" min="3" max="3"/>
+    <col width="9.5" customWidth="1" min="4" max="4"/>
+    <col width="9.5" customWidth="1" min="5" max="5"/>
+    <col width="9.5" customWidth="1" min="6" max="6"/>
+    <col width="9.5" customWidth="1" min="7" max="7"/>
+    <col width="9.5" customWidth="1" min="8" max="8"/>
+    <col width="9.5" customWidth="1" min="9" max="9"/>
+    <col width="9.5" customWidth="1" min="10" max="10"/>
+    <col width="9.5" customWidth="1" min="11" max="11"/>
+    <col width="9.5" customWidth="1" min="12" max="12"/>
+    <col width="9.5" customWidth="1" min="13" max="13"/>
+    <col width="9.5" customWidth="1" min="14" max="14"/>
+    <col width="9.5" customWidth="1" min="15" max="15"/>
+    <col width="9.5" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Battery Sizing Comparison — all formulas live off the Assumptions tab</t>
+          <t>Battery Sizing Comparison — all live</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Annual benefit = demand savings (kW shaved × demand rate) + arbitrage + resilience value.</t>
+          <t>Total benefit stacks: demand savings + arbitrage + GA(5CP) + grid programs + resilience.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Power
-(kW)</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Energy
-(kWh)</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Dur
-(h)</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Pwr kW</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Enr kWh</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Dur h</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>kW-mo
-shaved/yr</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
+shaved</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Demand
-savings $</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
+$/yr</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Arbitrage
 $/yr</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>Resilience
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>GA 5CP
 $/yr</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
-        <is>
-          <t>Yr-1 total
-benefit $</t>
-        </is>
-      </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>Grid prog
+$/yr</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>Resil
+$/yr</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL
+benefit</t>
+        </is>
+      </c>
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>Capex $</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="L4" s="11" t="inlineStr">
         <is>
           <t>ITC $</t>
         </is>
       </c>
-      <c r="K4" s="10" t="inlineStr">
-        <is>
-          <t>Net capex $</t>
-        </is>
-      </c>
-      <c r="L4" s="10" t="inlineStr">
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>Net
+capex $</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="inlineStr">
         <is>
           <t>Payback
-(yr)</t>
-        </is>
-      </c>
-      <c r="M4" s="10" t="inlineStr">
+yr</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="inlineStr">
         <is>
           <t>15-yr
 NPV $</t>
         </is>
       </c>
-      <c r="N4" s="10" t="inlineStr">
+      <c r="P4" s="11" t="inlineStr">
         <is>
           <t>IRR</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="13">
         <f>B5/A5</f>
         <v/>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="13" t="n">
         <v>153.9</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="14">
         <f>D5*Assumptions!$B$5</f>
         <v/>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="14">
         <f>B5*Assumptions!$B$13*Assumptions!$B$8*Assumptions!$B$9*Assumptions!$B$12</f>
         <v/>
       </c>
-      <c r="G5" s="13">
-        <f>Assumptions!$B$26</f>
-        <v/>
-      </c>
-      <c r="H5" s="13">
-        <f>E5+F5+G5</f>
-        <v/>
-      </c>
-      <c r="I5" s="13">
+      <c r="G5" s="14">
+        <f>A5*Assumptions!$B$25*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="H5" s="14">
+        <f>A5*Assumptions!$B$28*Assumptions!$B$29</f>
+        <v/>
+      </c>
+      <c r="I5" s="14">
+        <f>Assumptions!$B$41</f>
+        <v/>
+      </c>
+      <c r="J5" s="14">
+        <f>E5+F5+G5+H5+I5</f>
+        <v/>
+      </c>
+      <c r="K5" s="14">
         <f>A5*Assumptions!$B$17+B5*Assumptions!$B$18+Assumptions!$B$19</f>
         <v/>
       </c>
-      <c r="J5" s="13">
-        <f>I5*Assumptions!$B$20</f>
-        <v/>
-      </c>
-      <c r="K5" s="13">
-        <f>I5-J5</f>
-        <v/>
-      </c>
-      <c r="L5" s="12">
-        <f>K5/H5</f>
-        <v/>
-      </c>
-      <c r="M5" s="13">
+      <c r="L5" s="14">
+        <f>K5*Assumptions!$B$20</f>
+        <v/>
+      </c>
+      <c r="M5" s="14">
+        <f>K5-L5-Assumptions!$B$21</f>
+        <v/>
+      </c>
+      <c r="N5" s="13">
+        <f>M5/J5</f>
+        <v/>
+      </c>
+      <c r="O5" s="14">
         <f>'CF_Calc'!U5</f>
         <v/>
       </c>
-      <c r="N5" s="14">
+      <c r="P5" s="15">
         <f>'CF_Calc'!V5</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="17">
         <f>B6/A6</f>
         <v/>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>199.7</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="18">
         <f>D6*Assumptions!$B$5</f>
         <v/>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="18">
         <f>B6*Assumptions!$B$13*Assumptions!$B$8*Assumptions!$B$9*Assumptions!$B$12</f>
         <v/>
       </c>
-      <c r="G6" s="17">
-        <f>Assumptions!$B$26</f>
-        <v/>
-      </c>
-      <c r="H6" s="17">
-        <f>E6+F6+G6</f>
-        <v/>
-      </c>
-      <c r="I6" s="17">
+      <c r="G6" s="18">
+        <f>A6*Assumptions!$B$25*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="H6" s="18">
+        <f>A6*Assumptions!$B$28*Assumptions!$B$29</f>
+        <v/>
+      </c>
+      <c r="I6" s="18">
+        <f>Assumptions!$B$41</f>
+        <v/>
+      </c>
+      <c r="J6" s="18">
+        <f>E6+F6+G6+H6+I6</f>
+        <v/>
+      </c>
+      <c r="K6" s="18">
         <f>A6*Assumptions!$B$17+B6*Assumptions!$B$18+Assumptions!$B$19</f>
         <v/>
       </c>
-      <c r="J6" s="17">
-        <f>I6*Assumptions!$B$20</f>
-        <v/>
-      </c>
-      <c r="K6" s="17">
-        <f>I6-J6</f>
-        <v/>
-      </c>
-      <c r="L6" s="16">
-        <f>K6/H6</f>
-        <v/>
-      </c>
-      <c r="M6" s="17">
+      <c r="L6" s="18">
+        <f>K6*Assumptions!$B$20</f>
+        <v/>
+      </c>
+      <c r="M6" s="18">
+        <f>K6-L6-Assumptions!$B$21</f>
+        <v/>
+      </c>
+      <c r="N6" s="17">
+        <f>M6/J6</f>
+        <v/>
+      </c>
+      <c r="O6" s="18">
         <f>'CF_Calc'!U6</f>
         <v/>
       </c>
-      <c r="N6" s="18">
+      <c r="P6" s="19">
         <f>'CF_Calc'!V6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="20" t="n">
         <v>150</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="21">
         <f>B7/A7</f>
         <v/>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="21" t="n">
         <v>238.7</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="22">
         <f>D7*Assumptions!$B$5</f>
         <v/>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="22">
         <f>B7*Assumptions!$B$13*Assumptions!$B$8*Assumptions!$B$9*Assumptions!$B$12</f>
         <v/>
       </c>
-      <c r="G7" s="21">
-        <f>Assumptions!$B$26</f>
-        <v/>
-      </c>
-      <c r="H7" s="21">
-        <f>E7+F7+G7</f>
-        <v/>
-      </c>
-      <c r="I7" s="21">
+      <c r="G7" s="22">
+        <f>A7*Assumptions!$B$25*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="H7" s="22">
+        <f>A7*Assumptions!$B$28*Assumptions!$B$29</f>
+        <v/>
+      </c>
+      <c r="I7" s="22">
+        <f>Assumptions!$B$41</f>
+        <v/>
+      </c>
+      <c r="J7" s="22">
+        <f>E7+F7+G7+H7+I7</f>
+        <v/>
+      </c>
+      <c r="K7" s="22">
         <f>A7*Assumptions!$B$17+B7*Assumptions!$B$18+Assumptions!$B$19</f>
         <v/>
       </c>
-      <c r="J7" s="21">
-        <f>I7*Assumptions!$B$20</f>
-        <v/>
-      </c>
-      <c r="K7" s="21">
-        <f>I7-J7</f>
-        <v/>
-      </c>
-      <c r="L7" s="20">
-        <f>K7/H7</f>
-        <v/>
-      </c>
-      <c r="M7" s="21">
+      <c r="L7" s="22">
+        <f>K7*Assumptions!$B$20</f>
+        <v/>
+      </c>
+      <c r="M7" s="22">
+        <f>K7-L7-Assumptions!$B$21</f>
+        <v/>
+      </c>
+      <c r="N7" s="21">
+        <f>M7/J7</f>
+        <v/>
+      </c>
+      <c r="O7" s="22">
         <f>'CF_Calc'!U7</f>
         <v/>
       </c>
-      <c r="N7" s="22">
+      <c r="P7" s="23">
         <f>'CF_Calc'!V7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="16" t="n">
         <v>75</v>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="17">
         <f>B8/A8</f>
         <v/>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>238.7</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="18">
         <f>D8*Assumptions!$B$5</f>
         <v/>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="18">
         <f>B8*Assumptions!$B$13*Assumptions!$B$8*Assumptions!$B$9*Assumptions!$B$12</f>
         <v/>
       </c>
-      <c r="G8" s="17">
-        <f>Assumptions!$B$26</f>
-        <v/>
-      </c>
-      <c r="H8" s="17">
-        <f>E8+F8+G8</f>
-        <v/>
-      </c>
-      <c r="I8" s="17">
+      <c r="G8" s="18">
+        <f>A8*Assumptions!$B$25*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="H8" s="18">
+        <f>A8*Assumptions!$B$28*Assumptions!$B$29</f>
+        <v/>
+      </c>
+      <c r="I8" s="18">
+        <f>Assumptions!$B$41</f>
+        <v/>
+      </c>
+      <c r="J8" s="18">
+        <f>E8+F8+G8+H8+I8</f>
+        <v/>
+      </c>
+      <c r="K8" s="18">
         <f>A8*Assumptions!$B$17+B8*Assumptions!$B$18+Assumptions!$B$19</f>
         <v/>
       </c>
-      <c r="J8" s="17">
-        <f>I8*Assumptions!$B$20</f>
-        <v/>
-      </c>
-      <c r="K8" s="17">
-        <f>I8-J8</f>
-        <v/>
-      </c>
-      <c r="L8" s="16">
-        <f>K8/H8</f>
-        <v/>
-      </c>
-      <c r="M8" s="17">
+      <c r="L8" s="18">
+        <f>K8*Assumptions!$B$20</f>
+        <v/>
+      </c>
+      <c r="M8" s="18">
+        <f>K8-L8-Assumptions!$B$21</f>
+        <v/>
+      </c>
+      <c r="N8" s="17">
+        <f>M8/J8</f>
+        <v/>
+      </c>
+      <c r="O8" s="18">
         <f>'CF_Calc'!U8</f>
         <v/>
       </c>
-      <c r="N8" s="18">
+      <c r="P8" s="19">
         <f>'CF_Calc'!V8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="13">
         <f>B9/A9</f>
         <v/>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="13" t="n">
         <v>261</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="14">
         <f>D9*Assumptions!$B$5</f>
         <v/>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <f>B9*Assumptions!$B$13*Assumptions!$B$8*Assumptions!$B$9*Assumptions!$B$12</f>
         <v/>
       </c>
-      <c r="G9" s="13">
-        <f>Assumptions!$B$26</f>
-        <v/>
-      </c>
-      <c r="H9" s="13">
-        <f>E9+F9+G9</f>
-        <v/>
-      </c>
-      <c r="I9" s="13">
+      <c r="G9" s="14">
+        <f>A9*Assumptions!$B$25*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="H9" s="14">
+        <f>A9*Assumptions!$B$28*Assumptions!$B$29</f>
+        <v/>
+      </c>
+      <c r="I9" s="14">
+        <f>Assumptions!$B$41</f>
+        <v/>
+      </c>
+      <c r="J9" s="14">
+        <f>E9+F9+G9+H9+I9</f>
+        <v/>
+      </c>
+      <c r="K9" s="14">
         <f>A9*Assumptions!$B$17+B9*Assumptions!$B$18+Assumptions!$B$19</f>
         <v/>
       </c>
-      <c r="J9" s="13">
-        <f>I9*Assumptions!$B$20</f>
-        <v/>
-      </c>
-      <c r="K9" s="13">
-        <f>I9-J9</f>
-        <v/>
-      </c>
-      <c r="L9" s="12">
-        <f>K9/H9</f>
-        <v/>
-      </c>
-      <c r="M9" s="13">
+      <c r="L9" s="14">
+        <f>K9*Assumptions!$B$20</f>
+        <v/>
+      </c>
+      <c r="M9" s="14">
+        <f>K9-L9-Assumptions!$B$21</f>
+        <v/>
+      </c>
+      <c r="N9" s="13">
+        <f>M9/J9</f>
+        <v/>
+      </c>
+      <c r="O9" s="14">
         <f>'CF_Calc'!U9</f>
         <v/>
       </c>
-      <c r="N9" s="14">
+      <c r="P9" s="15">
         <f>'CF_Calc'!V9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n">
+      <c r="A10" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="B10" s="15" t="n">
-        <v>300</v>
-      </c>
-      <c r="C10" s="16">
+      <c r="B10" s="16" t="n">
+        <v>300</v>
+      </c>
+      <c r="C10" s="17">
         <f>B10/A10</f>
         <v/>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>285.8</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="18">
         <f>D10*Assumptions!$B$5</f>
         <v/>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="18">
         <f>B10*Assumptions!$B$13*Assumptions!$B$8*Assumptions!$B$9*Assumptions!$B$12</f>
         <v/>
       </c>
-      <c r="G10" s="17">
-        <f>Assumptions!$B$26</f>
-        <v/>
-      </c>
-      <c r="H10" s="17">
-        <f>E10+F10+G10</f>
-        <v/>
-      </c>
-      <c r="I10" s="17">
+      <c r="G10" s="18">
+        <f>A10*Assumptions!$B$25*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="H10" s="18">
+        <f>A10*Assumptions!$B$28*Assumptions!$B$29</f>
+        <v/>
+      </c>
+      <c r="I10" s="18">
+        <f>Assumptions!$B$41</f>
+        <v/>
+      </c>
+      <c r="J10" s="18">
+        <f>E10+F10+G10+H10+I10</f>
+        <v/>
+      </c>
+      <c r="K10" s="18">
         <f>A10*Assumptions!$B$17+B10*Assumptions!$B$18+Assumptions!$B$19</f>
         <v/>
       </c>
-      <c r="J10" s="17">
-        <f>I10*Assumptions!$B$20</f>
-        <v/>
-      </c>
-      <c r="K10" s="17">
-        <f>I10-J10</f>
-        <v/>
-      </c>
-      <c r="L10" s="16">
-        <f>K10/H10</f>
-        <v/>
-      </c>
-      <c r="M10" s="17">
+      <c r="L10" s="18">
+        <f>K10*Assumptions!$B$20</f>
+        <v/>
+      </c>
+      <c r="M10" s="18">
+        <f>K10-L10-Assumptions!$B$21</f>
+        <v/>
+      </c>
+      <c r="N10" s="17">
+        <f>M10/J10</f>
+        <v/>
+      </c>
+      <c r="O10" s="18">
         <f>'CF_Calc'!U10</f>
         <v/>
       </c>
-      <c r="N10" s="18">
+      <c r="P10" s="19">
         <f>'CF_Calc'!V10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="12" t="n">
         <v>400</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="13">
         <f>B11/A11</f>
         <v/>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="13" t="n">
         <v>301.2</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="14">
         <f>D11*Assumptions!$B$5</f>
         <v/>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="14">
         <f>B11*Assumptions!$B$13*Assumptions!$B$8*Assumptions!$B$9*Assumptions!$B$12</f>
         <v/>
       </c>
-      <c r="G11" s="13">
-        <f>Assumptions!$B$26</f>
-        <v/>
-      </c>
-      <c r="H11" s="13">
-        <f>E11+F11+G11</f>
-        <v/>
-      </c>
-      <c r="I11" s="13">
+      <c r="G11" s="14">
+        <f>A11*Assumptions!$B$25*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="H11" s="14">
+        <f>A11*Assumptions!$B$28*Assumptions!$B$29</f>
+        <v/>
+      </c>
+      <c r="I11" s="14">
+        <f>Assumptions!$B$41</f>
+        <v/>
+      </c>
+      <c r="J11" s="14">
+        <f>E11+F11+G11+H11+I11</f>
+        <v/>
+      </c>
+      <c r="K11" s="14">
         <f>A11*Assumptions!$B$17+B11*Assumptions!$B$18+Assumptions!$B$19</f>
         <v/>
       </c>
-      <c r="J11" s="13">
-        <f>I11*Assumptions!$B$20</f>
-        <v/>
-      </c>
-      <c r="K11" s="13">
-        <f>I11-J11</f>
-        <v/>
-      </c>
-      <c r="L11" s="12">
-        <f>K11/H11</f>
-        <v/>
-      </c>
-      <c r="M11" s="13">
+      <c r="L11" s="14">
+        <f>K11*Assumptions!$B$20</f>
+        <v/>
+      </c>
+      <c r="M11" s="14">
+        <f>K11-L11-Assumptions!$B$21</f>
+        <v/>
+      </c>
+      <c r="N11" s="13">
+        <f>M11/J11</f>
+        <v/>
+      </c>
+      <c r="O11" s="14">
         <f>'CF_Calc'!U11</f>
         <v/>
       </c>
-      <c r="N11" s="14">
+      <c r="P11" s="15">
         <f>'CF_Calc'!V11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="B12" s="15" t="n">
-        <v>300</v>
-      </c>
-      <c r="C12" s="16">
+      <c r="B12" s="16" t="n">
+        <v>300</v>
+      </c>
+      <c r="C12" s="17">
         <f>B12/A12</f>
         <v/>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>285.8</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="18">
         <f>D12*Assumptions!$B$5</f>
         <v/>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="18">
         <f>B12*Assumptions!$B$13*Assumptions!$B$8*Assumptions!$B$9*Assumptions!$B$12</f>
         <v/>
       </c>
-      <c r="G12" s="17">
-        <f>Assumptions!$B$26</f>
-        <v/>
-      </c>
-      <c r="H12" s="17">
-        <f>E12+F12+G12</f>
-        <v/>
-      </c>
-      <c r="I12" s="17">
+      <c r="G12" s="18">
+        <f>A12*Assumptions!$B$25*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="H12" s="18">
+        <f>A12*Assumptions!$B$28*Assumptions!$B$29</f>
+        <v/>
+      </c>
+      <c r="I12" s="18">
+        <f>Assumptions!$B$41</f>
+        <v/>
+      </c>
+      <c r="J12" s="18">
+        <f>E12+F12+G12+H12+I12</f>
+        <v/>
+      </c>
+      <c r="K12" s="18">
         <f>A12*Assumptions!$B$17+B12*Assumptions!$B$18+Assumptions!$B$19</f>
         <v/>
       </c>
-      <c r="J12" s="17">
-        <f>I12*Assumptions!$B$20</f>
-        <v/>
-      </c>
-      <c r="K12" s="17">
-        <f>I12-J12</f>
-        <v/>
-      </c>
-      <c r="L12" s="16">
-        <f>K12/H12</f>
-        <v/>
-      </c>
-      <c r="M12" s="17">
+      <c r="L12" s="18">
+        <f>K12*Assumptions!$B$20</f>
+        <v/>
+      </c>
+      <c r="M12" s="18">
+        <f>K12-L12-Assumptions!$B$21</f>
+        <v/>
+      </c>
+      <c r="N12" s="17">
+        <f>M12/J12</f>
+        <v/>
+      </c>
+      <c r="O12" s="18">
         <f>'CF_Calc'!U12</f>
         <v/>
       </c>
-      <c r="N12" s="18">
+      <c r="P12" s="19">
         <f>'CF_Calc'!V12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="12" t="n">
         <v>400</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="13">
         <f>B13/A13</f>
         <v/>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="13" t="n">
         <v>301.2</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="14">
         <f>D13*Assumptions!$B$5</f>
         <v/>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="14">
         <f>B13*Assumptions!$B$13*Assumptions!$B$8*Assumptions!$B$9*Assumptions!$B$12</f>
         <v/>
       </c>
-      <c r="G13" s="13">
-        <f>Assumptions!$B$26</f>
-        <v/>
-      </c>
-      <c r="H13" s="13">
-        <f>E13+F13+G13</f>
-        <v/>
-      </c>
-      <c r="I13" s="13">
+      <c r="G13" s="14">
+        <f>A13*Assumptions!$B$25*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="H13" s="14">
+        <f>A13*Assumptions!$B$28*Assumptions!$B$29</f>
+        <v/>
+      </c>
+      <c r="I13" s="14">
+        <f>Assumptions!$B$41</f>
+        <v/>
+      </c>
+      <c r="J13" s="14">
+        <f>E13+F13+G13+H13+I13</f>
+        <v/>
+      </c>
+      <c r="K13" s="14">
         <f>A13*Assumptions!$B$17+B13*Assumptions!$B$18+Assumptions!$B$19</f>
         <v/>
       </c>
-      <c r="J13" s="13">
-        <f>I13*Assumptions!$B$20</f>
-        <v/>
-      </c>
-      <c r="K13" s="13">
-        <f>I13-J13</f>
-        <v/>
-      </c>
-      <c r="L13" s="12">
-        <f>K13/H13</f>
-        <v/>
-      </c>
-      <c r="M13" s="13">
+      <c r="L13" s="14">
+        <f>K13*Assumptions!$B$20</f>
+        <v/>
+      </c>
+      <c r="M13" s="14">
+        <f>K13-L13-Assumptions!$B$21</f>
+        <v/>
+      </c>
+      <c r="N13" s="13">
+        <f>M13/J13</f>
+        <v/>
+      </c>
+      <c r="O13" s="14">
         <f>'CF_Calc'!U13</f>
         <v/>
       </c>
-      <c r="N13" s="14">
+      <c r="P13" s="15">
         <f>'CF_Calc'!V13</f>
         <v/>
       </c>
@@ -2877,13 +3749,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Green = value pick. Change Energy cost to 0 on Assumptions and watch Capex/Payback/NPV/IRR all move.</t>
+          <t>Green = value pick (50/150). With default inputs GA &amp; grid = $0 (not enabled). Turn them on in Assumptions.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2897,939 +3768,939 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Cash-flow engine (15 yrs) — feeds NPV/IRR on Sizing Comparison. Live.</t>
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Cash-flow engine (15 yrs) — feeds NPV/IRR. Live.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>size</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>net</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>benefit</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Y0</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
-      <c r="K4" s="10" t="inlineStr">
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>Y6</t>
         </is>
       </c>
-      <c r="L4" s="10" t="inlineStr">
+      <c r="L4" s="11" t="inlineStr">
         <is>
           <t>Y7</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr">
+      <c r="M4" s="11" t="inlineStr">
         <is>
           <t>Y8</t>
         </is>
       </c>
-      <c r="N4" s="10" t="inlineStr">
+      <c r="N4" s="11" t="inlineStr">
         <is>
           <t>Y9</t>
         </is>
       </c>
-      <c r="O4" s="10" t="inlineStr">
+      <c r="O4" s="11" t="inlineStr">
         <is>
           <t>Y10</t>
         </is>
       </c>
-      <c r="P4" s="10" t="inlineStr">
+      <c r="P4" s="11" t="inlineStr">
         <is>
           <t>Y11</t>
         </is>
       </c>
-      <c r="Q4" s="10" t="inlineStr">
+      <c r="Q4" s="11" t="inlineStr">
         <is>
           <t>Y12</t>
         </is>
       </c>
-      <c r="R4" s="10" t="inlineStr">
+      <c r="R4" s="11" t="inlineStr">
         <is>
           <t>Y13</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="11" t="inlineStr">
         <is>
           <t>Y14</t>
         </is>
       </c>
-      <c r="T4" s="10" t="inlineStr">
+      <c r="T4" s="11" t="inlineStr">
         <is>
           <t>Y15</t>
         </is>
       </c>
-      <c r="U4" s="10" t="inlineStr">
+      <c r="U4" s="11" t="inlineStr">
         <is>
           <t>NPV</t>
         </is>
       </c>
-      <c r="V4" s="10" t="inlineStr">
+      <c r="V4" s="11" t="inlineStr">
         <is>
           <t>IRR</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>30/60</t>
         </is>
       </c>
-      <c r="B5" s="11">
+      <c r="B5">
+        <f>'Sizing Comparison'!M5</f>
+        <v/>
+      </c>
+      <c r="C5">
+        <f>'Sizing Comparison'!J5</f>
+        <v/>
+      </c>
+      <c r="D5">
         <f>'Sizing Comparison'!K5</f>
         <v/>
       </c>
-      <c r="C5" s="11">
-        <f>'Sizing Comparison'!H5</f>
-        <v/>
-      </c>
-      <c r="D5" s="11">
-        <f>'Sizing Comparison'!I5</f>
-        <v/>
-      </c>
-      <c r="E5" s="11">
+      <c r="E5">
         <f>-B5</f>
         <v/>
       </c>
-      <c r="F5" s="11">
-        <f>C5*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D5*Assumptions!$B$23*(1+Assumptions!$B$24)^0</f>
-        <v/>
-      </c>
-      <c r="G5" s="11">
-        <f>C5*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D5*Assumptions!$B$23*(1+Assumptions!$B$24)^1</f>
-        <v/>
-      </c>
-      <c r="H5" s="11">
-        <f>C5*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D5*Assumptions!$B$23*(1+Assumptions!$B$24)^2</f>
-        <v/>
-      </c>
-      <c r="I5" s="11">
-        <f>C5*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D5*Assumptions!$B$23*(1+Assumptions!$B$24)^3</f>
-        <v/>
-      </c>
-      <c r="J5" s="11">
-        <f>C5*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D5*Assumptions!$B$23*(1+Assumptions!$B$24)^4</f>
-        <v/>
-      </c>
-      <c r="K5" s="11">
-        <f>C5*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D5*Assumptions!$B$23*(1+Assumptions!$B$24)^5</f>
-        <v/>
-      </c>
-      <c r="L5" s="11">
-        <f>C5*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D5*Assumptions!$B$23*(1+Assumptions!$B$24)^6</f>
-        <v/>
-      </c>
-      <c r="M5" s="11">
-        <f>C5*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D5*Assumptions!$B$23*(1+Assumptions!$B$24)^7</f>
-        <v/>
-      </c>
-      <c r="N5" s="11">
-        <f>C5*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D5*Assumptions!$B$23*(1+Assumptions!$B$24)^8</f>
-        <v/>
-      </c>
-      <c r="O5" s="11">
-        <f>C5*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D5*Assumptions!$B$23*(1+Assumptions!$B$24)^9</f>
-        <v/>
-      </c>
-      <c r="P5" s="11">
-        <f>C5*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D5*Assumptions!$B$23*(1+Assumptions!$B$24)^10</f>
-        <v/>
-      </c>
-      <c r="Q5" s="11">
-        <f>C5*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D5*Assumptions!$B$23*(1+Assumptions!$B$24)^11</f>
-        <v/>
-      </c>
-      <c r="R5" s="11">
-        <f>C5*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D5*Assumptions!$B$23*(1+Assumptions!$B$24)^12</f>
-        <v/>
-      </c>
-      <c r="S5" s="11">
-        <f>C5*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D5*Assumptions!$B$23*(1+Assumptions!$B$24)^13</f>
-        <v/>
-      </c>
-      <c r="T5" s="11">
-        <f>C5*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D5*Assumptions!$B$23*(1+Assumptions!$B$24)^14</f>
-        <v/>
-      </c>
-      <c r="U5" s="11">
-        <f>NPV(Assumptions!$B$25,F5:T5)+E5</f>
-        <v/>
-      </c>
-      <c r="V5" s="11">
+      <c r="F5">
+        <f>C5*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^0</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>C5*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^1</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>C5*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^2</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>C5*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^3</f>
+        <v/>
+      </c>
+      <c r="J5">
+        <f>C5*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^4</f>
+        <v/>
+      </c>
+      <c r="K5">
+        <f>C5*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^5</f>
+        <v/>
+      </c>
+      <c r="L5">
+        <f>C5*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^6</f>
+        <v/>
+      </c>
+      <c r="M5">
+        <f>C5*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^7</f>
+        <v/>
+      </c>
+      <c r="N5">
+        <f>C5*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^8</f>
+        <v/>
+      </c>
+      <c r="O5">
+        <f>C5*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^9</f>
+        <v/>
+      </c>
+      <c r="P5">
+        <f>C5*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^10</f>
+        <v/>
+      </c>
+      <c r="Q5">
+        <f>C5*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^11</f>
+        <v/>
+      </c>
+      <c r="R5">
+        <f>C5*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^12</f>
+        <v/>
+      </c>
+      <c r="S5">
+        <f>C5*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^13</f>
+        <v/>
+      </c>
+      <c r="T5">
+        <f>C5*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^14</f>
+        <v/>
+      </c>
+      <c r="U5">
+        <f>NPV(Assumptions!$B$40,F5:T5)+E5</f>
+        <v/>
+      </c>
+      <c r="V5">
         <f>IFERROR(IRR(E5:T5),"-")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>50/100</t>
         </is>
       </c>
-      <c r="B6" s="11">
+      <c r="B6">
+        <f>'Sizing Comparison'!M6</f>
+        <v/>
+      </c>
+      <c r="C6">
+        <f>'Sizing Comparison'!J6</f>
+        <v/>
+      </c>
+      <c r="D6">
         <f>'Sizing Comparison'!K6</f>
         <v/>
       </c>
-      <c r="C6" s="11">
-        <f>'Sizing Comparison'!H6</f>
-        <v/>
-      </c>
-      <c r="D6" s="11">
-        <f>'Sizing Comparison'!I6</f>
-        <v/>
-      </c>
-      <c r="E6" s="11">
+      <c r="E6">
         <f>-B6</f>
         <v/>
       </c>
-      <c r="F6" s="11">
-        <f>C6*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D6*Assumptions!$B$23*(1+Assumptions!$B$24)^0</f>
-        <v/>
-      </c>
-      <c r="G6" s="11">
-        <f>C6*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D6*Assumptions!$B$23*(1+Assumptions!$B$24)^1</f>
-        <v/>
-      </c>
-      <c r="H6" s="11">
-        <f>C6*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D6*Assumptions!$B$23*(1+Assumptions!$B$24)^2</f>
-        <v/>
-      </c>
-      <c r="I6" s="11">
-        <f>C6*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D6*Assumptions!$B$23*(1+Assumptions!$B$24)^3</f>
-        <v/>
-      </c>
-      <c r="J6" s="11">
-        <f>C6*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D6*Assumptions!$B$23*(1+Assumptions!$B$24)^4</f>
-        <v/>
-      </c>
-      <c r="K6" s="11">
-        <f>C6*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D6*Assumptions!$B$23*(1+Assumptions!$B$24)^5</f>
-        <v/>
-      </c>
-      <c r="L6" s="11">
-        <f>C6*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D6*Assumptions!$B$23*(1+Assumptions!$B$24)^6</f>
-        <v/>
-      </c>
-      <c r="M6" s="11">
-        <f>C6*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D6*Assumptions!$B$23*(1+Assumptions!$B$24)^7</f>
-        <v/>
-      </c>
-      <c r="N6" s="11">
-        <f>C6*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D6*Assumptions!$B$23*(1+Assumptions!$B$24)^8</f>
-        <v/>
-      </c>
-      <c r="O6" s="11">
-        <f>C6*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D6*Assumptions!$B$23*(1+Assumptions!$B$24)^9</f>
-        <v/>
-      </c>
-      <c r="P6" s="11">
-        <f>C6*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D6*Assumptions!$B$23*(1+Assumptions!$B$24)^10</f>
-        <v/>
-      </c>
-      <c r="Q6" s="11">
-        <f>C6*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D6*Assumptions!$B$23*(1+Assumptions!$B$24)^11</f>
-        <v/>
-      </c>
-      <c r="R6" s="11">
-        <f>C6*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D6*Assumptions!$B$23*(1+Assumptions!$B$24)^12</f>
-        <v/>
-      </c>
-      <c r="S6" s="11">
-        <f>C6*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D6*Assumptions!$B$23*(1+Assumptions!$B$24)^13</f>
-        <v/>
-      </c>
-      <c r="T6" s="11">
-        <f>C6*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D6*Assumptions!$B$23*(1+Assumptions!$B$24)^14</f>
-        <v/>
-      </c>
-      <c r="U6" s="11">
-        <f>NPV(Assumptions!$B$25,F6:T6)+E6</f>
-        <v/>
-      </c>
-      <c r="V6" s="11">
+      <c r="F6">
+        <f>C6*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^0</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>C6*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^1</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>C6*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^2</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>C6*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^3</f>
+        <v/>
+      </c>
+      <c r="J6">
+        <f>C6*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^4</f>
+        <v/>
+      </c>
+      <c r="K6">
+        <f>C6*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^5</f>
+        <v/>
+      </c>
+      <c r="L6">
+        <f>C6*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^6</f>
+        <v/>
+      </c>
+      <c r="M6">
+        <f>C6*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^7</f>
+        <v/>
+      </c>
+      <c r="N6">
+        <f>C6*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^8</f>
+        <v/>
+      </c>
+      <c r="O6">
+        <f>C6*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^9</f>
+        <v/>
+      </c>
+      <c r="P6">
+        <f>C6*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^10</f>
+        <v/>
+      </c>
+      <c r="Q6">
+        <f>C6*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^11</f>
+        <v/>
+      </c>
+      <c r="R6">
+        <f>C6*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^12</f>
+        <v/>
+      </c>
+      <c r="S6">
+        <f>C6*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^13</f>
+        <v/>
+      </c>
+      <c r="T6">
+        <f>C6*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^14</f>
+        <v/>
+      </c>
+      <c r="U6">
+        <f>NPV(Assumptions!$B$40,F6:T6)+E6</f>
+        <v/>
+      </c>
+      <c r="V6">
         <f>IFERROR(IRR(E6:T6),"-")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>50/150</t>
         </is>
       </c>
-      <c r="B7" s="11">
+      <c r="B7">
+        <f>'Sizing Comparison'!M7</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>'Sizing Comparison'!J7</f>
+        <v/>
+      </c>
+      <c r="D7">
         <f>'Sizing Comparison'!K7</f>
         <v/>
       </c>
-      <c r="C7" s="11">
-        <f>'Sizing Comparison'!H7</f>
-        <v/>
-      </c>
-      <c r="D7" s="11">
-        <f>'Sizing Comparison'!I7</f>
-        <v/>
-      </c>
-      <c r="E7" s="11">
+      <c r="E7">
         <f>-B7</f>
         <v/>
       </c>
-      <c r="F7" s="11">
-        <f>C7*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D7*Assumptions!$B$23*(1+Assumptions!$B$24)^0</f>
-        <v/>
-      </c>
-      <c r="G7" s="11">
-        <f>C7*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D7*Assumptions!$B$23*(1+Assumptions!$B$24)^1</f>
-        <v/>
-      </c>
-      <c r="H7" s="11">
-        <f>C7*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D7*Assumptions!$B$23*(1+Assumptions!$B$24)^2</f>
-        <v/>
-      </c>
-      <c r="I7" s="11">
-        <f>C7*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D7*Assumptions!$B$23*(1+Assumptions!$B$24)^3</f>
-        <v/>
-      </c>
-      <c r="J7" s="11">
-        <f>C7*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D7*Assumptions!$B$23*(1+Assumptions!$B$24)^4</f>
-        <v/>
-      </c>
-      <c r="K7" s="11">
-        <f>C7*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D7*Assumptions!$B$23*(1+Assumptions!$B$24)^5</f>
-        <v/>
-      </c>
-      <c r="L7" s="11">
-        <f>C7*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D7*Assumptions!$B$23*(1+Assumptions!$B$24)^6</f>
-        <v/>
-      </c>
-      <c r="M7" s="11">
-        <f>C7*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D7*Assumptions!$B$23*(1+Assumptions!$B$24)^7</f>
-        <v/>
-      </c>
-      <c r="N7" s="11">
-        <f>C7*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D7*Assumptions!$B$23*(1+Assumptions!$B$24)^8</f>
-        <v/>
-      </c>
-      <c r="O7" s="11">
-        <f>C7*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D7*Assumptions!$B$23*(1+Assumptions!$B$24)^9</f>
-        <v/>
-      </c>
-      <c r="P7" s="11">
-        <f>C7*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D7*Assumptions!$B$23*(1+Assumptions!$B$24)^10</f>
-        <v/>
-      </c>
-      <c r="Q7" s="11">
-        <f>C7*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D7*Assumptions!$B$23*(1+Assumptions!$B$24)^11</f>
-        <v/>
-      </c>
-      <c r="R7" s="11">
-        <f>C7*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D7*Assumptions!$B$23*(1+Assumptions!$B$24)^12</f>
-        <v/>
-      </c>
-      <c r="S7" s="11">
-        <f>C7*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D7*Assumptions!$B$23*(1+Assumptions!$B$24)^13</f>
-        <v/>
-      </c>
-      <c r="T7" s="11">
-        <f>C7*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D7*Assumptions!$B$23*(1+Assumptions!$B$24)^14</f>
-        <v/>
-      </c>
-      <c r="U7" s="11">
-        <f>NPV(Assumptions!$B$25,F7:T7)+E7</f>
-        <v/>
-      </c>
-      <c r="V7" s="11">
+      <c r="F7">
+        <f>C7*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^0</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>C7*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^1</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>C7*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^2</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>C7*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^3</f>
+        <v/>
+      </c>
+      <c r="J7">
+        <f>C7*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^4</f>
+        <v/>
+      </c>
+      <c r="K7">
+        <f>C7*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^5</f>
+        <v/>
+      </c>
+      <c r="L7">
+        <f>C7*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^6</f>
+        <v/>
+      </c>
+      <c r="M7">
+        <f>C7*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^7</f>
+        <v/>
+      </c>
+      <c r="N7">
+        <f>C7*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^8</f>
+        <v/>
+      </c>
+      <c r="O7">
+        <f>C7*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^9</f>
+        <v/>
+      </c>
+      <c r="P7">
+        <f>C7*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^10</f>
+        <v/>
+      </c>
+      <c r="Q7">
+        <f>C7*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^11</f>
+        <v/>
+      </c>
+      <c r="R7">
+        <f>C7*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^12</f>
+        <v/>
+      </c>
+      <c r="S7">
+        <f>C7*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^13</f>
+        <v/>
+      </c>
+      <c r="T7">
+        <f>C7*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^14</f>
+        <v/>
+      </c>
+      <c r="U7">
+        <f>NPV(Assumptions!$B$40,F7:T7)+E7</f>
+        <v/>
+      </c>
+      <c r="V7">
         <f>IFERROR(IRR(E7:T7),"-")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>75/150</t>
         </is>
       </c>
-      <c r="B8" s="11">
+      <c r="B8">
+        <f>'Sizing Comparison'!M8</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>'Sizing Comparison'!J8</f>
+        <v/>
+      </c>
+      <c r="D8">
         <f>'Sizing Comparison'!K8</f>
         <v/>
       </c>
-      <c r="C8" s="11">
-        <f>'Sizing Comparison'!H8</f>
-        <v/>
-      </c>
-      <c r="D8" s="11">
-        <f>'Sizing Comparison'!I8</f>
-        <v/>
-      </c>
-      <c r="E8" s="11">
+      <c r="E8">
         <f>-B8</f>
         <v/>
       </c>
-      <c r="F8" s="11">
-        <f>C8*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D8*Assumptions!$B$23*(1+Assumptions!$B$24)^0</f>
-        <v/>
-      </c>
-      <c r="G8" s="11">
-        <f>C8*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D8*Assumptions!$B$23*(1+Assumptions!$B$24)^1</f>
-        <v/>
-      </c>
-      <c r="H8" s="11">
-        <f>C8*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D8*Assumptions!$B$23*(1+Assumptions!$B$24)^2</f>
-        <v/>
-      </c>
-      <c r="I8" s="11">
-        <f>C8*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D8*Assumptions!$B$23*(1+Assumptions!$B$24)^3</f>
-        <v/>
-      </c>
-      <c r="J8" s="11">
-        <f>C8*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D8*Assumptions!$B$23*(1+Assumptions!$B$24)^4</f>
-        <v/>
-      </c>
-      <c r="K8" s="11">
-        <f>C8*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D8*Assumptions!$B$23*(1+Assumptions!$B$24)^5</f>
-        <v/>
-      </c>
-      <c r="L8" s="11">
-        <f>C8*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D8*Assumptions!$B$23*(1+Assumptions!$B$24)^6</f>
-        <v/>
-      </c>
-      <c r="M8" s="11">
-        <f>C8*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D8*Assumptions!$B$23*(1+Assumptions!$B$24)^7</f>
-        <v/>
-      </c>
-      <c r="N8" s="11">
-        <f>C8*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D8*Assumptions!$B$23*(1+Assumptions!$B$24)^8</f>
-        <v/>
-      </c>
-      <c r="O8" s="11">
-        <f>C8*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D8*Assumptions!$B$23*(1+Assumptions!$B$24)^9</f>
-        <v/>
-      </c>
-      <c r="P8" s="11">
-        <f>C8*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D8*Assumptions!$B$23*(1+Assumptions!$B$24)^10</f>
-        <v/>
-      </c>
-      <c r="Q8" s="11">
-        <f>C8*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D8*Assumptions!$B$23*(1+Assumptions!$B$24)^11</f>
-        <v/>
-      </c>
-      <c r="R8" s="11">
-        <f>C8*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D8*Assumptions!$B$23*(1+Assumptions!$B$24)^12</f>
-        <v/>
-      </c>
-      <c r="S8" s="11">
-        <f>C8*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D8*Assumptions!$B$23*(1+Assumptions!$B$24)^13</f>
-        <v/>
-      </c>
-      <c r="T8" s="11">
-        <f>C8*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D8*Assumptions!$B$23*(1+Assumptions!$B$24)^14</f>
-        <v/>
-      </c>
-      <c r="U8" s="11">
-        <f>NPV(Assumptions!$B$25,F8:T8)+E8</f>
-        <v/>
-      </c>
-      <c r="V8" s="11">
+      <c r="F8">
+        <f>C8*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^0</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>C8*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^1</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>C8*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^2</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>C8*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^3</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>C8*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^4</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>C8*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^5</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>C8*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^6</f>
+        <v/>
+      </c>
+      <c r="M8">
+        <f>C8*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^7</f>
+        <v/>
+      </c>
+      <c r="N8">
+        <f>C8*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^8</f>
+        <v/>
+      </c>
+      <c r="O8">
+        <f>C8*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^9</f>
+        <v/>
+      </c>
+      <c r="P8">
+        <f>C8*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^10</f>
+        <v/>
+      </c>
+      <c r="Q8">
+        <f>C8*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^11</f>
+        <v/>
+      </c>
+      <c r="R8">
+        <f>C8*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^12</f>
+        <v/>
+      </c>
+      <c r="S8">
+        <f>C8*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^13</f>
+        <v/>
+      </c>
+      <c r="T8">
+        <f>C8*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^14</f>
+        <v/>
+      </c>
+      <c r="U8">
+        <f>NPV(Assumptions!$B$40,F8:T8)+E8</f>
+        <v/>
+      </c>
+      <c r="V8">
         <f>IFERROR(IRR(E8:T8),"-")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>100/200</t>
         </is>
       </c>
-      <c r="B9" s="11">
+      <c r="B9">
+        <f>'Sizing Comparison'!M9</f>
+        <v/>
+      </c>
+      <c r="C9">
+        <f>'Sizing Comparison'!J9</f>
+        <v/>
+      </c>
+      <c r="D9">
         <f>'Sizing Comparison'!K9</f>
         <v/>
       </c>
-      <c r="C9" s="11">
-        <f>'Sizing Comparison'!H9</f>
-        <v/>
-      </c>
-      <c r="D9" s="11">
-        <f>'Sizing Comparison'!I9</f>
-        <v/>
-      </c>
-      <c r="E9" s="11">
+      <c r="E9">
         <f>-B9</f>
         <v/>
       </c>
-      <c r="F9" s="11">
-        <f>C9*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D9*Assumptions!$B$23*(1+Assumptions!$B$24)^0</f>
-        <v/>
-      </c>
-      <c r="G9" s="11">
-        <f>C9*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D9*Assumptions!$B$23*(1+Assumptions!$B$24)^1</f>
-        <v/>
-      </c>
-      <c r="H9" s="11">
-        <f>C9*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D9*Assumptions!$B$23*(1+Assumptions!$B$24)^2</f>
-        <v/>
-      </c>
-      <c r="I9" s="11">
-        <f>C9*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D9*Assumptions!$B$23*(1+Assumptions!$B$24)^3</f>
-        <v/>
-      </c>
-      <c r="J9" s="11">
-        <f>C9*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D9*Assumptions!$B$23*(1+Assumptions!$B$24)^4</f>
-        <v/>
-      </c>
-      <c r="K9" s="11">
-        <f>C9*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D9*Assumptions!$B$23*(1+Assumptions!$B$24)^5</f>
-        <v/>
-      </c>
-      <c r="L9" s="11">
-        <f>C9*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D9*Assumptions!$B$23*(1+Assumptions!$B$24)^6</f>
-        <v/>
-      </c>
-      <c r="M9" s="11">
-        <f>C9*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D9*Assumptions!$B$23*(1+Assumptions!$B$24)^7</f>
-        <v/>
-      </c>
-      <c r="N9" s="11">
-        <f>C9*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D9*Assumptions!$B$23*(1+Assumptions!$B$24)^8</f>
-        <v/>
-      </c>
-      <c r="O9" s="11">
-        <f>C9*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D9*Assumptions!$B$23*(1+Assumptions!$B$24)^9</f>
-        <v/>
-      </c>
-      <c r="P9" s="11">
-        <f>C9*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D9*Assumptions!$B$23*(1+Assumptions!$B$24)^10</f>
-        <v/>
-      </c>
-      <c r="Q9" s="11">
-        <f>C9*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D9*Assumptions!$B$23*(1+Assumptions!$B$24)^11</f>
-        <v/>
-      </c>
-      <c r="R9" s="11">
-        <f>C9*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D9*Assumptions!$B$23*(1+Assumptions!$B$24)^12</f>
-        <v/>
-      </c>
-      <c r="S9" s="11">
-        <f>C9*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D9*Assumptions!$B$23*(1+Assumptions!$B$24)^13</f>
-        <v/>
-      </c>
-      <c r="T9" s="11">
-        <f>C9*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D9*Assumptions!$B$23*(1+Assumptions!$B$24)^14</f>
-        <v/>
-      </c>
-      <c r="U9" s="11">
-        <f>NPV(Assumptions!$B$25,F9:T9)+E9</f>
-        <v/>
-      </c>
-      <c r="V9" s="11">
+      <c r="F9">
+        <f>C9*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^0</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>C9*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^1</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>C9*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^2</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>C9*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^3</f>
+        <v/>
+      </c>
+      <c r="J9">
+        <f>C9*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^4</f>
+        <v/>
+      </c>
+      <c r="K9">
+        <f>C9*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^5</f>
+        <v/>
+      </c>
+      <c r="L9">
+        <f>C9*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^6</f>
+        <v/>
+      </c>
+      <c r="M9">
+        <f>C9*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^7</f>
+        <v/>
+      </c>
+      <c r="N9">
+        <f>C9*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^8</f>
+        <v/>
+      </c>
+      <c r="O9">
+        <f>C9*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^9</f>
+        <v/>
+      </c>
+      <c r="P9">
+        <f>C9*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^10</f>
+        <v/>
+      </c>
+      <c r="Q9">
+        <f>C9*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^11</f>
+        <v/>
+      </c>
+      <c r="R9">
+        <f>C9*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^12</f>
+        <v/>
+      </c>
+      <c r="S9">
+        <f>C9*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^13</f>
+        <v/>
+      </c>
+      <c r="T9">
+        <f>C9*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^14</f>
+        <v/>
+      </c>
+      <c r="U9">
+        <f>NPV(Assumptions!$B$40,F9:T9)+E9</f>
+        <v/>
+      </c>
+      <c r="V9">
         <f>IFERROR(IRR(E9:T9),"-")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>100/300</t>
         </is>
       </c>
-      <c r="B10" s="11">
+      <c r="B10">
+        <f>'Sizing Comparison'!M10</f>
+        <v/>
+      </c>
+      <c r="C10">
+        <f>'Sizing Comparison'!J10</f>
+        <v/>
+      </c>
+      <c r="D10">
         <f>'Sizing Comparison'!K10</f>
         <v/>
       </c>
-      <c r="C10" s="11">
-        <f>'Sizing Comparison'!H10</f>
-        <v/>
-      </c>
-      <c r="D10" s="11">
-        <f>'Sizing Comparison'!I10</f>
-        <v/>
-      </c>
-      <c r="E10" s="11">
+      <c r="E10">
         <f>-B10</f>
         <v/>
       </c>
-      <c r="F10" s="11">
-        <f>C10*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D10*Assumptions!$B$23*(1+Assumptions!$B$24)^0</f>
-        <v/>
-      </c>
-      <c r="G10" s="11">
-        <f>C10*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D10*Assumptions!$B$23*(1+Assumptions!$B$24)^1</f>
-        <v/>
-      </c>
-      <c r="H10" s="11">
-        <f>C10*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D10*Assumptions!$B$23*(1+Assumptions!$B$24)^2</f>
-        <v/>
-      </c>
-      <c r="I10" s="11">
-        <f>C10*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D10*Assumptions!$B$23*(1+Assumptions!$B$24)^3</f>
-        <v/>
-      </c>
-      <c r="J10" s="11">
-        <f>C10*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D10*Assumptions!$B$23*(1+Assumptions!$B$24)^4</f>
-        <v/>
-      </c>
-      <c r="K10" s="11">
-        <f>C10*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D10*Assumptions!$B$23*(1+Assumptions!$B$24)^5</f>
-        <v/>
-      </c>
-      <c r="L10" s="11">
-        <f>C10*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D10*Assumptions!$B$23*(1+Assumptions!$B$24)^6</f>
-        <v/>
-      </c>
-      <c r="M10" s="11">
-        <f>C10*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D10*Assumptions!$B$23*(1+Assumptions!$B$24)^7</f>
-        <v/>
-      </c>
-      <c r="N10" s="11">
-        <f>C10*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D10*Assumptions!$B$23*(1+Assumptions!$B$24)^8</f>
-        <v/>
-      </c>
-      <c r="O10" s="11">
-        <f>C10*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D10*Assumptions!$B$23*(1+Assumptions!$B$24)^9</f>
-        <v/>
-      </c>
-      <c r="P10" s="11">
-        <f>C10*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D10*Assumptions!$B$23*(1+Assumptions!$B$24)^10</f>
-        <v/>
-      </c>
-      <c r="Q10" s="11">
-        <f>C10*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D10*Assumptions!$B$23*(1+Assumptions!$B$24)^11</f>
-        <v/>
-      </c>
-      <c r="R10" s="11">
-        <f>C10*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D10*Assumptions!$B$23*(1+Assumptions!$B$24)^12</f>
-        <v/>
-      </c>
-      <c r="S10" s="11">
-        <f>C10*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D10*Assumptions!$B$23*(1+Assumptions!$B$24)^13</f>
-        <v/>
-      </c>
-      <c r="T10" s="11">
-        <f>C10*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D10*Assumptions!$B$23*(1+Assumptions!$B$24)^14</f>
-        <v/>
-      </c>
-      <c r="U10" s="11">
-        <f>NPV(Assumptions!$B$25,F10:T10)+E10</f>
-        <v/>
-      </c>
-      <c r="V10" s="11">
+      <c r="F10">
+        <f>C10*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^0</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>C10*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^1</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>C10*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^2</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>C10*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^3</f>
+        <v/>
+      </c>
+      <c r="J10">
+        <f>C10*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^4</f>
+        <v/>
+      </c>
+      <c r="K10">
+        <f>C10*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^5</f>
+        <v/>
+      </c>
+      <c r="L10">
+        <f>C10*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^6</f>
+        <v/>
+      </c>
+      <c r="M10">
+        <f>C10*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^7</f>
+        <v/>
+      </c>
+      <c r="N10">
+        <f>C10*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^8</f>
+        <v/>
+      </c>
+      <c r="O10">
+        <f>C10*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^9</f>
+        <v/>
+      </c>
+      <c r="P10">
+        <f>C10*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^10</f>
+        <v/>
+      </c>
+      <c r="Q10">
+        <f>C10*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^11</f>
+        <v/>
+      </c>
+      <c r="R10">
+        <f>C10*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^12</f>
+        <v/>
+      </c>
+      <c r="S10">
+        <f>C10*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^13</f>
+        <v/>
+      </c>
+      <c r="T10">
+        <f>C10*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^14</f>
+        <v/>
+      </c>
+      <c r="U10">
+        <f>NPV(Assumptions!$B$40,F10:T10)+E10</f>
+        <v/>
+      </c>
+      <c r="V10">
         <f>IFERROR(IRR(E10:T10),"-")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>100/400</t>
         </is>
       </c>
-      <c r="B11" s="11">
+      <c r="B11">
+        <f>'Sizing Comparison'!M11</f>
+        <v/>
+      </c>
+      <c r="C11">
+        <f>'Sizing Comparison'!J11</f>
+        <v/>
+      </c>
+      <c r="D11">
         <f>'Sizing Comparison'!K11</f>
         <v/>
       </c>
-      <c r="C11" s="11">
-        <f>'Sizing Comparison'!H11</f>
-        <v/>
-      </c>
-      <c r="D11" s="11">
-        <f>'Sizing Comparison'!I11</f>
-        <v/>
-      </c>
-      <c r="E11" s="11">
+      <c r="E11">
         <f>-B11</f>
         <v/>
       </c>
-      <c r="F11" s="11">
-        <f>C11*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D11*Assumptions!$B$23*(1+Assumptions!$B$24)^0</f>
-        <v/>
-      </c>
-      <c r="G11" s="11">
-        <f>C11*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D11*Assumptions!$B$23*(1+Assumptions!$B$24)^1</f>
-        <v/>
-      </c>
-      <c r="H11" s="11">
-        <f>C11*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D11*Assumptions!$B$23*(1+Assumptions!$B$24)^2</f>
-        <v/>
-      </c>
-      <c r="I11" s="11">
-        <f>C11*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D11*Assumptions!$B$23*(1+Assumptions!$B$24)^3</f>
-        <v/>
-      </c>
-      <c r="J11" s="11">
-        <f>C11*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D11*Assumptions!$B$23*(1+Assumptions!$B$24)^4</f>
-        <v/>
-      </c>
-      <c r="K11" s="11">
-        <f>C11*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D11*Assumptions!$B$23*(1+Assumptions!$B$24)^5</f>
-        <v/>
-      </c>
-      <c r="L11" s="11">
-        <f>C11*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D11*Assumptions!$B$23*(1+Assumptions!$B$24)^6</f>
-        <v/>
-      </c>
-      <c r="M11" s="11">
-        <f>C11*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D11*Assumptions!$B$23*(1+Assumptions!$B$24)^7</f>
-        <v/>
-      </c>
-      <c r="N11" s="11">
-        <f>C11*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D11*Assumptions!$B$23*(1+Assumptions!$B$24)^8</f>
-        <v/>
-      </c>
-      <c r="O11" s="11">
-        <f>C11*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D11*Assumptions!$B$23*(1+Assumptions!$B$24)^9</f>
-        <v/>
-      </c>
-      <c r="P11" s="11">
-        <f>C11*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D11*Assumptions!$B$23*(1+Assumptions!$B$24)^10</f>
-        <v/>
-      </c>
-      <c r="Q11" s="11">
-        <f>C11*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D11*Assumptions!$B$23*(1+Assumptions!$B$24)^11</f>
-        <v/>
-      </c>
-      <c r="R11" s="11">
-        <f>C11*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D11*Assumptions!$B$23*(1+Assumptions!$B$24)^12</f>
-        <v/>
-      </c>
-      <c r="S11" s="11">
-        <f>C11*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D11*Assumptions!$B$23*(1+Assumptions!$B$24)^13</f>
-        <v/>
-      </c>
-      <c r="T11" s="11">
-        <f>C11*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D11*Assumptions!$B$23*(1+Assumptions!$B$24)^14</f>
-        <v/>
-      </c>
-      <c r="U11" s="11">
-        <f>NPV(Assumptions!$B$25,F11:T11)+E11</f>
-        <v/>
-      </c>
-      <c r="V11" s="11">
+      <c r="F11">
+        <f>C11*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^0</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>C11*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^1</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>C11*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^2</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>C11*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^3</f>
+        <v/>
+      </c>
+      <c r="J11">
+        <f>C11*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^4</f>
+        <v/>
+      </c>
+      <c r="K11">
+        <f>C11*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^5</f>
+        <v/>
+      </c>
+      <c r="L11">
+        <f>C11*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^6</f>
+        <v/>
+      </c>
+      <c r="M11">
+        <f>C11*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^7</f>
+        <v/>
+      </c>
+      <c r="N11">
+        <f>C11*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^8</f>
+        <v/>
+      </c>
+      <c r="O11">
+        <f>C11*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^9</f>
+        <v/>
+      </c>
+      <c r="P11">
+        <f>C11*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^10</f>
+        <v/>
+      </c>
+      <c r="Q11">
+        <f>C11*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^11</f>
+        <v/>
+      </c>
+      <c r="R11">
+        <f>C11*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^12</f>
+        <v/>
+      </c>
+      <c r="S11">
+        <f>C11*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^13</f>
+        <v/>
+      </c>
+      <c r="T11">
+        <f>C11*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^14</f>
+        <v/>
+      </c>
+      <c r="U11">
+        <f>NPV(Assumptions!$B$40,F11:T11)+E11</f>
+        <v/>
+      </c>
+      <c r="V11">
         <f>IFERROR(IRR(E11:T11),"-")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>150/300</t>
         </is>
       </c>
-      <c r="B12" s="11">
+      <c r="B12">
+        <f>'Sizing Comparison'!M12</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>'Sizing Comparison'!J12</f>
+        <v/>
+      </c>
+      <c r="D12">
         <f>'Sizing Comparison'!K12</f>
         <v/>
       </c>
-      <c r="C12" s="11">
-        <f>'Sizing Comparison'!H12</f>
-        <v/>
-      </c>
-      <c r="D12" s="11">
-        <f>'Sizing Comparison'!I12</f>
-        <v/>
-      </c>
-      <c r="E12" s="11">
+      <c r="E12">
         <f>-B12</f>
         <v/>
       </c>
-      <c r="F12" s="11">
-        <f>C12*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D12*Assumptions!$B$23*(1+Assumptions!$B$24)^0</f>
-        <v/>
-      </c>
-      <c r="G12" s="11">
-        <f>C12*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D12*Assumptions!$B$23*(1+Assumptions!$B$24)^1</f>
-        <v/>
-      </c>
-      <c r="H12" s="11">
-        <f>C12*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D12*Assumptions!$B$23*(1+Assumptions!$B$24)^2</f>
-        <v/>
-      </c>
-      <c r="I12" s="11">
-        <f>C12*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D12*Assumptions!$B$23*(1+Assumptions!$B$24)^3</f>
-        <v/>
-      </c>
-      <c r="J12" s="11">
-        <f>C12*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D12*Assumptions!$B$23*(1+Assumptions!$B$24)^4</f>
-        <v/>
-      </c>
-      <c r="K12" s="11">
-        <f>C12*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D12*Assumptions!$B$23*(1+Assumptions!$B$24)^5</f>
-        <v/>
-      </c>
-      <c r="L12" s="11">
-        <f>C12*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D12*Assumptions!$B$23*(1+Assumptions!$B$24)^6</f>
-        <v/>
-      </c>
-      <c r="M12" s="11">
-        <f>C12*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D12*Assumptions!$B$23*(1+Assumptions!$B$24)^7</f>
-        <v/>
-      </c>
-      <c r="N12" s="11">
-        <f>C12*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D12*Assumptions!$B$23*(1+Assumptions!$B$24)^8</f>
-        <v/>
-      </c>
-      <c r="O12" s="11">
-        <f>C12*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D12*Assumptions!$B$23*(1+Assumptions!$B$24)^9</f>
-        <v/>
-      </c>
-      <c r="P12" s="11">
-        <f>C12*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D12*Assumptions!$B$23*(1+Assumptions!$B$24)^10</f>
-        <v/>
-      </c>
-      <c r="Q12" s="11">
-        <f>C12*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D12*Assumptions!$B$23*(1+Assumptions!$B$24)^11</f>
-        <v/>
-      </c>
-      <c r="R12" s="11">
-        <f>C12*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D12*Assumptions!$B$23*(1+Assumptions!$B$24)^12</f>
-        <v/>
-      </c>
-      <c r="S12" s="11">
-        <f>C12*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D12*Assumptions!$B$23*(1+Assumptions!$B$24)^13</f>
-        <v/>
-      </c>
-      <c r="T12" s="11">
-        <f>C12*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D12*Assumptions!$B$23*(1+Assumptions!$B$24)^14</f>
-        <v/>
-      </c>
-      <c r="U12" s="11">
-        <f>NPV(Assumptions!$B$25,F12:T12)+E12</f>
-        <v/>
-      </c>
-      <c r="V12" s="11">
+      <c r="F12">
+        <f>C12*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^0</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>C12*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^1</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>C12*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^2</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>C12*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^3</f>
+        <v/>
+      </c>
+      <c r="J12">
+        <f>C12*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^4</f>
+        <v/>
+      </c>
+      <c r="K12">
+        <f>C12*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^5</f>
+        <v/>
+      </c>
+      <c r="L12">
+        <f>C12*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^6</f>
+        <v/>
+      </c>
+      <c r="M12">
+        <f>C12*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^7</f>
+        <v/>
+      </c>
+      <c r="N12">
+        <f>C12*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^8</f>
+        <v/>
+      </c>
+      <c r="O12">
+        <f>C12*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^9</f>
+        <v/>
+      </c>
+      <c r="P12">
+        <f>C12*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^10</f>
+        <v/>
+      </c>
+      <c r="Q12">
+        <f>C12*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^11</f>
+        <v/>
+      </c>
+      <c r="R12">
+        <f>C12*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^12</f>
+        <v/>
+      </c>
+      <c r="S12">
+        <f>C12*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^13</f>
+        <v/>
+      </c>
+      <c r="T12">
+        <f>C12*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^14</f>
+        <v/>
+      </c>
+      <c r="U12">
+        <f>NPV(Assumptions!$B$40,F12:T12)+E12</f>
+        <v/>
+      </c>
+      <c r="V12">
         <f>IFERROR(IRR(E12:T12),"-")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>200/400</t>
         </is>
       </c>
-      <c r="B13" s="11">
+      <c r="B13">
+        <f>'Sizing Comparison'!M13</f>
+        <v/>
+      </c>
+      <c r="C13">
+        <f>'Sizing Comparison'!J13</f>
+        <v/>
+      </c>
+      <c r="D13">
         <f>'Sizing Comparison'!K13</f>
         <v/>
       </c>
-      <c r="C13" s="11">
-        <f>'Sizing Comparison'!H13</f>
-        <v/>
-      </c>
-      <c r="D13" s="11">
-        <f>'Sizing Comparison'!I13</f>
-        <v/>
-      </c>
-      <c r="E13" s="11">
+      <c r="E13">
         <f>-B13</f>
         <v/>
       </c>
-      <c r="F13" s="11">
-        <f>C13*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D13*Assumptions!$B$23*(1+Assumptions!$B$24)^0</f>
-        <v/>
-      </c>
-      <c r="G13" s="11">
-        <f>C13*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D13*Assumptions!$B$23*(1+Assumptions!$B$24)^1</f>
-        <v/>
-      </c>
-      <c r="H13" s="11">
-        <f>C13*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D13*Assumptions!$B$23*(1+Assumptions!$B$24)^2</f>
-        <v/>
-      </c>
-      <c r="I13" s="11">
-        <f>C13*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D13*Assumptions!$B$23*(1+Assumptions!$B$24)^3</f>
-        <v/>
-      </c>
-      <c r="J13" s="11">
-        <f>C13*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D13*Assumptions!$B$23*(1+Assumptions!$B$24)^4</f>
-        <v/>
-      </c>
-      <c r="K13" s="11">
-        <f>C13*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D13*Assumptions!$B$23*(1+Assumptions!$B$24)^5</f>
-        <v/>
-      </c>
-      <c r="L13" s="11">
-        <f>C13*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D13*Assumptions!$B$23*(1+Assumptions!$B$24)^6</f>
-        <v/>
-      </c>
-      <c r="M13" s="11">
-        <f>C13*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D13*Assumptions!$B$23*(1+Assumptions!$B$24)^7</f>
-        <v/>
-      </c>
-      <c r="N13" s="11">
-        <f>C13*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D13*Assumptions!$B$23*(1+Assumptions!$B$24)^8</f>
-        <v/>
-      </c>
-      <c r="O13" s="11">
-        <f>C13*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D13*Assumptions!$B$23*(1+Assumptions!$B$24)^9</f>
-        <v/>
-      </c>
-      <c r="P13" s="11">
-        <f>C13*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D13*Assumptions!$B$23*(1+Assumptions!$B$24)^10</f>
-        <v/>
-      </c>
-      <c r="Q13" s="11">
-        <f>C13*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D13*Assumptions!$B$23*(1+Assumptions!$B$24)^11</f>
-        <v/>
-      </c>
-      <c r="R13" s="11">
-        <f>C13*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D13*Assumptions!$B$23*(1+Assumptions!$B$24)^12</f>
-        <v/>
-      </c>
-      <c r="S13" s="11">
-        <f>C13*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D13*Assumptions!$B$23*(1+Assumptions!$B$24)^13</f>
-        <v/>
-      </c>
-      <c r="T13" s="11">
-        <f>C13*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D13*Assumptions!$B$23*(1+Assumptions!$B$24)^14</f>
-        <v/>
-      </c>
-      <c r="U13" s="11">
-        <f>NPV(Assumptions!$B$25,F13:T13)+E13</f>
-        <v/>
-      </c>
-      <c r="V13" s="11">
+      <c r="F13">
+        <f>C13*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^0</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>C13*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^1</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>C13*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^2</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>C13*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^3</f>
+        <v/>
+      </c>
+      <c r="J13">
+        <f>C13*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^4</f>
+        <v/>
+      </c>
+      <c r="K13">
+        <f>C13*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^5</f>
+        <v/>
+      </c>
+      <c r="L13">
+        <f>C13*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^6</f>
+        <v/>
+      </c>
+      <c r="M13">
+        <f>C13*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^7</f>
+        <v/>
+      </c>
+      <c r="N13">
+        <f>C13*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^8</f>
+        <v/>
+      </c>
+      <c r="O13">
+        <f>C13*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^9</f>
+        <v/>
+      </c>
+      <c r="P13">
+        <f>C13*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^10</f>
+        <v/>
+      </c>
+      <c r="Q13">
+        <f>C13*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^11</f>
+        <v/>
+      </c>
+      <c r="R13">
+        <f>C13*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^12</f>
+        <v/>
+      </c>
+      <c r="S13">
+        <f>C13*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^13</f>
+        <v/>
+      </c>
+      <c r="T13">
+        <f>C13*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^14</f>
+        <v/>
+      </c>
+      <c r="U13">
+        <f>NPV(Assumptions!$B$40,F13:T13)+E13</f>
+        <v/>
+      </c>
+      <c r="V13">
         <f>IFERROR(IRR(E13:T13),"-")</f>
         <v/>
       </c>
@@ -3845,419 +4716,509 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Load Analysis — Calendar 2025 (representative year)</t>
+          <t>Solar PV add-on</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Set PV size on Assumptions (B32). Self-consumed PV saves the energy rate; exports earn the credit rate.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="inlineStr">
-        <is>
-          <t>Annual energy</t>
-        </is>
-      </c>
-      <c r="B3" s="29" t="n">
-        <v>224726</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="23" t="inlineStr">
-        <is>
-          <t>Peak demand</t>
-        </is>
-      </c>
-      <c r="B4" s="30" t="n">
-        <v>114.9</v>
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>⚠ This is a winter-heating load: PV peaks May–Aug when usage is tiny, near-zero Nov–Feb when usage is high. Expect heavy exports / low self-consumption.</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>Average load</t>
-        </is>
-      </c>
-      <c r="B5" s="30" t="n">
-        <v>25.7</v>
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Load (kWh)</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>PV share</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>PV gen (kWh)</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Self-consumed</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>Exported</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>$ saved</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
-        <is>
-          <t>Load factor</t>
-        </is>
-      </c>
-      <c r="B6" s="31">
-        <f>B5/B4</f>
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="n">
+        <v>35978</v>
+      </c>
+      <c r="C6" s="26" t="n">
+        <v>0.0292</v>
+      </c>
+      <c r="D6" s="26">
+        <f>Assumptions!$B$32*Assumptions!$B$33*C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="26">
+        <f>MIN(D6,B6)</f>
+        <v/>
+      </c>
+      <c r="F6" s="26">
+        <f>D6-E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="14">
+        <f>E6*Assumptions!$B$4+F6*Assumptions!$B$35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="n">
+        <v>34421</v>
+      </c>
+      <c r="C7" s="26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D7" s="26">
+        <f>Assumptions!$B$32*Assumptions!$B$33*C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="26">
+        <f>MIN(D7,B7)</f>
+        <v/>
+      </c>
+      <c r="F7" s="26">
+        <f>D7-E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="14">
+        <f>E7*Assumptions!$B$4+F7*Assumptions!$B$35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="n">
+        <v>43051</v>
+      </c>
+      <c r="C8" s="26" t="n">
+        <v>0.0885</v>
+      </c>
+      <c r="D8" s="26">
+        <f>Assumptions!$B$32*Assumptions!$B$33*C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="26">
+        <f>MIN(D8,B8)</f>
+        <v/>
+      </c>
+      <c r="F8" s="26">
+        <f>D8-E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="14">
+        <f>E8*Assumptions!$B$4+F8*Assumptions!$B$35</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Energy (kWh)</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Peak (kW)</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>Demand chg $</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>Energy chg $</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>Total $</t>
-        </is>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="n">
+        <v>28133</v>
+      </c>
+      <c r="C9" s="26" t="n">
+        <v>0.1125</v>
+      </c>
+      <c r="D9" s="26">
+        <f>Assumptions!$B$32*Assumptions!$B$33*C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="26">
+        <f>MIN(D9,B9)</f>
+        <v/>
+      </c>
+      <c r="F9" s="26">
+        <f>D9-E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="14">
+        <f>E9*Assumptions!$B$4+F9*Assumptions!$B$35</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="n">
-        <v>35978</v>
-      </c>
-      <c r="C10" s="11" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="D10" s="13">
-        <f>C10*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="E10" s="13">
-        <f>B10*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F10" s="13">
-        <f>D10+E10</f>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="n">
+        <v>6245</v>
+      </c>
+      <c r="C10" s="26" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="D10" s="26">
+        <f>Assumptions!$B$32*Assumptions!$B$33*C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="26">
+        <f>MIN(D10,B10)</f>
+        <v/>
+      </c>
+      <c r="F10" s="26">
+        <f>D10-E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="14">
+        <f>E10*Assumptions!$B$4+F10*Assumptions!$B$35</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="n">
-        <v>34421</v>
-      </c>
-      <c r="C11" s="11" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="D11" s="13">
-        <f>C11*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="E11" s="13">
-        <f>B11*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F11" s="13">
-        <f>D11+E11</f>
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="n">
+        <v>4765</v>
+      </c>
+      <c r="C11" s="26" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="D11" s="26">
+        <f>Assumptions!$B$32*Assumptions!$B$33*C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="26">
+        <f>MIN(D11,B11)</f>
+        <v/>
+      </c>
+      <c r="F11" s="26">
+        <f>D11-E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="14">
+        <f>E11*Assumptions!$B$4+F11*Assumptions!$B$35</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="n">
-        <v>43051</v>
-      </c>
-      <c r="C12" s="11" t="n">
-        <v>112.4</v>
-      </c>
-      <c r="D12" s="13">
-        <f>C12*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="E12" s="13">
-        <f>B12*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F12" s="13">
-        <f>D12+E12</f>
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="n">
+        <v>4316</v>
+      </c>
+      <c r="C12" s="26" t="n">
+        <v>0.1354</v>
+      </c>
+      <c r="D12" s="26">
+        <f>Assumptions!$B$32*Assumptions!$B$33*C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="26">
+        <f>MIN(D12,B12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="26">
+        <f>D12-E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="14">
+        <f>E12*Assumptions!$B$4+F12*Assumptions!$B$35</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="n">
-        <v>28133</v>
-      </c>
-      <c r="C13" s="11" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="D13" s="13">
-        <f>C13*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="E13" s="13">
-        <f>B13*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F13" s="13">
-        <f>D13+E13</f>
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="n">
+        <v>3468</v>
+      </c>
+      <c r="C13" s="26" t="n">
+        <v>0.1167</v>
+      </c>
+      <c r="D13" s="26">
+        <f>Assumptions!$B$32*Assumptions!$B$33*C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="26">
+        <f>MIN(D13,B13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="26">
+        <f>D13-E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="14">
+        <f>E13*Assumptions!$B$4+F13*Assumptions!$B$35</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="n">
-        <v>6245</v>
-      </c>
-      <c r="C14" s="11" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="D14" s="13">
-        <f>C14*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="E14" s="13">
-        <f>B14*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F14" s="13">
-        <f>D14+E14</f>
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="n">
+        <v>2927</v>
+      </c>
+      <c r="C14" s="26" t="n">
+        <v>0.0885</v>
+      </c>
+      <c r="D14" s="26">
+        <f>Assumptions!$B$32*Assumptions!$B$33*C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="26">
+        <f>MIN(D14,B14)</f>
+        <v/>
+      </c>
+      <c r="F14" s="26">
+        <f>D14-E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="14">
+        <f>E14*Assumptions!$B$4+F14*Assumptions!$B$35</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="n">
-        <v>4765</v>
-      </c>
-      <c r="C15" s="11" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="D15" s="13">
-        <f>C15*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="E15" s="13">
-        <f>B15*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F15" s="13">
-        <f>D15+E15</f>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="n">
+        <v>2606</v>
+      </c>
+      <c r="C15" s="26" t="n">
+        <v>0.0604</v>
+      </c>
+      <c r="D15" s="26">
+        <f>Assumptions!$B$32*Assumptions!$B$33*C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="26">
+        <f>MIN(D15,B15)</f>
+        <v/>
+      </c>
+      <c r="F15" s="26">
+        <f>D15-E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="14">
+        <f>E15*Assumptions!$B$4+F15*Assumptions!$B$35</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="n">
-        <v>4316</v>
-      </c>
-      <c r="C16" s="11" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="D16" s="13">
-        <f>C16*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="E16" s="13">
-        <f>B16*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F16" s="13">
-        <f>D16+E16</f>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="n">
+        <v>34658</v>
+      </c>
+      <c r="C16" s="26" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="D16" s="26">
+        <f>Assumptions!$B$32*Assumptions!$B$33*C16</f>
+        <v/>
+      </c>
+      <c r="E16" s="26">
+        <f>MIN(D16,B16)</f>
+        <v/>
+      </c>
+      <c r="F16" s="26">
+        <f>D16-E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="14">
+        <f>E16*Assumptions!$B$4+F16*Assumptions!$B$35</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="n">
-        <v>3468</v>
-      </c>
-      <c r="C17" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="D17" s="13">
-        <f>C17*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="E17" s="13">
-        <f>B17*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F17" s="13">
-        <f>D17+E17</f>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="n">
+        <v>24158</v>
+      </c>
+      <c r="C17" s="26" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="D17" s="26">
+        <f>Assumptions!$B$32*Assumptions!$B$33*C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="26">
+        <f>MIN(D17,B17)</f>
+        <v/>
+      </c>
+      <c r="F17" s="26">
+        <f>D17-E17</f>
+        <v/>
+      </c>
+      <c r="G17" s="14">
+        <f>E17*Assumptions!$B$4+F17*Assumptions!$B$35</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="n">
-        <v>2927</v>
-      </c>
-      <c r="C18" s="11" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="D18" s="13">
-        <f>C18*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="E18" s="13">
-        <f>B18*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F18" s="13">
-        <f>D18+E18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="n">
-        <v>2606</v>
-      </c>
-      <c r="C19" s="11" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="D19" s="13">
-        <f>C19*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="E19" s="13">
-        <f>B19*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F19" s="13">
-        <f>D19+E19</f>
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="28">
+        <f>SUM(D6:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="28">
+        <f>SUM(E6:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="28">
+        <f>SUM(F6:F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="29">
+        <f>SUM(G6:G17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="n">
-        <v>34658</v>
-      </c>
-      <c r="C20" s="11" t="n">
-        <v>114.9</v>
-      </c>
-      <c r="D20" s="13">
-        <f>C20*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="E20" s="13">
-        <f>B20*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F20" s="13">
-        <f>D20+E20</f>
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>PV capex ($)</t>
+        </is>
+      </c>
+      <c r="B20" s="31">
+        <f>Assumptions!$B$32*Assumptions!$B$34</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="n">
-        <v>24158</v>
-      </c>
-      <c r="C21" s="11" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="D21" s="13">
-        <f>C21*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="E21" s="13">
-        <f>B21*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F21" s="13">
-        <f>D21+E21</f>
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>PV net after ITC ($)</t>
+        </is>
+      </c>
+      <c r="B21" s="31">
+        <f>B20*(1-Assumptions!$B$20)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="32" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B22" s="32">
-        <f>SUM(B10:B21)</f>
-        <v/>
-      </c>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="33">
-        <f>SUM(D10:D21)</f>
-        <v/>
-      </c>
-      <c r="E22" s="33">
-        <f>SUM(E10:E21)</f>
-        <v/>
-      </c>
-      <c r="F22" s="33">
-        <f>SUM(F10:F21)</f>
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>PV annual value ($)</t>
+        </is>
+      </c>
+      <c r="B22" s="31">
+        <f>G18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>PV simple payback (yr)</t>
+        </is>
+      </c>
+      <c r="B23" s="32">
+        <f>IFERROR(B21/B22,"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>PV self-consumption %</t>
+        </is>
+      </c>
+      <c r="B24" s="33">
+        <f>IFERROR(E18/D18,0)</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4267,429 +5228,157 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Monthly Bill — Before vs After (50 kW / 150 kWh)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Peak before kW</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Peak after kW</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>kW shaved</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>Bill before $</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>Bill after $</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>Savings $</t>
+          <t>Value Stack — recommended battery (50/150) + optional PV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Combines every stream into one project view. Battery streams pull from Sizing row 7; PV from the Solar tab.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="C4" s="11" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="D4" s="11">
-        <f>B4-C4</f>
-        <v/>
-      </c>
-      <c r="E4" s="13">
-        <f>B4*Assumptions!$B$5+35978*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F4" s="13">
-        <f>C4*Assumptions!$B$5+35978*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="G4" s="13">
-        <f>E4-F4</f>
-        <v/>
+          <t>Value stream</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>$ / year</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="C5" s="11" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="D5" s="11">
-        <f>B5-C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="13">
-        <f>B5*Assumptions!$B$5+34421*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F5" s="13">
-        <f>C5*Assumptions!$B$5+34421*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="G5" s="13">
-        <f>E5-F5</f>
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Demand-charge savings</t>
+        </is>
+      </c>
+      <c r="B5" s="14">
+        <f>'Sizing Comparison'!E7</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="n">
-        <v>112.4</v>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>93.59999999999999</v>
-      </c>
-      <c r="D6" s="11">
-        <f>B6-C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="13">
-        <f>B6*Assumptions!$B$5+43051*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F6" s="13">
-        <f>C6*Assumptions!$B$5+43051*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="G6" s="13">
-        <f>E6-F6</f>
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Energy arbitrage (TOU)</t>
+        </is>
+      </c>
+      <c r="B6" s="14">
+        <f>'Sizing Comparison'!F7</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="C7" s="11" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="D7" s="11">
-        <f>B7-C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="13">
-        <f>B7*Assumptions!$B$5+28133*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F7" s="13">
-        <f>C7*Assumptions!$B$5+28133*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="G7" s="13">
-        <f>E7-F7</f>
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Global Adjustment (5CP)</t>
+        </is>
+      </c>
+      <c r="B7" s="14">
+        <f>'Sizing Comparison'!G7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="C8" s="11" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="D8" s="11">
-        <f>B8-C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="13">
-        <f>B8*Assumptions!$B$5+6245*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F8" s="13">
-        <f>C8*Assumptions!$B$5+6245*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="G8" s="13">
-        <f>E8-F8</f>
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Grid program / capacity</t>
+        </is>
+      </c>
+      <c r="B8" s="14">
+        <f>'Sizing Comparison'!H7</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="C9" s="11" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="D9" s="11">
-        <f>B9-C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="13">
-        <f>B9*Assumptions!$B$5+4765*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F9" s="13">
-        <f>C9*Assumptions!$B$5+4765*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="G9" s="13">
-        <f>E9-F9</f>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Resilience / backup value</t>
+        </is>
+      </c>
+      <c r="B9" s="14">
+        <f>'Sizing Comparison'!I7</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="C10" s="11" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="D10" s="11">
-        <f>B10-C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="13">
-        <f>B10*Assumptions!$B$5+4316*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F10" s="13">
-        <f>C10*Assumptions!$B$5+4316*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="G10" s="13">
-        <f>E10-F10</f>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Solar PV energy value</t>
+        </is>
+      </c>
+      <c r="B10" s="14">
+        <f>'Solar + Storage'!B22</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="C11" s="11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="D11" s="11">
-        <f>B11-C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="13">
-        <f>B11*Assumptions!$B$5+3468*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F11" s="13">
-        <f>C11*Assumptions!$B$5+3468*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="G11" s="13">
-        <f>E11-F11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="C12" s="11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D12" s="11">
-        <f>B12-C12</f>
-        <v/>
-      </c>
-      <c r="E12" s="13">
-        <f>B12*Assumptions!$B$5+2927*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F12" s="13">
-        <f>C12*Assumptions!$B$5+2927*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="G12" s="13">
-        <f>E12-F12</f>
+      <c r="A11" s="30" t="inlineStr">
+        <is>
+          <t>TOTAL ANNUAL BENEFIT</t>
+        </is>
+      </c>
+      <c r="B11" s="34">
+        <f>SUM(B5:B10)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="C13" s="11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D13" s="11">
-        <f>B13-C13</f>
-        <v/>
-      </c>
-      <c r="E13" s="13">
-        <f>B13*Assumptions!$B$5+2606*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F13" s="13">
-        <f>C13*Assumptions!$B$5+2606*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="G13" s="13">
-        <f>E13-F13</f>
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>Battery net capex</t>
+        </is>
+      </c>
+      <c r="B13" s="31">
+        <f>'Sizing Comparison'!M7</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="n">
-        <v>114.9</v>
-      </c>
-      <c r="C14" s="11" t="n">
-        <v>90</v>
-      </c>
-      <c r="D14" s="11">
-        <f>B14-C14</f>
-        <v/>
-      </c>
-      <c r="E14" s="13">
-        <f>B14*Assumptions!$B$5+34658*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F14" s="13">
-        <f>C14*Assumptions!$B$5+34658*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="G14" s="13">
-        <f>E14-F14</f>
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>Solar net capex</t>
+        </is>
+      </c>
+      <c r="B14" s="31">
+        <f>'Solar + Storage'!B21</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="C15" s="11" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="D15" s="11">
-        <f>B15-C15</f>
-        <v/>
-      </c>
-      <c r="E15" s="13">
-        <f>B15*Assumptions!$B$5+24158*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="F15" s="13">
-        <f>C15*Assumptions!$B$5+24158*Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="G15" s="13">
-        <f>E15-F15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="32" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="33">
-        <f>SUM(E4:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="33">
-        <f>SUM(F4:F15)</f>
-        <v/>
-      </c>
-      <c r="G16" s="33">
-        <f>SUM(G4:G15)</f>
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>TOTAL net capex</t>
+        </is>
+      </c>
+      <c r="B15" s="31">
+        <f>B13+B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>Combined simple payback (yr)</t>
+        </is>
+      </c>
+      <c r="B17" s="36">
+        <f>IFERROR(B15/B11,"-")</f>
         <v/>
       </c>
     </row>
@@ -4700,6 +5389,866 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Load Analysis — Calendar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>Annual energy</t>
+        </is>
+      </c>
+      <c r="B3" s="41" t="n">
+        <v>224726</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>Peak demand</t>
+        </is>
+      </c>
+      <c r="B4" s="42" t="n">
+        <v>114.9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>Average load</t>
+        </is>
+      </c>
+      <c r="B5" s="42" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>Load factor</t>
+        </is>
+      </c>
+      <c r="B6" s="33">
+        <f>B5/B4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Energy kWh</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Peak kW</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Demand $</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Energy $</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>Total $</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>35978</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="D10" s="14">
+        <f>C10*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="E10" s="14">
+        <f>B10*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F10" s="14">
+        <f>D10+E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>34421</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="D11" s="14">
+        <f>C11*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="E11" s="14">
+        <f>B11*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F11" s="14">
+        <f>D11+E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>43051</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="D12" s="14">
+        <f>C12*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="E12" s="14">
+        <f>B12*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F12" s="14">
+        <f>D12+E12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>28133</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="D13" s="14">
+        <f>C13*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="E13" s="14">
+        <f>B13*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F13" s="14">
+        <f>D13+E13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>6245</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="D14" s="14">
+        <f>C14*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="E14" s="14">
+        <f>B14*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F14" s="14">
+        <f>D14+E14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>4765</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D15" s="14">
+        <f>C15*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="E15" s="14">
+        <f>B15*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F15" s="14">
+        <f>D15+E15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>4316</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="D16" s="14">
+        <f>C16*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="E16" s="14">
+        <f>B16*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F16" s="14">
+        <f>D16+E16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>3468</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="D17" s="14">
+        <f>C17*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="E17" s="14">
+        <f>B17*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F17" s="14">
+        <f>D17+E17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>2927</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="D18" s="14">
+        <f>C18*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="E18" s="14">
+        <f>B18*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F18" s="14">
+        <f>D18+E18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>2606</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="D19" s="14">
+        <f>C19*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="E19" s="14">
+        <f>B19*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F19" s="14">
+        <f>D19+E19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>34658</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="D20" s="14">
+        <f>C20*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="E20" s="14">
+        <f>B20*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F20" s="14">
+        <f>D20+E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>24158</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="D21" s="14">
+        <f>C21*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="E21" s="14">
+        <f>B21*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F21" s="14">
+        <f>D21+E21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="27" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B22" s="27">
+        <f>SUM(B10:B21)</f>
+        <v/>
+      </c>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="29">
+        <f>SUM(D10:D21)</f>
+        <v/>
+      </c>
+      <c r="E22" s="29">
+        <f>SUM(E10:E21)</f>
+        <v/>
+      </c>
+      <c r="F22" s="29">
+        <f>SUM(F10:F21)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly Bill — Before vs After (50 kW / 150 kWh)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Peak before</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Peak after</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>kW shaved</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Bill before $</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>Bill after $</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>Savings $</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="D4" s="12">
+        <f>B4-C4</f>
+        <v/>
+      </c>
+      <c r="E4" s="14">
+        <f>B4*Assumptions!$B$5+35978*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F4" s="14">
+        <f>C4*Assumptions!$B$5+35978*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="G4" s="14">
+        <f>E4-F4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="D5" s="12">
+        <f>B5-C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="14">
+        <f>B5*Assumptions!$B$5+34421*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F5" s="14">
+        <f>C5*Assumptions!$B$5+34421*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="G5" s="14">
+        <f>E5-F5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="D6" s="12">
+        <f>B6-C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="14">
+        <f>B6*Assumptions!$B$5+43051*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F6" s="14">
+        <f>C6*Assumptions!$B$5+43051*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="G6" s="14">
+        <f>E6-F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="D7" s="12">
+        <f>B7-C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="14">
+        <f>B7*Assumptions!$B$5+28133*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F7" s="14">
+        <f>C7*Assumptions!$B$5+28133*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="G7" s="14">
+        <f>E7-F7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="D8" s="12">
+        <f>B8-C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="14">
+        <f>B8*Assumptions!$B$5+6245*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F8" s="14">
+        <f>C8*Assumptions!$B$5+6245*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="G8" s="14">
+        <f>E8-F8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D9" s="12">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="14">
+        <f>B9*Assumptions!$B$5+4765*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F9" s="14">
+        <f>C9*Assumptions!$B$5+4765*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="G9" s="14">
+        <f>E9-F9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D10" s="12">
+        <f>B10-C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="14">
+        <f>B10*Assumptions!$B$5+4316*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F10" s="14">
+        <f>C10*Assumptions!$B$5+4316*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="G10" s="14">
+        <f>E10-F10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D11" s="12">
+        <f>B11-C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="14">
+        <f>B11*Assumptions!$B$5+3468*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F11" s="14">
+        <f>C11*Assumptions!$B$5+3468*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="G11" s="14">
+        <f>E11-F11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D12" s="12">
+        <f>B12-C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="14">
+        <f>B12*Assumptions!$B$5+2927*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F12" s="14">
+        <f>C12*Assumptions!$B$5+2927*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="G12" s="14">
+        <f>E12-F12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D13" s="12">
+        <f>B13-C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="14">
+        <f>B13*Assumptions!$B$5+2606*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F13" s="14">
+        <f>C13*Assumptions!$B$5+2606*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="G13" s="14">
+        <f>E13-F13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="D14" s="12">
+        <f>B14-C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="14">
+        <f>B14*Assumptions!$B$5+34658*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F14" s="14">
+        <f>C14*Assumptions!$B$5+34658*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="G14" s="14">
+        <f>E14-F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="D15" s="12">
+        <f>B15-C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="14">
+        <f>B15*Assumptions!$B$5+24158*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="F15" s="14">
+        <f>C15*Assumptions!$B$5+24158*Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="G15" s="14">
+        <f>E15-F15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="29">
+        <f>SUM(E4:E15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="29">
+        <f>SUM(F4:F15)</f>
+        <v/>
+      </c>
+      <c r="G16" s="29">
+        <f>SUM(G4:G15)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4717,27 +6266,27 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>What the Battery Does — cold week Mar 2025 (100 kW/300 kWh, ceiling ~80.9 kW)</t>
+          <t>What the Battery Does — cold week Mar 2025 (100/300, ceiling ~80.9 kW)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Hour</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Load kW</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>Net grid kW</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>SOC kWh</t>
         </is>
@@ -7435,747 +8984,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>15-Year Cash Flow — pulls live from CF_Calc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>These two sizes mirror the CF_Calc engine. Change Assumptions and they move.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Value pick: 50/150</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Deep shave: 100/300</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>Net cash flow $</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>Cumulative $</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>Net cash flow $</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>Cumulative $</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B6" s="34">
-        <f>'CF_Calc'!E7</f>
-        <v/>
-      </c>
-      <c r="C6" s="34">
-        <f>B6</f>
-        <v/>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="34">
-        <f>'CF_Calc'!E10</f>
-        <v/>
-      </c>
-      <c r="G6" s="34">
-        <f>F6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="34">
-        <f>'CF_Calc'!F7</f>
-        <v/>
-      </c>
-      <c r="C7" s="34">
-        <f>C6+B7</f>
-        <v/>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="34">
-        <f>'CF_Calc'!F10</f>
-        <v/>
-      </c>
-      <c r="G7" s="34">
-        <f>G6+F7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="34">
-        <f>'CF_Calc'!G7</f>
-        <v/>
-      </c>
-      <c r="C8" s="34">
-        <f>C7+B8</f>
-        <v/>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="34">
-        <f>'CF_Calc'!G10</f>
-        <v/>
-      </c>
-      <c r="G8" s="34">
-        <f>G7+F8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="34">
-        <f>'CF_Calc'!H7</f>
-        <v/>
-      </c>
-      <c r="C9" s="34">
-        <f>C8+B9</f>
-        <v/>
-      </c>
-      <c r="E9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="34">
-        <f>'CF_Calc'!H10</f>
-        <v/>
-      </c>
-      <c r="G9" s="34">
-        <f>G8+F9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="34">
-        <f>'CF_Calc'!I7</f>
-        <v/>
-      </c>
-      <c r="C10" s="34">
-        <f>C9+B10</f>
-        <v/>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" s="34">
-        <f>'CF_Calc'!I10</f>
-        <v/>
-      </c>
-      <c r="G10" s="34">
-        <f>G9+F10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="34">
-        <f>'CF_Calc'!J7</f>
-        <v/>
-      </c>
-      <c r="C11" s="34">
-        <f>C10+B11</f>
-        <v/>
-      </c>
-      <c r="E11" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" s="34">
-        <f>'CF_Calc'!J10</f>
-        <v/>
-      </c>
-      <c r="G11" s="34">
-        <f>G10+F11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="34">
-        <f>'CF_Calc'!K7</f>
-        <v/>
-      </c>
-      <c r="C12" s="34">
-        <f>C11+B12</f>
-        <v/>
-      </c>
-      <c r="E12" t="n">
-        <v>6</v>
-      </c>
-      <c r="F12" s="34">
-        <f>'CF_Calc'!K10</f>
-        <v/>
-      </c>
-      <c r="G12" s="34">
-        <f>G11+F12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="34">
-        <f>'CF_Calc'!L7</f>
-        <v/>
-      </c>
-      <c r="C13" s="34">
-        <f>C12+B13</f>
-        <v/>
-      </c>
-      <c r="E13" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="34">
-        <f>'CF_Calc'!L10</f>
-        <v/>
-      </c>
-      <c r="G13" s="34">
-        <f>G12+F13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="34">
-        <f>'CF_Calc'!M7</f>
-        <v/>
-      </c>
-      <c r="C14" s="34">
-        <f>C13+B14</f>
-        <v/>
-      </c>
-      <c r="E14" t="n">
-        <v>8</v>
-      </c>
-      <c r="F14" s="34">
-        <f>'CF_Calc'!M10</f>
-        <v/>
-      </c>
-      <c r="G14" s="34">
-        <f>G13+F14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="34">
-        <f>'CF_Calc'!N7</f>
-        <v/>
-      </c>
-      <c r="C15" s="34">
-        <f>C14+B15</f>
-        <v/>
-      </c>
-      <c r="E15" t="n">
-        <v>9</v>
-      </c>
-      <c r="F15" s="34">
-        <f>'CF_Calc'!N10</f>
-        <v/>
-      </c>
-      <c r="G15" s="34">
-        <f>G14+F15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="34">
-        <f>'CF_Calc'!O7</f>
-        <v/>
-      </c>
-      <c r="C16" s="34">
-        <f>C15+B16</f>
-        <v/>
-      </c>
-      <c r="E16" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" s="34">
-        <f>'CF_Calc'!O10</f>
-        <v/>
-      </c>
-      <c r="G16" s="34">
-        <f>G15+F16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="34">
-        <f>'CF_Calc'!P7</f>
-        <v/>
-      </c>
-      <c r="C17" s="34">
-        <f>C16+B17</f>
-        <v/>
-      </c>
-      <c r="E17" t="n">
-        <v>11</v>
-      </c>
-      <c r="F17" s="34">
-        <f>'CF_Calc'!P10</f>
-        <v/>
-      </c>
-      <c r="G17" s="34">
-        <f>G16+F17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>12</v>
-      </c>
-      <c r="B18" s="34">
-        <f>'CF_Calc'!Q7</f>
-        <v/>
-      </c>
-      <c r="C18" s="34">
-        <f>C17+B18</f>
-        <v/>
-      </c>
-      <c r="E18" t="n">
-        <v>12</v>
-      </c>
-      <c r="F18" s="34">
-        <f>'CF_Calc'!Q10</f>
-        <v/>
-      </c>
-      <c r="G18" s="34">
-        <f>G17+F18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>13</v>
-      </c>
-      <c r="B19" s="34">
-        <f>'CF_Calc'!R7</f>
-        <v/>
-      </c>
-      <c r="C19" s="34">
-        <f>C18+B19</f>
-        <v/>
-      </c>
-      <c r="E19" t="n">
-        <v>13</v>
-      </c>
-      <c r="F19" s="34">
-        <f>'CF_Calc'!R10</f>
-        <v/>
-      </c>
-      <c r="G19" s="34">
-        <f>G18+F19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>14</v>
-      </c>
-      <c r="B20" s="34">
-        <f>'CF_Calc'!S7</f>
-        <v/>
-      </c>
-      <c r="C20" s="34">
-        <f>C19+B20</f>
-        <v/>
-      </c>
-      <c r="E20" t="n">
-        <v>14</v>
-      </c>
-      <c r="F20" s="34">
-        <f>'CF_Calc'!S10</f>
-        <v/>
-      </c>
-      <c r="G20" s="34">
-        <f>G19+F20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>15</v>
-      </c>
-      <c r="B21" s="34">
-        <f>'CF_Calc'!T7</f>
-        <v/>
-      </c>
-      <c r="C21" s="34">
-        <f>C20+B21</f>
-        <v/>
-      </c>
-      <c r="E21" t="n">
-        <v>15</v>
-      </c>
-      <c r="F21" s="34">
-        <f>'CF_Calc'!T10</f>
-        <v/>
-      </c>
-      <c r="G21" s="34">
-        <f>G20+F21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="23" t="inlineStr">
-        <is>
-          <t>Payback (yr)</t>
-        </is>
-      </c>
-      <c r="B23" s="35">
-        <f>'Sizing Comparison'!L7</f>
-        <v/>
-      </c>
-      <c r="E23" s="23" t="inlineStr">
-        <is>
-          <t>Payback (yr)</t>
-        </is>
-      </c>
-      <c r="F23" s="35">
-        <f>'Sizing Comparison'!L10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="23" t="inlineStr">
-        <is>
-          <t>NPV</t>
-        </is>
-      </c>
-      <c r="B24" s="34">
-        <f>'CF_Calc'!U7</f>
-        <v/>
-      </c>
-      <c r="E24" s="23" t="inlineStr">
-        <is>
-          <t>NPV</t>
-        </is>
-      </c>
-      <c r="F24" s="34">
-        <f>'CF_Calc'!U10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="23" t="inlineStr">
-        <is>
-          <t>IRR</t>
-        </is>
-      </c>
-      <c r="B25" s="31">
-        <f>'CF_Calc'!V7</f>
-        <v/>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
-        <is>
-          <t>IRR</t>
-        </is>
-      </c>
-      <c r="F25" s="31">
-        <f>'CF_Calc'!V10</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Backup / Resilience — outage runtime (hours)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Usable = Energy × DoD (Assumptions!B13). Runtime = usable ÷ load served.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Energy kWh</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Usable kWh</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Winter ~48 kW</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Shoulder ~25 kW</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Summer ~5 kW</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>Critical ~10 kW</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="n">
-        <v>60</v>
-      </c>
-      <c r="B5" s="36">
-        <f>A5*Assumptions!$B$13</f>
-        <v/>
-      </c>
-      <c r="C5" s="36">
-        <f>B5/48</f>
-        <v/>
-      </c>
-      <c r="D5" s="36">
-        <f>B5/25</f>
-        <v/>
-      </c>
-      <c r="E5" s="36">
-        <f>B5/5</f>
-        <v/>
-      </c>
-      <c r="F5" s="36">
-        <f>B5/10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" s="36">
-        <f>A6*Assumptions!$B$13</f>
-        <v/>
-      </c>
-      <c r="C6" s="36">
-        <f>B6/48</f>
-        <v/>
-      </c>
-      <c r="D6" s="36">
-        <f>B6/25</f>
-        <v/>
-      </c>
-      <c r="E6" s="36">
-        <f>B6/5</f>
-        <v/>
-      </c>
-      <c r="F6" s="36">
-        <f>B6/10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" s="36">
-        <f>A7*Assumptions!$B$13</f>
-        <v/>
-      </c>
-      <c r="C7" s="36">
-        <f>B7/48</f>
-        <v/>
-      </c>
-      <c r="D7" s="36">
-        <f>B7/25</f>
-        <v/>
-      </c>
-      <c r="E7" s="36">
-        <f>B7/5</f>
-        <v/>
-      </c>
-      <c r="F7" s="36">
-        <f>B7/10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" s="36">
-        <f>A8*Assumptions!$B$13</f>
-        <v/>
-      </c>
-      <c r="C8" s="36">
-        <f>B8/48</f>
-        <v/>
-      </c>
-      <c r="D8" s="36">
-        <f>B8/25</f>
-        <v/>
-      </c>
-      <c r="E8" s="36">
-        <f>B8/5</f>
-        <v/>
-      </c>
-      <c r="F8" s="36">
-        <f>B8/10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>300</v>
-      </c>
-      <c r="B9" s="36">
-        <f>A9*Assumptions!$B$13</f>
-        <v/>
-      </c>
-      <c r="C9" s="36">
-        <f>B9/48</f>
-        <v/>
-      </c>
-      <c r="D9" s="36">
-        <f>B9/25</f>
-        <v/>
-      </c>
-      <c r="E9" s="36">
-        <f>B9/5</f>
-        <v/>
-      </c>
-      <c r="F9" s="36">
-        <f>B9/10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>400</v>
-      </c>
-      <c r="B10" s="36">
-        <f>A10*Assumptions!$B$13</f>
-        <v/>
-      </c>
-      <c r="C10" s="36">
-        <f>B10/48</f>
-        <v/>
-      </c>
-      <c r="D10" s="36">
-        <f>B10/25</f>
-        <v/>
-      </c>
-      <c r="E10" s="36">
-        <f>B10/5</f>
-        <v/>
-      </c>
-      <c r="F10" s="36">
-        <f>B10/10</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/castellan_btm_model/Castellan_BESS_Model.xlsx
+++ b/castellan_btm_model/Castellan_BESS_Model.xlsx
@@ -1568,7 +1568,7 @@
       </c>
       <c r="E12" s="37">
         <f>'Sizing Comparison'!J7</f>
-        <v/>
+        <v>6168.008</v>
       </c>
     </row>
     <row r="13">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="E13" s="37">
         <f>'Sizing Comparison'!M7</f>
-        <v/>
+        <v>80500</v>
       </c>
     </row>
     <row r="14">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="E14" s="38">
         <f>'Sizing Comparison'!N7</f>
-        <v/>
+        <v>13.05121524</v>
       </c>
     </row>
     <row r="15">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="E15" s="37">
         <f>'Sizing Comparison'!O7</f>
-        <v/>
+        <v>-45301.89769</v>
       </c>
     </row>
     <row r="16">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="E16" s="39">
         <f>'Sizing Comparison'!P7</f>
-        <v/>
+        <v>-0.035832867</v>
       </c>
     </row>
     <row r="17">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E17" s="38">
         <f>'Value Stacking'!B17</f>
-        <v/>
+        <v>13.05121524</v>
       </c>
     </row>
     <row r="19">
@@ -1817,22 +1817,22 @@
       </c>
       <c r="B5" s="31">
         <f>'CF_Calc'!E7</f>
-        <v/>
+        <v>-80500</v>
       </c>
       <c r="C5" s="31">
         <f>B5</f>
-        <v/>
+        <v>-80500</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="31">
         <f>'CF_Calc'!E10</f>
-        <v/>
+        <v>-147000</v>
       </c>
       <c r="G5" s="31">
         <f>F5</f>
-        <v/>
+        <v>-147000</v>
       </c>
     </row>
     <row r="6">
@@ -1841,22 +1841,22 @@
       </c>
       <c r="B6" s="31">
         <f>'CF_Calc'!F7</f>
-        <v/>
+        <v>4443.008</v>
       </c>
       <c r="C6" s="31">
         <f>C5+B6</f>
-        <v/>
+        <v>-76056.992</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="31">
         <f>'CF_Calc'!F10</f>
-        <v/>
+        <v>4235.072</v>
       </c>
       <c r="G6" s="31">
         <f>G5+F6</f>
-        <v/>
+        <v>-142764.928</v>
       </c>
     </row>
     <row r="7">
@@ -1865,22 +1865,22 @@
       </c>
       <c r="B7" s="31">
         <f>'CF_Calc'!G7</f>
-        <v/>
+        <v>4404.652995</v>
       </c>
       <c r="C7" s="31">
         <f>C6+B7</f>
-        <v/>
+        <v>-71652.33901</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="31">
         <f>'CF_Calc'!G10</f>
-        <v/>
+        <v>4167.45633</v>
       </c>
       <c r="G7" s="31">
         <f>G6+F7</f>
-        <v/>
+        <v>-138597.4717</v>
       </c>
     </row>
     <row r="8">
@@ -1889,22 +1889,22 @@
       </c>
       <c r="B8" s="31">
         <f>'CF_Calc'!H7</f>
-        <v/>
+        <v>4361.560235</v>
       </c>
       <c r="C8" s="31">
         <f>C7+B8</f>
-        <v/>
+        <v>-67290.77877</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="31">
         <f>'CF_Calc'!H10</f>
-        <v/>
+        <v>4093.734206</v>
       </c>
       <c r="G8" s="31">
         <f>G7+F8</f>
-        <v/>
+        <v>-134503.7375</v>
       </c>
     </row>
     <row r="9">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="B9" s="31">
         <f>'CF_Calc'!I7</f>
-        <v/>
+        <v>4313.515941</v>
       </c>
       <c r="C9" s="31">
         <f>C8+B9</f>
-        <v/>
+        <v>-62977.26283</v>
       </c>
       <c r="E9" t="n">
         <v>4</v>
       </c>
       <c r="F9" s="31">
         <f>'CF_Calc'!I10</f>
-        <v/>
+        <v>4013.640992</v>
       </c>
       <c r="G9" s="31">
         <f>G8+F9</f>
-        <v/>
+        <v>-130490.0965</v>
       </c>
     </row>
     <row r="10">
@@ -1937,22 +1937,22 @@
       </c>
       <c r="B10" s="31">
         <f>'CF_Calc'!J7</f>
-        <v/>
+        <v>4260.29859</v>
       </c>
       <c r="C10" s="31">
         <f>C9+B10</f>
-        <v/>
+        <v>-58716.96424</v>
       </c>
       <c r="E10" t="n">
         <v>5</v>
       </c>
       <c r="F10" s="31">
         <f>'CF_Calc'!J10</f>
-        <v/>
+        <v>3926.902601</v>
       </c>
       <c r="G10" s="31">
         <f>G9+F10</f>
-        <v/>
+        <v>-126563.1939</v>
       </c>
     </row>
     <row r="11">
@@ -1961,22 +1961,22 @@
       </c>
       <c r="B11" s="31">
         <f>'CF_Calc'!K7</f>
-        <v/>
+        <v>4201.678659</v>
       </c>
       <c r="C11" s="31">
         <f>C10+B11</f>
-        <v/>
+        <v>-54515.28558</v>
       </c>
       <c r="E11" t="n">
         <v>6</v>
       </c>
       <c r="F11" s="31">
         <f>'CF_Calc'!K10</f>
-        <v/>
+        <v>3833.235194</v>
       </c>
       <c r="G11" s="31">
         <f>G10+F11</f>
-        <v/>
+        <v>-122729.9587</v>
       </c>
     </row>
     <row r="12">
@@ -1985,22 +1985,22 @@
       </c>
       <c r="B12" s="31">
         <f>'CF_Calc'!L7</f>
-        <v/>
+        <v>4137.418366</v>
       </c>
       <c r="C12" s="31">
         <f>C11+B12</f>
-        <v/>
+        <v>-50377.86721</v>
       </c>
       <c r="E12" t="n">
         <v>7</v>
       </c>
       <c r="F12" s="31">
         <f>'CF_Calc'!L10</f>
-        <v/>
+        <v>3732.344862</v>
       </c>
       <c r="G12" s="31">
         <f>G11+F12</f>
-        <v/>
+        <v>-118997.6138</v>
       </c>
     </row>
     <row r="13">
@@ -2009,22 +2009,22 @@
       </c>
       <c r="B13" s="31">
         <f>'CF_Calc'!M7</f>
-        <v/>
+        <v>4067.271395</v>
       </c>
       <c r="C13" s="31">
         <f>C12+B13</f>
-        <v/>
+        <v>-46310.59582</v>
       </c>
       <c r="E13" t="n">
         <v>8</v>
       </c>
       <c r="F13" s="31">
         <f>'CF_Calc'!M10</f>
-        <v/>
+        <v>3623.927295</v>
       </c>
       <c r="G13" s="31">
         <f>G12+F13</f>
-        <v/>
+        <v>-115373.6865</v>
       </c>
     </row>
     <row r="14">
@@ -2033,22 +2033,22 @@
       </c>
       <c r="B14" s="31">
         <f>'CF_Calc'!N7</f>
-        <v/>
+        <v>3990.982623</v>
       </c>
       <c r="C14" s="31">
         <f>C13+B14</f>
-        <v/>
+        <v>-42319.6132</v>
       </c>
       <c r="E14" t="n">
         <v>9</v>
       </c>
       <c r="F14" s="31">
         <f>'CF_Calc'!N10</f>
-        <v/>
+        <v>3507.667448</v>
       </c>
       <c r="G14" s="31">
         <f>G13+F14</f>
-        <v/>
+        <v>-111866.0191</v>
       </c>
     </row>
     <row r="15">
@@ -2057,22 +2057,22 @@
       </c>
       <c r="B15" s="31">
         <f>'CF_Calc'!O7</f>
-        <v/>
+        <v>3908.287831</v>
       </c>
       <c r="C15" s="31">
         <f>C14+B15</f>
-        <v/>
+        <v>-38411.32537</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" s="31">
         <f>'CF_Calc'!O10</f>
-        <v/>
+        <v>3383.239196</v>
       </c>
       <c r="G15" s="31">
         <f>G14+F15</f>
-        <v/>
+        <v>-108482.7799</v>
       </c>
     </row>
     <row r="16">
@@ -2081,22 +2081,22 @@
       </c>
       <c r="B16" s="31">
         <f>'CF_Calc'!P7</f>
-        <v/>
+        <v>3818.913407</v>
       </c>
       <c r="C16" s="31">
         <f>C15+B16</f>
-        <v/>
+        <v>-34592.41196</v>
       </c>
       <c r="E16" t="n">
         <v>11</v>
       </c>
       <c r="F16" s="31">
         <f>'CF_Calc'!P10</f>
-        <v/>
+        <v>3250.304971</v>
       </c>
       <c r="G16" s="31">
         <f>G15+F16</f>
-        <v/>
+        <v>-105232.4749</v>
       </c>
     </row>
     <row r="17">
@@ -2105,22 +2105,22 @@
       </c>
       <c r="B17" s="31">
         <f>'CF_Calc'!Q7</f>
-        <v/>
+        <v>3722.576044</v>
       </c>
       <c r="C17" s="31">
         <f>C16+B17</f>
-        <v/>
+        <v>-30869.83591</v>
       </c>
       <c r="E17" t="n">
         <v>12</v>
       </c>
       <c r="F17" s="31">
         <f>'CF_Calc'!Q10</f>
-        <v/>
+        <v>3108.515396</v>
       </c>
       <c r="G17" s="31">
         <f>G16+F17</f>
-        <v/>
+        <v>-102123.9595</v>
       </c>
     </row>
     <row r="18">
@@ -2129,22 +2129,22 @@
       </c>
       <c r="B18" s="31">
         <f>'CF_Calc'!R7</f>
-        <v/>
+        <v>3618.982423</v>
       </c>
       <c r="C18" s="31">
         <f>C17+B18</f>
-        <v/>
+        <v>-27250.85349</v>
       </c>
       <c r="E18" t="n">
         <v>13</v>
       </c>
       <c r="F18" s="31">
         <f>'CF_Calc'!R10</f>
-        <v/>
+        <v>2957.508906</v>
       </c>
       <c r="G18" s="31">
         <f>G17+F18</f>
-        <v/>
+        <v>-99166.4506</v>
       </c>
     </row>
     <row r="19">
@@ -2153,22 +2153,22 @@
       </c>
       <c r="B19" s="31">
         <f>'CF_Calc'!S7</f>
-        <v/>
+        <v>3507.828891</v>
       </c>
       <c r="C19" s="31">
         <f>C18+B19</f>
-        <v/>
+        <v>-23743.0246</v>
       </c>
       <c r="E19" t="n">
         <v>14</v>
       </c>
       <c r="F19" s="31">
         <f>'CF_Calc'!S10</f>
-        <v/>
+        <v>2796.911354</v>
       </c>
       <c r="G19" s="31">
         <f>G18+F19</f>
-        <v/>
+        <v>-96369.53925</v>
       </c>
     </row>
     <row r="20">
@@ -2177,22 +2177,22 @@
       </c>
       <c r="B20" s="31">
         <f>'CF_Calc'!T7</f>
-        <v/>
+        <v>3388.801124</v>
       </c>
       <c r="C20" s="31">
         <f>C19+B20</f>
-        <v/>
+        <v>-20354.22348</v>
       </c>
       <c r="E20" t="n">
         <v>15</v>
       </c>
       <c r="F20" s="31">
         <f>'CF_Calc'!T10</f>
-        <v/>
+        <v>2626.335608</v>
       </c>
       <c r="G20" s="31">
         <f>G19+F20</f>
-        <v/>
+        <v>-93743.20364</v>
       </c>
     </row>
     <row r="22">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="B22" s="32">
         <f>'Sizing Comparison'!N7</f>
-        <v/>
+        <v>13.05121524</v>
       </c>
       <c r="E22" s="30" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F22" s="32">
         <f>'Sizing Comparison'!N10</f>
-        <v/>
+        <v>19.90501921</v>
       </c>
     </row>
     <row r="23">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B23" s="31">
         <f>'CF_Calc'!U7</f>
-        <v/>
+        <v>-45301.89769</v>
       </c>
       <c r="E23" s="30" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="F23" s="31">
         <f>'CF_Calc'!U10</f>
-        <v/>
+        <v>-115264.1005</v>
       </c>
     </row>
     <row r="24">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="B24" s="33">
         <f>'CF_Calc'!V7</f>
-        <v/>
+        <v>-0.035832867</v>
       </c>
       <c r="E24" s="30" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="F24" s="33">
         <f>'CF_Calc'!V10</f>
-        <v/>
+        <v>-0.1128356093</v>
       </c>
     </row>
   </sheetData>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="B13" s="12">
         <f>Assumptions!B24</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="B14" s="12">
         <f>'Sizing Comparison'!A7</f>
-        <v/>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="B15" s="14">
         <f>Assumptions!B25</f>
-        <v/>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="B16" s="43">
         <f>'Sizing Comparison'!G7</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2465,23 +2465,23 @@
       </c>
       <c r="B5" s="13">
         <f>(150*400*(1-Assumptions!$B$20))/(238.7*10)</f>
-        <v/>
+        <v>17.59530792</v>
       </c>
       <c r="C5" s="13">
         <f>(150*500*(1-Assumptions!$B$20))/(238.7*10)</f>
-        <v/>
+        <v>21.9941349</v>
       </c>
       <c r="D5" s="13">
         <f>(150*600*(1-Assumptions!$B$20))/(238.7*10)</f>
-        <v/>
+        <v>26.39296188</v>
       </c>
       <c r="E5" s="13">
         <f>(150*700*(1-Assumptions!$B$20))/(238.7*10)</f>
-        <v/>
+        <v>30.79178886</v>
       </c>
       <c r="F5" s="13">
         <f>(150*800*(1-Assumptions!$B$20))/(238.7*10)</f>
-        <v/>
+        <v>35.19061584</v>
       </c>
     </row>
     <row r="6">
@@ -2490,23 +2490,23 @@
       </c>
       <c r="B6" s="13">
         <f>(150*400*(1-Assumptions!$B$20))/(238.7*15)</f>
-        <v/>
+        <v>11.73020528</v>
       </c>
       <c r="C6" s="13">
         <f>(150*500*(1-Assumptions!$B$20))/(238.7*15)</f>
-        <v/>
+        <v>14.6627566</v>
       </c>
       <c r="D6" s="13">
         <f>(150*600*(1-Assumptions!$B$20))/(238.7*15)</f>
-        <v/>
+        <v>17.59530792</v>
       </c>
       <c r="E6" s="13">
         <f>(150*700*(1-Assumptions!$B$20))/(238.7*15)</f>
-        <v/>
+        <v>20.52785924</v>
       </c>
       <c r="F6" s="13">
         <f>(150*800*(1-Assumptions!$B$20))/(238.7*15)</f>
-        <v/>
+        <v>23.46041056</v>
       </c>
     </row>
     <row r="7">
@@ -2515,23 +2515,23 @@
       </c>
       <c r="B7" s="13">
         <f>(150*400*(1-Assumptions!$B$20))/(238.7*20)</f>
-        <v/>
+        <v>8.797653959</v>
       </c>
       <c r="C7" s="13">
         <f>(150*500*(1-Assumptions!$B$20))/(238.7*20)</f>
-        <v/>
+        <v>10.99706745</v>
       </c>
       <c r="D7" s="13">
         <f>(150*600*(1-Assumptions!$B$20))/(238.7*20)</f>
-        <v/>
+        <v>13.19648094</v>
       </c>
       <c r="E7" s="13">
         <f>(150*700*(1-Assumptions!$B$20))/(238.7*20)</f>
-        <v/>
+        <v>15.39589443</v>
       </c>
       <c r="F7" s="13">
         <f>(150*800*(1-Assumptions!$B$20))/(238.7*20)</f>
-        <v/>
+        <v>17.59530792</v>
       </c>
     </row>
     <row r="8">
@@ -2540,23 +2540,23 @@
       </c>
       <c r="B8" s="13">
         <f>(150*400*(1-Assumptions!$B$20))/(238.7*25.84)</f>
-        <v/>
+        <v>6.80932969</v>
       </c>
       <c r="C8" s="13">
         <f>(150*500*(1-Assumptions!$B$20))/(238.7*25.84)</f>
-        <v/>
+        <v>8.511662112</v>
       </c>
       <c r="D8" s="13">
         <f>(150*600*(1-Assumptions!$B$20))/(238.7*25.84)</f>
-        <v/>
+        <v>10.21399453</v>
       </c>
       <c r="E8" s="13">
         <f>(150*700*(1-Assumptions!$B$20))/(238.7*25.84)</f>
-        <v/>
+        <v>11.91632696</v>
       </c>
       <c r="F8" s="13">
         <f>(150*800*(1-Assumptions!$B$20))/(238.7*25.84)</f>
-        <v/>
+        <v>13.61865938</v>
       </c>
     </row>
     <row r="9">
@@ -2565,23 +2565,23 @@
       </c>
       <c r="B9" s="13">
         <f>(150*400*(1-Assumptions!$B$20))/(238.7*30)</f>
-        <v/>
+        <v>5.865102639</v>
       </c>
       <c r="C9" s="13">
         <f>(150*500*(1-Assumptions!$B$20))/(238.7*30)</f>
-        <v/>
+        <v>7.331378299</v>
       </c>
       <c r="D9" s="13">
         <f>(150*600*(1-Assumptions!$B$20))/(238.7*30)</f>
-        <v/>
+        <v>8.797653959</v>
       </c>
       <c r="E9" s="13">
         <f>(150*700*(1-Assumptions!$B$20))/(238.7*30)</f>
-        <v/>
+        <v>10.26392962</v>
       </c>
       <c r="F9" s="13">
         <f>(150*800*(1-Assumptions!$B$20))/(238.7*30)</f>
-        <v/>
+        <v>11.73020528</v>
       </c>
     </row>
     <row r="10">
@@ -2590,23 +2590,23 @@
       </c>
       <c r="B10" s="13">
         <f>(150*400*(1-Assumptions!$B$20))/(238.7*40)</f>
-        <v/>
+        <v>4.398826979</v>
       </c>
       <c r="C10" s="13">
         <f>(150*500*(1-Assumptions!$B$20))/(238.7*40)</f>
-        <v/>
+        <v>5.498533724</v>
       </c>
       <c r="D10" s="13">
         <f>(150*600*(1-Assumptions!$B$20))/(238.7*40)</f>
-        <v/>
+        <v>6.598240469</v>
       </c>
       <c r="E10" s="13">
         <f>(150*700*(1-Assumptions!$B$20))/(238.7*40)</f>
-        <v/>
+        <v>7.697947214</v>
       </c>
       <c r="F10" s="13">
         <f>(150*800*(1-Assumptions!$B$20))/(238.7*40)</f>
-        <v/>
+        <v>8.797653959</v>
       </c>
     </row>
     <row r="12">
@@ -3188,58 +3188,58 @@
       </c>
       <c r="C5" s="13">
         <f>B5/A5</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D5" s="13" t="n">
         <v>153.9</v>
       </c>
       <c r="E5" s="14">
         <f>D5*Assumptions!$B$5</f>
-        <v/>
+        <v>3976.776</v>
       </c>
       <c r="F5" s="14">
         <f>B5*Assumptions!$B$13*Assumptions!$B$8*Assumptions!$B$9*Assumptions!$B$12</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G5" s="14">
         <f>A5*Assumptions!$B$25*Assumptions!$B$24</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H5" s="14">
         <f>A5*Assumptions!$B$28*Assumptions!$B$29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I5" s="14">
         <f>Assumptions!$B$41</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J5" s="14">
         <f>E5+F5+G5+H5+I5</f>
-        <v/>
+        <v>3976.776</v>
       </c>
       <c r="K5" s="14">
         <f>A5*Assumptions!$B$17+B5*Assumptions!$B$18+Assumptions!$B$19</f>
-        <v/>
+        <v>62000</v>
       </c>
       <c r="L5" s="14">
         <f>K5*Assumptions!$B$20</f>
-        <v/>
+        <v>18600</v>
       </c>
       <c r="M5" s="14">
         <f>K5-L5-Assumptions!$B$21</f>
-        <v/>
+        <v>43400</v>
       </c>
       <c r="N5" s="13">
         <f>M5/J5</f>
-        <v/>
+        <v>10.91336299</v>
       </c>
       <c r="O5" s="14">
         <f>'CF_Calc'!U5</f>
-        <v/>
+        <v>-18958.1907</v>
       </c>
       <c r="P5" s="15">
         <f>'CF_Calc'!V5</f>
-        <v/>
+        <v>-0.004440704189</v>
       </c>
     </row>
     <row r="6">
@@ -3251,58 +3251,58 @@
       </c>
       <c r="C6" s="17">
         <f>B6/A6</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D6" s="17" t="n">
         <v>199.7</v>
       </c>
       <c r="E6" s="18">
         <f>D6*Assumptions!$B$5</f>
-        <v/>
+        <v>5160.248</v>
       </c>
       <c r="F6" s="18">
         <f>B6*Assumptions!$B$13*Assumptions!$B$8*Assumptions!$B$9*Assumptions!$B$12</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G6" s="18">
         <f>A6*Assumptions!$B$25*Assumptions!$B$24</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H6" s="18">
         <f>A6*Assumptions!$B$28*Assumptions!$B$29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I6" s="18">
         <f>Assumptions!$B$41</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J6" s="18">
         <f>E6+F6+G6+H6+I6</f>
-        <v/>
+        <v>5160.248</v>
       </c>
       <c r="K6" s="18">
         <f>A6*Assumptions!$B$17+B6*Assumptions!$B$18+Assumptions!$B$19</f>
-        <v/>
+        <v>90000</v>
       </c>
       <c r="L6" s="18">
         <f>K6*Assumptions!$B$20</f>
-        <v/>
+        <v>27000</v>
       </c>
       <c r="M6" s="18">
         <f>K6-L6-Assumptions!$B$21</f>
-        <v/>
+        <v>63000</v>
       </c>
       <c r="N6" s="17">
         <f>M6/J6</f>
-        <v/>
+        <v>12.20871555</v>
       </c>
       <c r="O6" s="18">
         <f>'CF_Calc'!U6</f>
-        <v/>
+        <v>-32658.82052</v>
       </c>
       <c r="P6" s="19">
         <f>'CF_Calc'!V6</f>
-        <v/>
+        <v>-0.02416452145</v>
       </c>
     </row>
     <row r="7">
@@ -3314,58 +3314,58 @@
       </c>
       <c r="C7" s="21">
         <f>B7/A7</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="D7" s="21" t="n">
         <v>238.7</v>
       </c>
       <c r="E7" s="22">
         <f>D7*Assumptions!$B$5</f>
-        <v/>
+        <v>6168.008</v>
       </c>
       <c r="F7" s="22">
         <f>B7*Assumptions!$B$13*Assumptions!$B$8*Assumptions!$B$9*Assumptions!$B$12</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G7" s="22">
         <f>A7*Assumptions!$B$25*Assumptions!$B$24</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H7" s="22">
         <f>A7*Assumptions!$B$28*Assumptions!$B$29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I7" s="22">
         <f>Assumptions!$B$41</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J7" s="22">
         <f>E7+F7+G7+H7+I7</f>
-        <v/>
+        <v>6168.008</v>
       </c>
       <c r="K7" s="22">
         <f>A7*Assumptions!$B$17+B7*Assumptions!$B$18+Assumptions!$B$19</f>
-        <v/>
+        <v>115000</v>
       </c>
       <c r="L7" s="22">
         <f>K7*Assumptions!$B$20</f>
-        <v/>
+        <v>34500</v>
       </c>
       <c r="M7" s="22">
         <f>K7-L7-Assumptions!$B$21</f>
-        <v/>
+        <v>80500</v>
       </c>
       <c r="N7" s="21">
         <f>M7/J7</f>
-        <v/>
+        <v>13.05121524</v>
       </c>
       <c r="O7" s="22">
         <f>'CF_Calc'!U7</f>
-        <v/>
+        <v>-45301.89769</v>
       </c>
       <c r="P7" s="23">
         <f>'CF_Calc'!V7</f>
-        <v/>
+        <v>-0.035832867</v>
       </c>
     </row>
     <row r="8">
@@ -3377,58 +3377,58 @@
       </c>
       <c r="C8" s="17">
         <f>B8/A8</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D8" s="17" t="n">
         <v>238.7</v>
       </c>
       <c r="E8" s="18">
         <f>D8*Assumptions!$B$5</f>
-        <v/>
+        <v>6168.008</v>
       </c>
       <c r="F8" s="18">
         <f>B8*Assumptions!$B$13*Assumptions!$B$8*Assumptions!$B$9*Assumptions!$B$12</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G8" s="18">
         <f>A8*Assumptions!$B$25*Assumptions!$B$24</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H8" s="18">
         <f>A8*Assumptions!$B$28*Assumptions!$B$29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I8" s="18">
         <f>Assumptions!$B$41</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J8" s="18">
         <f>E8+F8+G8+H8+I8</f>
-        <v/>
+        <v>6168.008</v>
       </c>
       <c r="K8" s="18">
         <f>A8*Assumptions!$B$17+B8*Assumptions!$B$18+Assumptions!$B$19</f>
-        <v/>
+        <v>125000</v>
       </c>
       <c r="L8" s="18">
         <f>K8*Assumptions!$B$20</f>
-        <v/>
+        <v>37500</v>
       </c>
       <c r="M8" s="18">
         <f>K8-L8-Assumptions!$B$21</f>
-        <v/>
+        <v>87500</v>
       </c>
       <c r="N8" s="17">
         <f>M8/J8</f>
-        <v/>
+        <v>14.18610352</v>
       </c>
       <c r="O8" s="18">
         <f>'CF_Calc'!U8</f>
-        <v/>
+        <v>-53741.21312</v>
       </c>
       <c r="P8" s="19">
         <f>'CF_Calc'!V8</f>
-        <v/>
+        <v>-0.05043723692</v>
       </c>
     </row>
     <row r="9">
@@ -3440,58 +3440,58 @@
       </c>
       <c r="C9" s="13">
         <f>B9/A9</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D9" s="13" t="n">
         <v>261</v>
       </c>
       <c r="E9" s="14">
         <f>D9*Assumptions!$B$5</f>
-        <v/>
+        <v>6744.24</v>
       </c>
       <c r="F9" s="14">
         <f>B9*Assumptions!$B$13*Assumptions!$B$8*Assumptions!$B$9*Assumptions!$B$12</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G9" s="14">
         <f>A9*Assumptions!$B$25*Assumptions!$B$24</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H9" s="14">
         <f>A9*Assumptions!$B$28*Assumptions!$B$29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I9" s="14">
         <f>Assumptions!$B$41</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J9" s="14">
         <f>E9+F9+G9+H9+I9</f>
-        <v/>
+        <v>6744.24</v>
       </c>
       <c r="K9" s="14">
         <f>A9*Assumptions!$B$17+B9*Assumptions!$B$18+Assumptions!$B$19</f>
-        <v/>
+        <v>160000</v>
       </c>
       <c r="L9" s="14">
         <f>K9*Assumptions!$B$20</f>
-        <v/>
+        <v>48000</v>
       </c>
       <c r="M9" s="14">
         <f>K9-L9-Assumptions!$B$21</f>
-        <v/>
+        <v>112000</v>
       </c>
       <c r="N9" s="13">
         <f>M9/J9</f>
-        <v/>
+        <v>16.6067637</v>
       </c>
       <c r="O9" s="14">
         <f>'CF_Calc'!U9</f>
-        <v/>
+        <v>-78444.1706</v>
       </c>
       <c r="P9" s="15">
         <f>'CF_Calc'!V9</f>
-        <v/>
+        <v>-0.07851302868</v>
       </c>
     </row>
     <row r="10">
@@ -3503,58 +3503,58 @@
       </c>
       <c r="C10" s="17">
         <f>B10/A10</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="D10" s="17" t="n">
         <v>285.8</v>
       </c>
       <c r="E10" s="18">
         <f>D10*Assumptions!$B$5</f>
-        <v/>
+        <v>7385.072</v>
       </c>
       <c r="F10" s="18">
         <f>B10*Assumptions!$B$13*Assumptions!$B$8*Assumptions!$B$9*Assumptions!$B$12</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G10" s="18">
         <f>A10*Assumptions!$B$25*Assumptions!$B$24</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H10" s="18">
         <f>A10*Assumptions!$B$28*Assumptions!$B$29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I10" s="18">
         <f>Assumptions!$B$41</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J10" s="18">
         <f>E10+F10+G10+H10+I10</f>
-        <v/>
+        <v>7385.072</v>
       </c>
       <c r="K10" s="18">
         <f>A10*Assumptions!$B$17+B10*Assumptions!$B$18+Assumptions!$B$19</f>
-        <v/>
+        <v>210000</v>
       </c>
       <c r="L10" s="18">
         <f>K10*Assumptions!$B$20</f>
-        <v/>
+        <v>63000</v>
       </c>
       <c r="M10" s="18">
         <f>K10-L10-Assumptions!$B$21</f>
-        <v/>
+        <v>147000</v>
       </c>
       <c r="N10" s="17">
         <f>M10/J10</f>
-        <v/>
+        <v>19.90501921</v>
       </c>
       <c r="O10" s="18">
         <f>'CF_Calc'!U10</f>
-        <v/>
+        <v>-115264.1005</v>
       </c>
       <c r="P10" s="19">
         <f>'CF_Calc'!V10</f>
-        <v/>
+        <v>-0.1128356093</v>
       </c>
     </row>
     <row r="11">
@@ -3566,58 +3566,58 @@
       </c>
       <c r="C11" s="13">
         <f>B11/A11</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="D11" s="13" t="n">
         <v>301.2</v>
       </c>
       <c r="E11" s="14">
         <f>D11*Assumptions!$B$5</f>
-        <v/>
+        <v>7783.008</v>
       </c>
       <c r="F11" s="14">
         <f>B11*Assumptions!$B$13*Assumptions!$B$8*Assumptions!$B$9*Assumptions!$B$12</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G11" s="14">
         <f>A11*Assumptions!$B$25*Assumptions!$B$24</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H11" s="14">
         <f>A11*Assumptions!$B$28*Assumptions!$B$29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I11" s="14">
         <f>Assumptions!$B$41</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J11" s="14">
         <f>E11+F11+G11+H11+I11</f>
-        <v/>
+        <v>7783.008</v>
       </c>
       <c r="K11" s="14">
         <f>A11*Assumptions!$B$17+B11*Assumptions!$B$18+Assumptions!$B$19</f>
-        <v/>
+        <v>260000</v>
       </c>
       <c r="L11" s="14">
         <f>K11*Assumptions!$B$20</f>
-        <v/>
+        <v>78000</v>
       </c>
       <c r="M11" s="14">
         <f>K11-L11-Assumptions!$B$21</f>
-        <v/>
+        <v>182000</v>
       </c>
       <c r="N11" s="13">
         <f>M11/J11</f>
-        <v/>
+        <v>23.38427508</v>
       </c>
       <c r="O11" s="14">
         <f>'CF_Calc'!U11</f>
-        <v/>
+        <v>-154121.9531</v>
       </c>
       <c r="P11" s="15">
         <f>'CF_Calc'!V11</f>
-        <v/>
+        <v>-0.1475420424</v>
       </c>
     </row>
     <row r="12">
@@ -3629,58 +3629,58 @@
       </c>
       <c r="C12" s="17">
         <f>B12/A12</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D12" s="17" t="n">
         <v>285.8</v>
       </c>
       <c r="E12" s="18">
         <f>D12*Assumptions!$B$5</f>
-        <v/>
+        <v>7385.072</v>
       </c>
       <c r="F12" s="18">
         <f>B12*Assumptions!$B$13*Assumptions!$B$8*Assumptions!$B$9*Assumptions!$B$12</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G12" s="18">
         <f>A12*Assumptions!$B$25*Assumptions!$B$24</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H12" s="18">
         <f>A12*Assumptions!$B$28*Assumptions!$B$29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I12" s="18">
         <f>Assumptions!$B$41</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J12" s="18">
         <f>E12+F12+G12+H12+I12</f>
-        <v/>
+        <v>7385.072</v>
       </c>
       <c r="K12" s="18">
         <f>A12*Assumptions!$B$17+B12*Assumptions!$B$18+Assumptions!$B$19</f>
-        <v/>
+        <v>230000</v>
       </c>
       <c r="L12" s="18">
         <f>K12*Assumptions!$B$20</f>
-        <v/>
+        <v>69000</v>
       </c>
       <c r="M12" s="18">
         <f>K12-L12-Assumptions!$B$21</f>
-        <v/>
+        <v>161000</v>
       </c>
       <c r="N12" s="17">
         <f>M12/J12</f>
-        <v/>
+        <v>21.80073532</v>
       </c>
       <c r="O12" s="18">
         <f>'CF_Calc'!U12</f>
-        <v/>
+        <v>-132142.7313</v>
       </c>
       <c r="P12" s="19">
         <f>'CF_Calc'!V12</f>
-        <v/>
+        <v>-0.131715269</v>
       </c>
     </row>
     <row r="13">
@@ -3692,58 +3692,58 @@
       </c>
       <c r="C13" s="13">
         <f>B13/A13</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D13" s="13" t="n">
         <v>301.2</v>
       </c>
       <c r="E13" s="14">
         <f>D13*Assumptions!$B$5</f>
-        <v/>
+        <v>7783.008</v>
       </c>
       <c r="F13" s="14">
         <f>B13*Assumptions!$B$13*Assumptions!$B$8*Assumptions!$B$9*Assumptions!$B$12</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G13" s="14">
         <f>A13*Assumptions!$B$25*Assumptions!$B$24</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H13" s="14">
         <f>A13*Assumptions!$B$28*Assumptions!$B$29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I13" s="14">
         <f>Assumptions!$B$41</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J13" s="14">
         <f>E13+F13+G13+H13+I13</f>
-        <v/>
+        <v>7783.008</v>
       </c>
       <c r="K13" s="14">
         <f>A13*Assumptions!$B$17+B13*Assumptions!$B$18+Assumptions!$B$19</f>
-        <v/>
+        <v>300000</v>
       </c>
       <c r="L13" s="14">
         <f>K13*Assumptions!$B$20</f>
-        <v/>
+        <v>90000</v>
       </c>
       <c r="M13" s="14">
         <f>K13-L13-Assumptions!$B$21</f>
-        <v/>
+        <v>210000</v>
       </c>
       <c r="N13" s="13">
         <f>M13/J13</f>
-        <v/>
+        <v>26.98185586</v>
       </c>
       <c r="O13" s="14">
         <f>'CF_Calc'!U13</f>
-        <v/>
+        <v>-187879.2148</v>
       </c>
       <c r="P13" s="15">
         <f>'CF_Calc'!V13</f>
-        <v/>
+        <v>-0.1859918097</v>
       </c>
     </row>
     <row r="15">
@@ -3894,87 +3894,87 @@
       </c>
       <c r="B5">
         <f>'Sizing Comparison'!M5</f>
-        <v/>
+        <v>43400</v>
       </c>
       <c r="C5">
         <f>'Sizing Comparison'!J5</f>
-        <v/>
+        <v>3976.776</v>
       </c>
       <c r="D5">
         <f>'Sizing Comparison'!K5</f>
-        <v/>
+        <v>62000</v>
       </c>
       <c r="E5">
         <f>-B5</f>
-        <v/>
+        <v>-43400</v>
       </c>
       <c r="F5">
         <f>C5*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^0</f>
-        <v/>
+        <v>3046.776</v>
       </c>
       <c r="G5">
         <f>C5*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^1</f>
-        <v/>
+        <v>3025.690515</v>
       </c>
       <c r="H5">
         <f>C5*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^2</f>
-        <v/>
+        <v>3001.623271</v>
       </c>
       <c r="I5">
         <f>C5*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^3</f>
-        <v/>
+        <v>2974.437893</v>
       </c>
       <c r="J5">
         <f>C5*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^4</f>
-        <v/>
+        <v>2943.993042</v>
       </c>
       <c r="K5">
         <f>C5*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^5</f>
-        <v/>
+        <v>2910.142252</v>
       </c>
       <c r="L5">
         <f>C5*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^6</f>
-        <v/>
+        <v>2872.73376</v>
       </c>
       <c r="M5">
         <f>C5*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^7</f>
-        <v/>
+        <v>2831.610335</v>
       </c>
       <c r="N5">
         <f>C5*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^8</f>
-        <v/>
+        <v>2786.609097</v>
       </c>
       <c r="O5">
         <f>C5*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^9</f>
-        <v/>
+        <v>2737.561333</v>
       </c>
       <c r="P5">
         <f>C5*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^10</f>
-        <v/>
+        <v>2684.292309</v>
       </c>
       <c r="Q5">
         <f>C5*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^11</f>
-        <v/>
+        <v>2626.621073</v>
       </c>
       <c r="R5">
         <f>C5*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^12</f>
-        <v/>
+        <v>2564.36025</v>
       </c>
       <c r="S5">
         <f>C5*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^13</f>
-        <v/>
+        <v>2497.31584</v>
       </c>
       <c r="T5">
         <f>C5*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D5*Assumptions!$B$38*(1+Assumptions!$B$39)^14</f>
-        <v/>
+        <v>2425.286997</v>
       </c>
       <c r="U5">
         <f>NPV(Assumptions!$B$40,F5:T5)+E5</f>
-        <v/>
+        <v>-18958.1907</v>
       </c>
       <c r="V5">
         <f>IFERROR(IRR(E5:T5),"-")</f>
-        <v/>
+        <v>-0.004440704189</v>
       </c>
     </row>
     <row r="6">
@@ -3985,87 +3985,87 @@
       </c>
       <c r="B6">
         <f>'Sizing Comparison'!M6</f>
-        <v/>
+        <v>63000</v>
       </c>
       <c r="C6">
         <f>'Sizing Comparison'!J6</f>
-        <v/>
+        <v>5160.248</v>
       </c>
       <c r="D6">
         <f>'Sizing Comparison'!K6</f>
-        <v/>
+        <v>90000</v>
       </c>
       <c r="E6">
         <f>-B6</f>
-        <v/>
+        <v>-63000</v>
       </c>
       <c r="F6">
         <f>C6*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^0</f>
-        <v/>
+        <v>3810.248</v>
       </c>
       <c r="G6">
         <f>C6*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^1</f>
-        <v/>
+        <v>3780.022845</v>
       </c>
       <c r="H6">
         <f>C6*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^2</f>
-        <v/>
+        <v>3745.871277</v>
       </c>
       <c r="I6">
         <f>C6*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^3</f>
-        <v/>
+        <v>3707.615192</v>
       </c>
       <c r="J6">
         <f>C6*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^4</f>
-        <v/>
+        <v>3665.070019</v>
       </c>
       <c r="K6">
         <f>C6*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^5</f>
-        <v/>
+        <v>3618.044512</v>
       </c>
       <c r="L6">
         <f>C6*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^6</f>
-        <v/>
+        <v>3566.34053</v>
       </c>
       <c r="M6">
         <f>C6*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^7</f>
-        <v/>
+        <v>3509.752807</v>
       </c>
       <c r="N6">
         <f>C6*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^8</f>
-        <v/>
+        <v>3448.068728</v>
       </c>
       <c r="O6">
         <f>C6*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^9</f>
-        <v/>
+        <v>3381.068081</v>
       </c>
       <c r="P6">
         <f>C6*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^10</f>
-        <v/>
+        <v>3308.522815</v>
       </c>
       <c r="Q6">
         <f>C6*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^11</f>
-        <v/>
+        <v>3230.196784</v>
       </c>
       <c r="R6">
         <f>C6*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^12</f>
-        <v/>
+        <v>3145.845483</v>
       </c>
       <c r="S6">
         <f>C6*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^13</f>
-        <v/>
+        <v>3055.215781</v>
       </c>
       <c r="T6">
         <f>C6*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D6*Assumptions!$B$38*(1+Assumptions!$B$39)^14</f>
-        <v/>
+        <v>2958.045637</v>
       </c>
       <c r="U6">
         <f>NPV(Assumptions!$B$40,F6:T6)+E6</f>
-        <v/>
+        <v>-32658.82052</v>
       </c>
       <c r="V6">
         <f>IFERROR(IRR(E6:T6),"-")</f>
-        <v/>
+        <v>-0.02416452145</v>
       </c>
     </row>
     <row r="7">
@@ -4076,87 +4076,87 @@
       </c>
       <c r="B7">
         <f>'Sizing Comparison'!M7</f>
-        <v/>
+        <v>80500</v>
       </c>
       <c r="C7">
         <f>'Sizing Comparison'!J7</f>
-        <v/>
+        <v>6168.008</v>
       </c>
       <c r="D7">
         <f>'Sizing Comparison'!K7</f>
-        <v/>
+        <v>115000</v>
       </c>
       <c r="E7">
         <f>-B7</f>
-        <v/>
+        <v>-80500</v>
       </c>
       <c r="F7">
         <f>C7*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^0</f>
-        <v/>
+        <v>4443.008</v>
       </c>
       <c r="G7">
         <f>C7*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^1</f>
-        <v/>
+        <v>4404.652995</v>
       </c>
       <c r="H7">
         <f>C7*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^2</f>
-        <v/>
+        <v>4361.560235</v>
       </c>
       <c r="I7">
         <f>C7*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^3</f>
-        <v/>
+        <v>4313.515941</v>
       </c>
       <c r="J7">
         <f>C7*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^4</f>
-        <v/>
+        <v>4260.29859</v>
       </c>
       <c r="K7">
         <f>C7*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^5</f>
-        <v/>
+        <v>4201.678659</v>
       </c>
       <c r="L7">
         <f>C7*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^6</f>
-        <v/>
+        <v>4137.418366</v>
       </c>
       <c r="M7">
         <f>C7*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^7</f>
-        <v/>
+        <v>4067.271395</v>
       </c>
       <c r="N7">
         <f>C7*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^8</f>
-        <v/>
+        <v>3990.982623</v>
       </c>
       <c r="O7">
         <f>C7*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^9</f>
-        <v/>
+        <v>3908.287831</v>
       </c>
       <c r="P7">
         <f>C7*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^10</f>
-        <v/>
+        <v>3818.913407</v>
       </c>
       <c r="Q7">
         <f>C7*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^11</f>
-        <v/>
+        <v>3722.576044</v>
       </c>
       <c r="R7">
         <f>C7*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^12</f>
-        <v/>
+        <v>3618.982423</v>
       </c>
       <c r="S7">
         <f>C7*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^13</f>
-        <v/>
+        <v>3507.828891</v>
       </c>
       <c r="T7">
         <f>C7*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D7*Assumptions!$B$38*(1+Assumptions!$B$39)^14</f>
-        <v/>
+        <v>3388.801124</v>
       </c>
       <c r="U7">
         <f>NPV(Assumptions!$B$40,F7:T7)+E7</f>
-        <v/>
+        <v>-45301.89769</v>
       </c>
       <c r="V7">
         <f>IFERROR(IRR(E7:T7),"-")</f>
-        <v/>
+        <v>-0.035832867</v>
       </c>
     </row>
     <row r="8">
@@ -4167,87 +4167,87 @@
       </c>
       <c r="B8">
         <f>'Sizing Comparison'!M8</f>
-        <v/>
+        <v>87500</v>
       </c>
       <c r="C8">
         <f>'Sizing Comparison'!J8</f>
-        <v/>
+        <v>6168.008</v>
       </c>
       <c r="D8">
         <f>'Sizing Comparison'!K8</f>
-        <v/>
+        <v>125000</v>
       </c>
       <c r="E8">
         <f>-B8</f>
-        <v/>
+        <v>-87500</v>
       </c>
       <c r="F8">
         <f>C8*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^0</f>
-        <v/>
+        <v>4293.008</v>
       </c>
       <c r="G8">
         <f>C8*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^1</f>
-        <v/>
+        <v>4251.652995</v>
       </c>
       <c r="H8">
         <f>C8*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^2</f>
-        <v/>
+        <v>4205.500235</v>
       </c>
       <c r="I8">
         <f>C8*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^3</f>
-        <v/>
+        <v>4154.334741</v>
       </c>
       <c r="J8">
         <f>C8*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^4</f>
-        <v/>
+        <v>4097.933766</v>
       </c>
       <c r="K8">
         <f>C8*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^5</f>
-        <v/>
+        <v>4036.066539</v>
       </c>
       <c r="L8">
         <f>C8*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^6</f>
-        <v/>
+        <v>3968.494003</v>
       </c>
       <c r="M8">
         <f>C8*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^7</f>
-        <v/>
+        <v>3894.968545</v>
       </c>
       <c r="N8">
         <f>C8*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^8</f>
-        <v/>
+        <v>3815.233716</v>
       </c>
       <c r="O8">
         <f>C8*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^9</f>
-        <v/>
+        <v>3729.023946</v>
       </c>
       <c r="P8">
         <f>C8*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^10</f>
-        <v/>
+        <v>3636.064244</v>
       </c>
       <c r="Q8">
         <f>C8*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^11</f>
-        <v/>
+        <v>3536.069898</v>
       </c>
       <c r="R8">
         <f>C8*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^12</f>
-        <v/>
+        <v>3428.746154</v>
       </c>
       <c r="S8">
         <f>C8*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^13</f>
-        <v/>
+        <v>3313.787896</v>
       </c>
       <c r="T8">
         <f>C8*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D8*Assumptions!$B$38*(1+Assumptions!$B$39)^14</f>
-        <v/>
+        <v>3190.87931</v>
       </c>
       <c r="U8">
         <f>NPV(Assumptions!$B$40,F8:T8)+E8</f>
-        <v/>
+        <v>-53741.21312</v>
       </c>
       <c r="V8">
         <f>IFERROR(IRR(E8:T8),"-")</f>
-        <v/>
+        <v>-0.05043723692</v>
       </c>
     </row>
     <row r="9">
@@ -4258,87 +4258,87 @@
       </c>
       <c r="B9">
         <f>'Sizing Comparison'!M9</f>
-        <v/>
+        <v>112000</v>
       </c>
       <c r="C9">
         <f>'Sizing Comparison'!J9</f>
-        <v/>
+        <v>6744.24</v>
       </c>
       <c r="D9">
         <f>'Sizing Comparison'!K9</f>
-        <v/>
+        <v>160000</v>
       </c>
       <c r="E9">
         <f>-B9</f>
-        <v/>
+        <v>-112000</v>
       </c>
       <c r="F9">
         <f>C9*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^0</f>
-        <v/>
+        <v>4344.24</v>
       </c>
       <c r="G9">
         <f>C9*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^1</f>
-        <v/>
+        <v>4292.02485</v>
       </c>
       <c r="H9">
         <f>C9*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^2</f>
-        <v/>
+        <v>4234.423792</v>
       </c>
       <c r="I9">
         <f>C9*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^3</f>
-        <v/>
+        <v>4171.198967</v>
       </c>
       <c r="J9">
         <f>C9*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^4</f>
-        <v/>
+        <v>4102.103961</v>
       </c>
       <c r="K9">
         <f>C9*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^5</f>
-        <v/>
+        <v>4026.883532</v>
       </c>
       <c r="L9">
         <f>C9*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^6</f>
-        <v/>
+        <v>3945.273322</v>
       </c>
       <c r="M9">
         <f>C9*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^7</f>
-        <v/>
+        <v>3856.999554</v>
       </c>
       <c r="N9">
         <f>C9*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^8</f>
-        <v/>
+        <v>3761.778732</v>
       </c>
       <c r="O9">
         <f>C9*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^9</f>
-        <v/>
+        <v>3659.317323</v>
       </c>
       <c r="P9">
         <f>C9*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^10</f>
-        <v/>
+        <v>3549.311432</v>
       </c>
       <c r="Q9">
         <f>C9*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^11</f>
-        <v/>
+        <v>3431.446468</v>
       </c>
       <c r="R9">
         <f>C9*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^12</f>
-        <v/>
+        <v>3305.396796</v>
       </c>
       <c r="S9">
         <f>C9*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^13</f>
-        <v/>
+        <v>3170.825384</v>
       </c>
       <c r="T9">
         <f>C9*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D9*Assumptions!$B$38*(1+Assumptions!$B$39)^14</f>
-        <v/>
+        <v>3027.383434</v>
       </c>
       <c r="U9">
         <f>NPV(Assumptions!$B$40,F9:T9)+E9</f>
-        <v/>
+        <v>-78444.1706</v>
       </c>
       <c r="V9">
         <f>IFERROR(IRR(E9:T9),"-")</f>
-        <v/>
+        <v>-0.07851302868</v>
       </c>
     </row>
     <row r="10">
@@ -4349,87 +4349,87 @@
       </c>
       <c r="B10">
         <f>'Sizing Comparison'!M10</f>
-        <v/>
+        <v>147000</v>
       </c>
       <c r="C10">
         <f>'Sizing Comparison'!J10</f>
-        <v/>
+        <v>7385.072</v>
       </c>
       <c r="D10">
         <f>'Sizing Comparison'!K10</f>
-        <v/>
+        <v>210000</v>
       </c>
       <c r="E10">
         <f>-B10</f>
-        <v/>
+        <v>-147000</v>
       </c>
       <c r="F10">
         <f>C10*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^0</f>
-        <v/>
+        <v>4235.072</v>
       </c>
       <c r="G10">
         <f>C10*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^1</f>
-        <v/>
+        <v>4167.45633</v>
       </c>
       <c r="H10">
         <f>C10*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^2</f>
-        <v/>
+        <v>4093.734206</v>
       </c>
       <c r="I10">
         <f>C10*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^3</f>
-        <v/>
+        <v>4013.640992</v>
       </c>
       <c r="J10">
         <f>C10*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^4</f>
-        <v/>
+        <v>3926.902601</v>
       </c>
       <c r="K10">
         <f>C10*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^5</f>
-        <v/>
+        <v>3833.235194</v>
       </c>
       <c r="L10">
         <f>C10*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^6</f>
-        <v/>
+        <v>3732.344862</v>
       </c>
       <c r="M10">
         <f>C10*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^7</f>
-        <v/>
+        <v>3623.927295</v>
       </c>
       <c r="N10">
         <f>C10*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^8</f>
-        <v/>
+        <v>3507.667448</v>
       </c>
       <c r="O10">
         <f>C10*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^9</f>
-        <v/>
+        <v>3383.239196</v>
       </c>
       <c r="P10">
         <f>C10*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^10</f>
-        <v/>
+        <v>3250.304971</v>
       </c>
       <c r="Q10">
         <f>C10*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^11</f>
-        <v/>
+        <v>3108.515396</v>
       </c>
       <c r="R10">
         <f>C10*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^12</f>
-        <v/>
+        <v>2957.508906</v>
       </c>
       <c r="S10">
         <f>C10*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^13</f>
-        <v/>
+        <v>2796.911354</v>
       </c>
       <c r="T10">
         <f>C10*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D10*Assumptions!$B$38*(1+Assumptions!$B$39)^14</f>
-        <v/>
+        <v>2626.335608</v>
       </c>
       <c r="U10">
         <f>NPV(Assumptions!$B$40,F10:T10)+E10</f>
-        <v/>
+        <v>-115264.1005</v>
       </c>
       <c r="V10">
         <f>IFERROR(IRR(E10:T10),"-")</f>
-        <v/>
+        <v>-0.1128356093</v>
       </c>
     </row>
     <row r="11">
@@ -4440,87 +4440,87 @@
       </c>
       <c r="B11">
         <f>'Sizing Comparison'!M11</f>
-        <v/>
+        <v>182000</v>
       </c>
       <c r="C11">
         <f>'Sizing Comparison'!J11</f>
-        <v/>
+        <v>7783.008</v>
       </c>
       <c r="D11">
         <f>'Sizing Comparison'!K11</f>
-        <v/>
+        <v>260000</v>
       </c>
       <c r="E11">
         <f>-B11</f>
-        <v/>
+        <v>-182000</v>
       </c>
       <c r="F11">
         <f>C11*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^0</f>
-        <v/>
+        <v>3883.008</v>
       </c>
       <c r="G11">
         <f>C11*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^1</f>
-        <v/>
+        <v>3800.14362</v>
       </c>
       <c r="H11">
         <f>C11*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^2</f>
-        <v/>
+        <v>3710.611641</v>
       </c>
       <c r="I11">
         <f>C11*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^3</f>
-        <v/>
+        <v>3614.128523</v>
       </c>
       <c r="J11">
         <f>C11*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^4</f>
-        <v/>
+        <v>3510.400678</v>
       </c>
       <c r="K11">
         <f>C11*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^5</f>
-        <v/>
+        <v>3399.124143</v>
       </c>
       <c r="L11">
         <f>C11*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^6</f>
-        <v/>
+        <v>3279.984244</v>
       </c>
       <c r="M11">
         <f>C11*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^7</f>
-        <v/>
+        <v>3152.655249</v>
       </c>
       <c r="N11">
         <f>C11*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^8</f>
-        <v/>
+        <v>3016.800013</v>
       </c>
       <c r="O11">
         <f>C11*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^9</f>
-        <v/>
+        <v>2872.069609</v>
       </c>
       <c r="P11">
         <f>C11*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^10</f>
-        <v/>
+        <v>2718.102948</v>
       </c>
       <c r="Q11">
         <f>C11*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^11</f>
-        <v/>
+        <v>2554.526389</v>
       </c>
       <c r="R11">
         <f>C11*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^12</f>
-        <v/>
+        <v>2380.953336</v>
       </c>
       <c r="S11">
         <f>C11*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^13</f>
-        <v/>
+        <v>2196.983822</v>
       </c>
       <c r="T11">
         <f>C11*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D11*Assumptions!$B$38*(1+Assumptions!$B$39)^14</f>
-        <v/>
+        <v>2002.204083</v>
       </c>
       <c r="U11">
         <f>NPV(Assumptions!$B$40,F11:T11)+E11</f>
-        <v/>
+        <v>-154121.9531</v>
       </c>
       <c r="V11">
         <f>IFERROR(IRR(E11:T11),"-")</f>
-        <v/>
+        <v>-0.1475420424</v>
       </c>
     </row>
     <row r="12">
@@ -4531,87 +4531,87 @@
       </c>
       <c r="B12">
         <f>'Sizing Comparison'!M12</f>
-        <v/>
+        <v>161000</v>
       </c>
       <c r="C12">
         <f>'Sizing Comparison'!J12</f>
-        <v/>
+        <v>7385.072</v>
       </c>
       <c r="D12">
         <f>'Sizing Comparison'!K12</f>
-        <v/>
+        <v>230000</v>
       </c>
       <c r="E12">
         <f>-B12</f>
-        <v/>
+        <v>-161000</v>
       </c>
       <c r="F12">
         <f>C12*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^0</f>
-        <v/>
+        <v>3935.072</v>
       </c>
       <c r="G12">
         <f>C12*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^1</f>
-        <v/>
+        <v>3861.45633</v>
       </c>
       <c r="H12">
         <f>C12*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^2</f>
-        <v/>
+        <v>3781.614206</v>
       </c>
       <c r="I12">
         <f>C12*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^3</f>
-        <v/>
+        <v>3695.278592</v>
       </c>
       <c r="J12">
         <f>C12*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^4</f>
-        <v/>
+        <v>3602.172953</v>
       </c>
       <c r="K12">
         <f>C12*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^5</f>
-        <v/>
+        <v>3502.010953</v>
       </c>
       <c r="L12">
         <f>C12*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^6</f>
-        <v/>
+        <v>3394.496136</v>
       </c>
       <c r="M12">
         <f>C12*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^7</f>
-        <v/>
+        <v>3279.321594</v>
       </c>
       <c r="N12">
         <f>C12*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^8</f>
-        <v/>
+        <v>3156.169634</v>
       </c>
       <c r="O12">
         <f>C12*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^9</f>
-        <v/>
+        <v>3024.711425</v>
       </c>
       <c r="P12">
         <f>C12*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^10</f>
-        <v/>
+        <v>2884.606645</v>
       </c>
       <c r="Q12">
         <f>C12*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^11</f>
-        <v/>
+        <v>2735.503104</v>
       </c>
       <c r="R12">
         <f>C12*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^12</f>
-        <v/>
+        <v>2577.036368</v>
       </c>
       <c r="S12">
         <f>C12*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^13</f>
-        <v/>
+        <v>2408.829365</v>
       </c>
       <c r="T12">
         <f>C12*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D12*Assumptions!$B$38*(1+Assumptions!$B$39)^14</f>
-        <v/>
+        <v>2230.491979</v>
       </c>
       <c r="U12">
         <f>NPV(Assumptions!$B$40,F12:T12)+E12</f>
-        <v/>
+        <v>-132142.7313</v>
       </c>
       <c r="V12">
         <f>IFERROR(IRR(E12:T12),"-")</f>
-        <v/>
+        <v>-0.131715269</v>
       </c>
     </row>
     <row r="13">
@@ -4622,87 +4622,87 @@
       </c>
       <c r="B13">
         <f>'Sizing Comparison'!M13</f>
-        <v/>
+        <v>210000</v>
       </c>
       <c r="C13">
         <f>'Sizing Comparison'!J13</f>
-        <v/>
+        <v>7783.008</v>
       </c>
       <c r="D13">
         <f>'Sizing Comparison'!K13</f>
-        <v/>
+        <v>300000</v>
       </c>
       <c r="E13">
         <f>-B13</f>
-        <v/>
+        <v>-210000</v>
       </c>
       <c r="F13">
         <f>C13*(1+Assumptions!$B$7)^0*(1-Assumptions!$B$14*0)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^0</f>
-        <v/>
+        <v>3283.008</v>
       </c>
       <c r="G13">
         <f>C13*(1+Assumptions!$B$7)^1*(1-Assumptions!$B$14*1)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^1</f>
-        <v/>
+        <v>3188.14362</v>
       </c>
       <c r="H13">
         <f>C13*(1+Assumptions!$B$7)^2*(1-Assumptions!$B$14*2)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^2</f>
-        <v/>
+        <v>3086.371641</v>
       </c>
       <c r="I13">
         <f>C13*(1+Assumptions!$B$7)^3*(1-Assumptions!$B$14*3)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^3</f>
-        <v/>
+        <v>2977.403723</v>
       </c>
       <c r="J13">
         <f>C13*(1+Assumptions!$B$7)^4*(1-Assumptions!$B$14*4)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^4</f>
-        <v/>
+        <v>2860.941382</v>
       </c>
       <c r="K13">
         <f>C13*(1+Assumptions!$B$7)^5*(1-Assumptions!$B$14*5)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^5</f>
-        <v/>
+        <v>2736.675661</v>
       </c>
       <c r="L13">
         <f>C13*(1+Assumptions!$B$7)^6*(1-Assumptions!$B$14*6)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^6</f>
-        <v/>
+        <v>2604.286792</v>
       </c>
       <c r="M13">
         <f>C13*(1+Assumptions!$B$7)^7*(1-Assumptions!$B$14*7)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^7</f>
-        <v/>
+        <v>2463.443848</v>
       </c>
       <c r="N13">
         <f>C13*(1+Assumptions!$B$7)^8*(1-Assumptions!$B$14*8)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^8</f>
-        <v/>
+        <v>2313.804384</v>
       </c>
       <c r="O13">
         <f>C13*(1+Assumptions!$B$7)^9*(1-Assumptions!$B$14*9)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^9</f>
-        <v/>
+        <v>2155.014068</v>
       </c>
       <c r="P13">
         <f>C13*(1+Assumptions!$B$7)^10*(1-Assumptions!$B$14*10)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^10</f>
-        <v/>
+        <v>1986.706296</v>
       </c>
       <c r="Q13">
         <f>C13*(1+Assumptions!$B$7)^11*(1-Assumptions!$B$14*11)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^11</f>
-        <v/>
+        <v>1808.501804</v>
       </c>
       <c r="R13">
         <f>C13*(1+Assumptions!$B$7)^12*(1-Assumptions!$B$14*12)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^12</f>
-        <v/>
+        <v>1620.008259</v>
       </c>
       <c r="S13">
         <f>C13*(1+Assumptions!$B$7)^13*(1-Assumptions!$B$14*13)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^13</f>
-        <v/>
+        <v>1420.819844</v>
       </c>
       <c r="T13">
         <f>C13*(1+Assumptions!$B$7)^14*(1-Assumptions!$B$14*14)-D13*Assumptions!$B$38*(1+Assumptions!$B$39)^14</f>
-        <v/>
+        <v>1210.516825</v>
       </c>
       <c r="U13">
         <f>NPV(Assumptions!$B$40,F13:T13)+E13</f>
-        <v/>
+        <v>-187879.2148</v>
       </c>
       <c r="V13">
         <f>IFERROR(IRR(E13:T13),"-")</f>
-        <v/>
+        <v>-0.1859918097</v>
       </c>
     </row>
   </sheetData>
@@ -4800,19 +4800,19 @@
       </c>
       <c r="D6" s="26">
         <f>Assumptions!$B$32*Assumptions!$B$33*C6</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E6" s="26">
         <f>MIN(D6,B6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F6" s="26">
         <f>D6-E6</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G6" s="14">
         <f>E6*Assumptions!$B$4+F6*Assumptions!$B$35</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4829,19 +4829,19 @@
       </c>
       <c r="D7" s="26">
         <f>Assumptions!$B$32*Assumptions!$B$33*C7</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E7" s="26">
         <f>MIN(D7,B7)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F7" s="26">
         <f>D7-E7</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G7" s="14">
         <f>E7*Assumptions!$B$4+F7*Assumptions!$B$35</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4858,19 +4858,19 @@
       </c>
       <c r="D8" s="26">
         <f>Assumptions!$B$32*Assumptions!$B$33*C8</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E8" s="26">
         <f>MIN(D8,B8)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F8" s="26">
         <f>D8-E8</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G8" s="14">
         <f>E8*Assumptions!$B$4+F8*Assumptions!$B$35</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4887,19 +4887,19 @@
       </c>
       <c r="D9" s="26">
         <f>Assumptions!$B$32*Assumptions!$B$33*C9</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E9" s="26">
         <f>MIN(D9,B9)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F9" s="26">
         <f>D9-E9</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G9" s="14">
         <f>E9*Assumptions!$B$4+F9*Assumptions!$B$35</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4916,19 +4916,19 @@
       </c>
       <c r="D10" s="26">
         <f>Assumptions!$B$32*Assumptions!$B$33*C10</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E10" s="26">
         <f>MIN(D10,B10)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F10" s="26">
         <f>D10-E10</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G10" s="14">
         <f>E10*Assumptions!$B$4+F10*Assumptions!$B$35</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4945,19 +4945,19 @@
       </c>
       <c r="D11" s="26">
         <f>Assumptions!$B$32*Assumptions!$B$33*C11</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E11" s="26">
         <f>MIN(D11,B11)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F11" s="26">
         <f>D11-E11</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G11" s="14">
         <f>E11*Assumptions!$B$4+F11*Assumptions!$B$35</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4974,19 +4974,19 @@
       </c>
       <c r="D12" s="26">
         <f>Assumptions!$B$32*Assumptions!$B$33*C12</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E12" s="26">
         <f>MIN(D12,B12)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F12" s="26">
         <f>D12-E12</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G12" s="14">
         <f>E12*Assumptions!$B$4+F12*Assumptions!$B$35</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5003,19 +5003,19 @@
       </c>
       <c r="D13" s="26">
         <f>Assumptions!$B$32*Assumptions!$B$33*C13</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E13" s="26">
         <f>MIN(D13,B13)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F13" s="26">
         <f>D13-E13</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G13" s="14">
         <f>E13*Assumptions!$B$4+F13*Assumptions!$B$35</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -5032,19 +5032,19 @@
       </c>
       <c r="D14" s="26">
         <f>Assumptions!$B$32*Assumptions!$B$33*C14</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E14" s="26">
         <f>MIN(D14,B14)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F14" s="26">
         <f>D14-E14</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G14" s="14">
         <f>E14*Assumptions!$B$4+F14*Assumptions!$B$35</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5061,19 +5061,19 @@
       </c>
       <c r="D15" s="26">
         <f>Assumptions!$B$32*Assumptions!$B$33*C15</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E15" s="26">
         <f>MIN(D15,B15)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F15" s="26">
         <f>D15-E15</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G15" s="14">
         <f>E15*Assumptions!$B$4+F15*Assumptions!$B$35</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5090,19 +5090,19 @@
       </c>
       <c r="D16" s="26">
         <f>Assumptions!$B$32*Assumptions!$B$33*C16</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E16" s="26">
         <f>MIN(D16,B16)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F16" s="26">
         <f>D16-E16</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G16" s="14">
         <f>E16*Assumptions!$B$4+F16*Assumptions!$B$35</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5119,19 +5119,19 @@
       </c>
       <c r="D17" s="26">
         <f>Assumptions!$B$32*Assumptions!$B$33*C17</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E17" s="26">
         <f>MIN(D17,B17)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F17" s="26">
         <f>D17-E17</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G17" s="14">
         <f>E17*Assumptions!$B$4+F17*Assumptions!$B$35</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -5148,15 +5148,15 @@
       </c>
       <c r="E18" s="28">
         <f>SUM(E6:E17)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F18" s="28">
         <f>SUM(F6:F17)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G18" s="29">
         <f>SUM(G6:G17)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="B20" s="31">
         <f>Assumptions!$B$32*Assumptions!$B$34</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="B21" s="31">
         <f>B20*(1-Assumptions!$B$20)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="B22" s="31">
         <f>G18</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -5198,9 +5198,9 @@
           <t>PV simple payback (yr)</t>
         </is>
       </c>
-      <c r="B23" s="32">
+      <c t="str" r="B23" s="32">
         <f>IFERROR(B21/B22,"-")</f>
-        <v/>
+        <v>-</v>
       </c>
     </row>
     <row r="24">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="B24" s="33">
         <f>IFERROR(E18/D18,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="B5" s="14">
         <f>'Sizing Comparison'!E7</f>
-        <v/>
+        <v>6168.008</v>
       </c>
     </row>
     <row r="6">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="B6" s="14">
         <f>'Sizing Comparison'!F7</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="B7" s="14">
         <f>'Sizing Comparison'!G7</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="B8" s="14">
         <f>'Sizing Comparison'!H7</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="B9" s="14">
         <f>'Sizing Comparison'!I7</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="B10" s="14">
         <f>'Solar + Storage'!B22</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="B11" s="34">
         <f>SUM(B5:B10)</f>
-        <v/>
+        <v>6168.008</v>
       </c>
     </row>
     <row r="13">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="B13" s="31">
         <f>'Sizing Comparison'!M7</f>
-        <v/>
+        <v>80500</v>
       </c>
     </row>
     <row r="14">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="B14" s="31">
         <f>'Solar + Storage'!B21</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="B15" s="31">
         <f>B13+B14</f>
-        <v/>
+        <v>80500</v>
       </c>
     </row>
     <row r="17">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="B17" s="36">
         <f>IFERROR(B15/B11,"-")</f>
-        <v/>
+        <v>13.05121524</v>
       </c>
     </row>
   </sheetData>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="B6" s="33">
         <f>B5/B4</f>
-        <v/>
+        <v>0.2236727589</v>
       </c>
     </row>
     <row r="9">
@@ -5494,15 +5494,15 @@
       </c>
       <c r="D10" s="14">
         <f>C10*Assumptions!$B$5</f>
-        <v/>
+        <v>2090.456</v>
       </c>
       <c r="E10" s="14">
         <f>B10*Assumptions!$B$4</f>
-        <v/>
+        <v>3989.9602</v>
       </c>
       <c r="F10" s="14">
         <f>D10+E10</f>
-        <v/>
+        <v>6080.4162</v>
       </c>
     </row>
     <row r="11">
@@ -5519,15 +5519,15 @@
       </c>
       <c r="D11" s="14">
         <f>C11*Assumptions!$B$5</f>
-        <v/>
+        <v>2341.104</v>
       </c>
       <c r="E11" s="14">
         <f>B11*Assumptions!$B$4</f>
-        <v/>
+        <v>3817.2889</v>
       </c>
       <c r="F11" s="14">
         <f>D11+E11</f>
-        <v/>
+        <v>6158.3929</v>
       </c>
     </row>
     <row r="12">
@@ -5544,15 +5544,15 @@
       </c>
       <c r="D12" s="14">
         <f>C12*Assumptions!$B$5</f>
-        <v/>
+        <v>2904.416</v>
       </c>
       <c r="E12" s="14">
         <f>B12*Assumptions!$B$4</f>
-        <v/>
+        <v>4774.3559</v>
       </c>
       <c r="F12" s="14">
         <f>D12+E12</f>
-        <v/>
+        <v>7678.7719</v>
       </c>
     </row>
     <row r="13">
@@ -5569,15 +5569,15 @@
       </c>
       <c r="D13" s="14">
         <f>C13*Assumptions!$B$5</f>
-        <v/>
+        <v>2098.208</v>
       </c>
       <c r="E13" s="14">
         <f>B13*Assumptions!$B$4</f>
-        <v/>
+        <v>3119.9497</v>
       </c>
       <c r="F13" s="14">
         <f>D13+E13</f>
-        <v/>
+        <v>5218.1577</v>
       </c>
     </row>
     <row r="14">
@@ -5594,15 +5594,15 @@
       </c>
       <c r="D14" s="14">
         <f>C14*Assumptions!$B$5</f>
-        <v/>
+        <v>762.28</v>
       </c>
       <c r="E14" s="14">
         <f>B14*Assumptions!$B$4</f>
-        <v/>
+        <v>692.5705</v>
       </c>
       <c r="F14" s="14">
         <f>D14+E14</f>
-        <v/>
+        <v>1454.8505</v>
       </c>
     </row>
     <row r="15">
@@ -5619,15 +5619,15 @@
       </c>
       <c r="D15" s="14">
         <f>C15*Assumptions!$B$5</f>
-        <v/>
+        <v>684.76</v>
       </c>
       <c r="E15" s="14">
         <f>B15*Assumptions!$B$4</f>
-        <v/>
+        <v>528.4385</v>
       </c>
       <c r="F15" s="14">
         <f>D15+E15</f>
-        <v/>
+        <v>1213.1985</v>
       </c>
     </row>
     <row r="16">
@@ -5644,15 +5644,15 @@
       </c>
       <c r="D16" s="14">
         <f>C16*Assumptions!$B$5</f>
-        <v/>
+        <v>550.392</v>
       </c>
       <c r="E16" s="14">
         <f>B16*Assumptions!$B$4</f>
-        <v/>
+        <v>478.6444</v>
       </c>
       <c r="F16" s="14">
         <f>D16+E16</f>
-        <v/>
+        <v>1029.0364</v>
       </c>
     </row>
     <row r="17">
@@ -5669,15 +5669,15 @@
       </c>
       <c r="D17" s="14">
         <f>C17*Assumptions!$B$5</f>
-        <v/>
+        <v>620.16</v>
       </c>
       <c r="E17" s="14">
         <f>B17*Assumptions!$B$4</f>
-        <v/>
+        <v>384.6012</v>
       </c>
       <c r="F17" s="14">
         <f>D17+E17</f>
-        <v/>
+        <v>1004.7612</v>
       </c>
     </row>
     <row r="18">
@@ -5694,15 +5694,15 @@
       </c>
       <c r="D18" s="14">
         <f>C18*Assumptions!$B$5</f>
-        <v/>
+        <v>436.696</v>
       </c>
       <c r="E18" s="14">
         <f>B18*Assumptions!$B$4</f>
-        <v/>
+        <v>324.6043</v>
       </c>
       <c r="F18" s="14">
         <f>D18+E18</f>
-        <v/>
+        <v>761.3003</v>
       </c>
     </row>
     <row r="19">
@@ -5719,15 +5719,15 @@
       </c>
       <c r="D19" s="14">
         <f>C19*Assumptions!$B$5</f>
-        <v/>
+        <v>475.456</v>
       </c>
       <c r="E19" s="14">
         <f>B19*Assumptions!$B$4</f>
-        <v/>
+        <v>289.0054</v>
       </c>
       <c r="F19" s="14">
         <f>D19+E19</f>
-        <v/>
+        <v>764.4614</v>
       </c>
     </row>
     <row r="20">
@@ -5744,15 +5744,15 @@
       </c>
       <c r="D20" s="14">
         <f>C20*Assumptions!$B$5</f>
-        <v/>
+        <v>2969.016</v>
       </c>
       <c r="E20" s="14">
         <f>B20*Assumptions!$B$4</f>
-        <v/>
+        <v>3843.5722</v>
       </c>
       <c r="F20" s="14">
         <f>D20+E20</f>
-        <v/>
+        <v>6812.5882</v>
       </c>
     </row>
     <row r="21">
@@ -5769,15 +5769,15 @@
       </c>
       <c r="D21" s="14">
         <f>C21*Assumptions!$B$5</f>
-        <v/>
+        <v>1832.056</v>
       </c>
       <c r="E21" s="14">
         <f>B21*Assumptions!$B$4</f>
-        <v/>
+        <v>2679.1222</v>
       </c>
       <c r="F21" s="14">
         <f>D21+E21</f>
-        <v/>
+        <v>4511.1782</v>
       </c>
     </row>
     <row r="22">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="B22" s="27">
         <f>SUM(B10:B21)</f>
-        <v/>
+        <v>224726</v>
       </c>
       <c r="C22" s="12" t="n"/>
       <c r="D22" s="29">
@@ -5797,11 +5797,11 @@
       </c>
       <c r="E22" s="29">
         <f>SUM(E10:E21)</f>
-        <v/>
+        <v>24922.1134</v>
       </c>
       <c r="F22" s="29">
         <f>SUM(F10:F21)</f>
-        <v/>
+        <v>42687.1134</v>
       </c>
     </row>
   </sheetData>
@@ -5886,19 +5886,19 @@
       </c>
       <c r="D4" s="12">
         <f>B4-C4</f>
-        <v/>
+        <v>26.2</v>
       </c>
       <c r="E4" s="14">
         <f>B4*Assumptions!$B$5+35978*Assumptions!$B$4</f>
-        <v/>
+        <v>6080.4162</v>
       </c>
       <c r="F4" s="14">
         <f>C4*Assumptions!$B$5+35978*Assumptions!$B$4</f>
-        <v/>
+        <v>5403.4082</v>
       </c>
       <c r="G4" s="14">
         <f>E4-F4</f>
-        <v/>
+        <v>677.008</v>
       </c>
     </row>
     <row r="5">
@@ -5915,19 +5915,19 @@
       </c>
       <c r="D5" s="12">
         <f>B5-C5</f>
-        <v/>
+        <v>32.1</v>
       </c>
       <c r="E5" s="14">
         <f>B5*Assumptions!$B$5+34421*Assumptions!$B$4</f>
-        <v/>
+        <v>6158.3929</v>
       </c>
       <c r="F5" s="14">
         <f>C5*Assumptions!$B$5+34421*Assumptions!$B$4</f>
-        <v/>
+        <v>5328.9289</v>
       </c>
       <c r="G5" s="14">
         <f>E5-F5</f>
-        <v/>
+        <v>829.464</v>
       </c>
     </row>
     <row r="6">
@@ -5944,19 +5944,19 @@
       </c>
       <c r="D6" s="12">
         <f>B6-C6</f>
-        <v/>
+        <v>18.8</v>
       </c>
       <c r="E6" s="14">
         <f>B6*Assumptions!$B$5+43051*Assumptions!$B$4</f>
-        <v/>
+        <v>7678.7719</v>
       </c>
       <c r="F6" s="14">
         <f>C6*Assumptions!$B$5+43051*Assumptions!$B$4</f>
-        <v/>
+        <v>7192.9799</v>
       </c>
       <c r="G6" s="14">
         <f>E6-F6</f>
-        <v/>
+        <v>485.792</v>
       </c>
     </row>
     <row r="7">
@@ -5973,19 +5973,19 @@
       </c>
       <c r="D7" s="12">
         <f>B7-C7</f>
-        <v/>
+        <v>16.3</v>
       </c>
       <c r="E7" s="14">
         <f>B7*Assumptions!$B$5+28133*Assumptions!$B$4</f>
-        <v/>
+        <v>5218.1577</v>
       </c>
       <c r="F7" s="14">
         <f>C7*Assumptions!$B$5+28133*Assumptions!$B$4</f>
-        <v/>
+        <v>4796.9657</v>
       </c>
       <c r="G7" s="14">
         <f>E7-F7</f>
-        <v/>
+        <v>421.192</v>
       </c>
     </row>
     <row r="8">
@@ -6002,19 +6002,19 @@
       </c>
       <c r="D8" s="12">
         <f>B8-C8</f>
-        <v/>
+        <v>19.6</v>
       </c>
       <c r="E8" s="14">
         <f>B8*Assumptions!$B$5+6245*Assumptions!$B$4</f>
-        <v/>
+        <v>1454.8505</v>
       </c>
       <c r="F8" s="14">
         <f>C8*Assumptions!$B$5+6245*Assumptions!$B$4</f>
-        <v/>
+        <v>948.3865</v>
       </c>
       <c r="G8" s="14">
         <f>E8-F8</f>
-        <v/>
+        <v>506.464</v>
       </c>
     </row>
     <row r="9">
@@ -6031,19 +6031,19 @@
       </c>
       <c r="D9" s="12">
         <f>B9-C9</f>
-        <v/>
+        <v>15.1</v>
       </c>
       <c r="E9" s="14">
         <f>B9*Assumptions!$B$5+4765*Assumptions!$B$4</f>
-        <v/>
+        <v>1213.1985</v>
       </c>
       <c r="F9" s="14">
         <f>C9*Assumptions!$B$5+4765*Assumptions!$B$4</f>
-        <v/>
+        <v>823.0145</v>
       </c>
       <c r="G9" s="14">
         <f>E9-F9</f>
-        <v/>
+        <v>390.184</v>
       </c>
     </row>
     <row r="10">
@@ -6060,19 +6060,19 @@
       </c>
       <c r="D10" s="12">
         <f>B10-C10</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="E10" s="14">
         <f>B10*Assumptions!$B$5+4316*Assumptions!$B$4</f>
-        <v/>
+        <v>1029.0364</v>
       </c>
       <c r="F10" s="14">
         <f>C10*Assumptions!$B$5+4316*Assumptions!$B$4</f>
-        <v/>
+        <v>641.4364</v>
       </c>
       <c r="G10" s="14">
         <f>E10-F10</f>
-        <v/>
+        <v>387.6</v>
       </c>
     </row>
     <row r="11">
@@ -6089,19 +6089,19 @@
       </c>
       <c r="D11" s="12">
         <f>B11-C11</f>
-        <v/>
+        <v>18.4</v>
       </c>
       <c r="E11" s="14">
         <f>B11*Assumptions!$B$5+3468*Assumptions!$B$4</f>
-        <v/>
+        <v>1004.7612</v>
       </c>
       <c r="F11" s="14">
         <f>C11*Assumptions!$B$5+3468*Assumptions!$B$4</f>
-        <v/>
+        <v>529.3052</v>
       </c>
       <c r="G11" s="14">
         <f>E11-F11</f>
-        <v/>
+        <v>475.456</v>
       </c>
     </row>
     <row r="12">
@@ -6118,19 +6118,19 @@
       </c>
       <c r="D12" s="12">
         <f>B12-C12</f>
-        <v/>
+        <v>11.6</v>
       </c>
       <c r="E12" s="14">
         <f>B12*Assumptions!$B$5+2927*Assumptions!$B$4</f>
-        <v/>
+        <v>761.3003</v>
       </c>
       <c r="F12" s="14">
         <f>C12*Assumptions!$B$5+2927*Assumptions!$B$4</f>
-        <v/>
+        <v>461.5563</v>
       </c>
       <c r="G12" s="14">
         <f>E12-F12</f>
-        <v/>
+        <v>299.744</v>
       </c>
     </row>
     <row r="13">
@@ -6147,19 +6147,19 @@
       </c>
       <c r="D13" s="12">
         <f>B13-C13</f>
-        <v/>
+        <v>12.6</v>
       </c>
       <c r="E13" s="14">
         <f>B13*Assumptions!$B$5+2606*Assumptions!$B$4</f>
-        <v/>
+        <v>764.4614</v>
       </c>
       <c r="F13" s="14">
         <f>C13*Assumptions!$B$5+2606*Assumptions!$B$4</f>
-        <v/>
+        <v>438.8774</v>
       </c>
       <c r="G13" s="14">
         <f>E13-F13</f>
-        <v/>
+        <v>325.584</v>
       </c>
     </row>
     <row r="14">
@@ -6176,19 +6176,19 @@
       </c>
       <c r="D14" s="12">
         <f>B14-C14</f>
-        <v/>
+        <v>24.9</v>
       </c>
       <c r="E14" s="14">
         <f>B14*Assumptions!$B$5+34658*Assumptions!$B$4</f>
-        <v/>
+        <v>6812.5882</v>
       </c>
       <c r="F14" s="14">
         <f>C14*Assumptions!$B$5+34658*Assumptions!$B$4</f>
-        <v/>
+        <v>6169.1722</v>
       </c>
       <c r="G14" s="14">
         <f>E14-F14</f>
-        <v/>
+        <v>643.416</v>
       </c>
     </row>
     <row r="15">
@@ -6205,19 +6205,19 @@
       </c>
       <c r="D15" s="12">
         <f>B15-C15</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="E15" s="14">
         <f>B15*Assumptions!$B$5+24158*Assumptions!$B$4</f>
-        <v/>
+        <v>4511.1782</v>
       </c>
       <c r="F15" s="14">
         <f>C15*Assumptions!$B$5+24158*Assumptions!$B$4</f>
-        <v/>
+        <v>3787.6582</v>
       </c>
       <c r="G15" s="14">
         <f>E15-F15</f>
-        <v/>
+        <v>723.52</v>
       </c>
     </row>
     <row r="16">
@@ -6235,11 +6235,11 @@
       </c>
       <c r="F16" s="29">
         <f>SUM(F4:F15)</f>
-        <v/>
+        <v>36521.6894</v>
       </c>
       <c r="G16" s="29">
         <f>SUM(G4:G15)</f>
-        <v/>
+        <v>6165.424</v>
       </c>
     </row>
   </sheetData>
